--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D2AD962-7BE8-476A-A04A-F4DD934ED8AD}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7917E32D-DF88-497E-9A02-179212386FDD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="species" sheetId="1" r:id="rId1"/>
-    <sheet name="origin" sheetId="5" r:id="rId2"/>
-    <sheet name="codes" sheetId="6" r:id="rId3"/>
-    <sheet name="all data" sheetId="4" r:id="rId4"/>
+    <sheet name="colors" sheetId="7" r:id="rId2"/>
+    <sheet name="origin" sheetId="5" r:id="rId3"/>
+    <sheet name="codes" sheetId="6" r:id="rId4"/>
+    <sheet name="all data" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'all data'!$AC$1:$AC$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$D$1:$D$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'all data'!$AC$1:$AC$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">colors!$A$1:$A$335</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18946" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19616" uniqueCount="2268">
   <si>
     <t>ID</t>
   </si>
@@ -6812,6 +6813,48 @@
   </si>
   <si>
     <t xml:space="preserve"> yellowgreen</t>
+  </si>
+  <si>
+    <t>taxon</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>olive</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>tan</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>teal</t>
+  </si>
+  <si>
+    <t>thistle</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>American Yellowwood</t>
+  </si>
+  <si>
+    <t>yelowgreen</t>
+  </si>
+  <si>
+    <t>Yellowwood</t>
+  </si>
+  <si>
+    <t>Aesulus</t>
+  </si>
+  <si>
+    <t>Sambucus</t>
   </si>
 </sst>
 </file>
@@ -7332,7 +7375,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7359,7 +7402,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7719,7 +7770,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P442"/>
+  <dimension ref="A1:P301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
@@ -7731,8 +7782,9 @@
     <col min="10" max="10" width="15.7109375" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="13" width="16.85546875" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -7785,7 +7837,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7831,11 +7883,11 @@
       <c r="O2">
         <v>0.79</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P2" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7881,11 +7933,11 @@
       <c r="O3">
         <v>0.79</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7928,11 +7980,11 @@
       <c r="O4">
         <v>0.79</v>
       </c>
-      <c r="P4" s="12" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7978,11 +8030,11 @@
       <c r="O5">
         <v>0.79</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>318</v>
       </c>
@@ -8022,11 +8074,11 @@
       <c r="M6" t="s">
         <v>36</v>
       </c>
-      <c r="P6" s="7" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8066,11 +8118,11 @@
       <c r="M7" t="s">
         <v>36</v>
       </c>
-      <c r="P7" s="7" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8116,11 +8168,11 @@
       <c r="O8">
         <v>0.85</v>
       </c>
-      <c r="P8" s="7" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P8" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8160,11 +8212,11 @@
       <c r="M9" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>282</v>
       </c>
@@ -8204,11 +8256,11 @@
       <c r="M10" t="s">
         <v>36</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8254,11 +8306,11 @@
       <c r="O11">
         <v>0.84</v>
       </c>
-      <c r="P11" s="7" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -8304,11 +8356,11 @@
       <c r="O12">
         <v>0.84</v>
       </c>
-      <c r="P12" s="7" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -8354,11 +8406,11 @@
       <c r="O13">
         <v>0.85</v>
       </c>
-      <c r="P13" s="7" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -8404,11 +8456,11 @@
       <c r="O14">
         <v>0.83</v>
       </c>
-      <c r="P14" s="7" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -8454,11 +8506,11 @@
       <c r="O15">
         <v>0.84</v>
       </c>
-      <c r="P15" s="7" t="s">
-        <v>2122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -8501,11 +8553,11 @@
       <c r="O16">
         <v>0.84</v>
       </c>
-      <c r="P16" s="7" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -8551,11 +8603,11 @@
       <c r="O17">
         <v>0.84</v>
       </c>
-      <c r="P17" s="7" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -8601,11 +8653,11 @@
       <c r="O18">
         <v>0.8</v>
       </c>
-      <c r="P18" s="7" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -8651,11 +8703,11 @@
       <c r="O19">
         <v>0.74</v>
       </c>
-      <c r="P19" s="7" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -8701,11 +8753,11 @@
       <c r="O20">
         <v>0.88</v>
       </c>
-      <c r="P20" s="7" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -8751,11 +8803,11 @@
       <c r="O21">
         <v>0.88</v>
       </c>
-      <c r="P21" s="7" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -8801,11 +8853,11 @@
       <c r="O22">
         <v>0.79</v>
       </c>
-      <c r="P22" s="7" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P22" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -8851,11 +8903,11 @@
       <c r="O23">
         <v>0.88</v>
       </c>
-      <c r="P23" s="7" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -8898,11 +8950,11 @@
       <c r="O24">
         <v>0.88</v>
       </c>
-      <c r="P24" s="7" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>312</v>
       </c>
@@ -8945,11 +8997,11 @@
       <c r="O25">
         <v>0.82</v>
       </c>
-      <c r="P25" s="7" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -8995,11 +9047,11 @@
       <c r="O26">
         <v>0.82</v>
       </c>
-      <c r="P26" s="7" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -9045,11 +9097,11 @@
       <c r="O27">
         <v>0.82</v>
       </c>
-      <c r="P27" s="7" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P27" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -9095,11 +9147,11 @@
       <c r="O28">
         <v>0.82</v>
       </c>
-      <c r="P28" s="7" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P28" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -9145,11 +9197,11 @@
       <c r="O29">
         <v>0.82</v>
       </c>
-      <c r="P29" s="7" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P29" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -9195,11 +9247,11 @@
       <c r="O30">
         <v>0.82</v>
       </c>
-      <c r="P30" s="7" t="s">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P30" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -9242,11 +9294,11 @@
       <c r="O31">
         <v>0.82</v>
       </c>
-      <c r="P31" s="7" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P31" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -9292,11 +9344,11 @@
       <c r="O32">
         <v>0.82</v>
       </c>
-      <c r="P32" s="7" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -9342,11 +9394,11 @@
       <c r="O33">
         <v>0.82</v>
       </c>
-      <c r="P33" s="7" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -9392,11 +9444,11 @@
       <c r="O34">
         <v>0.79</v>
       </c>
-      <c r="P34" s="7" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P34" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -9442,11 +9494,11 @@
       <c r="O35">
         <v>0.88</v>
       </c>
-      <c r="P35" s="7" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P35" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -9492,11 +9544,11 @@
       <c r="O36">
         <v>0.88</v>
       </c>
-      <c r="P36" s="7" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P36" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -9539,11 +9591,11 @@
       <c r="O37">
         <v>0.7</v>
       </c>
-      <c r="P37" s="7" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P37" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -9589,11 +9641,11 @@
       <c r="O38">
         <v>0.88</v>
       </c>
-      <c r="P38" s="7" t="s">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>319</v>
       </c>
@@ -9636,11 +9688,11 @@
       <c r="O39">
         <v>0.88</v>
       </c>
-      <c r="P39" s="7" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P39" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>320</v>
       </c>
@@ -9677,11 +9729,11 @@
       <c r="M40" t="s">
         <v>36</v>
       </c>
-      <c r="P40" s="7" t="s">
-        <v>2147</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P40" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>36</v>
       </c>
@@ -9727,11 +9779,11 @@
       <c r="O41">
         <v>0.91</v>
       </c>
-      <c r="P41" s="7" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P41" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -9777,11 +9829,11 @@
       <c r="O42">
         <v>0.76</v>
       </c>
-      <c r="P42" s="7" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P42" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>38</v>
       </c>
@@ -9827,11 +9879,11 @@
       <c r="O43">
         <v>0.76</v>
       </c>
-      <c r="P43" s="7" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P43" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>39</v>
       </c>
@@ -9877,11 +9929,11 @@
       <c r="O44">
         <v>0.76</v>
       </c>
-      <c r="P44" s="7" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P44" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -9924,11 +9976,11 @@
       <c r="O45">
         <v>0.76</v>
       </c>
-      <c r="P45" s="7" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P45" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>41</v>
       </c>
@@ -9974,11 +10026,11 @@
       <c r="O46">
         <v>0.79</v>
       </c>
-      <c r="P46" s="7" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P46" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>42</v>
       </c>
@@ -10024,11 +10076,11 @@
       <c r="O47">
         <v>0.79</v>
       </c>
-      <c r="P47" s="7" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P47" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>43</v>
       </c>
@@ -10074,11 +10126,11 @@
       <c r="O48">
         <v>0.79</v>
       </c>
-      <c r="P48" s="7" t="s">
-        <v>2155</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P48" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -10121,11 +10173,11 @@
       <c r="O49">
         <v>0.7</v>
       </c>
-      <c r="P49" s="7" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P49" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>307</v>
       </c>
@@ -10165,11 +10217,11 @@
       <c r="M50" t="s">
         <v>36</v>
       </c>
-      <c r="P50" s="7" t="s">
-        <v>2157</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P50" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>45</v>
       </c>
@@ -10215,11 +10267,11 @@
       <c r="O51">
         <v>0.79</v>
       </c>
-      <c r="P51" s="7" t="s">
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P51" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>46</v>
       </c>
@@ -10265,11 +10317,11 @@
       <c r="O52">
         <v>0.79</v>
       </c>
-      <c r="P52" s="7" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P52" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>47</v>
       </c>
@@ -10315,11 +10367,11 @@
       <c r="O53">
         <v>0.79</v>
       </c>
-      <c r="P53" s="7" t="s">
+      <c r="P53" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>48</v>
       </c>
@@ -10365,11 +10417,11 @@
       <c r="O54">
         <v>0.79</v>
       </c>
-      <c r="P54" s="7" t="s">
+      <c r="P54" t="s">
         <v>2161</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>49</v>
       </c>
@@ -10415,11 +10467,11 @@
       <c r="O55">
         <v>0.79</v>
       </c>
-      <c r="P55" s="7" t="s">
-        <v>2162</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P55" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>50</v>
       </c>
@@ -10465,11 +10517,11 @@
       <c r="O56">
         <v>0.79</v>
       </c>
-      <c r="P56" s="7" t="s">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P56" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>51</v>
       </c>
@@ -10515,11 +10567,11 @@
       <c r="O57">
         <v>0.79</v>
       </c>
-      <c r="P57" s="7" t="s">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P57" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>52</v>
       </c>
@@ -10565,11 +10617,11 @@
       <c r="O58">
         <v>0.79</v>
       </c>
-      <c r="P58" s="7" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P58" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>53</v>
       </c>
@@ -10615,11 +10667,11 @@
       <c r="O59">
         <v>0.79</v>
       </c>
-      <c r="P59" s="7" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P59" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>54</v>
       </c>
@@ -10665,11 +10717,11 @@
       <c r="O60">
         <v>0.79</v>
       </c>
-      <c r="P60" s="7" t="s">
-        <v>2167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P60" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>55</v>
       </c>
@@ -10715,11 +10767,11 @@
       <c r="O61">
         <v>0.79</v>
       </c>
-      <c r="P61" s="7" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P61" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>56</v>
       </c>
@@ -10765,11 +10817,11 @@
       <c r="O62">
         <v>0.79</v>
       </c>
-      <c r="P62" s="7" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P62" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>57</v>
       </c>
@@ -10815,11 +10867,11 @@
       <c r="O63">
         <v>0.79</v>
       </c>
-      <c r="P63" s="7" t="s">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P63" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>58</v>
       </c>
@@ -10859,11 +10911,11 @@
       <c r="M64" t="s">
         <v>36</v>
       </c>
-      <c r="P64" s="7" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P64" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>59</v>
       </c>
@@ -10906,11 +10958,11 @@
       <c r="O65">
         <v>0.79</v>
       </c>
-      <c r="P65" s="7" t="s">
-        <v>2172</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P65" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>60</v>
       </c>
@@ -10956,11 +11008,11 @@
       <c r="O66">
         <v>0.86</v>
       </c>
-      <c r="P66" s="7" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P66" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>61</v>
       </c>
@@ -11006,11 +11058,11 @@
       <c r="O67">
         <v>0.79</v>
       </c>
-      <c r="P67" s="7" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P67" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>62</v>
       </c>
@@ -11056,11 +11108,11 @@
       <c r="O68">
         <v>0.85</v>
       </c>
-      <c r="P68" s="7" t="s">
-        <v>2175</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P68" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
@@ -11106,11 +11158,11 @@
       <c r="O69">
         <v>0.85</v>
       </c>
-      <c r="P69" s="7" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P69" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
@@ -11156,11 +11208,11 @@
       <c r="O70">
         <v>0.85</v>
       </c>
-      <c r="P70" s="7" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P70" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
@@ -11206,11 +11258,11 @@
       <c r="O71">
         <v>0.79</v>
       </c>
-      <c r="P71" s="7" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P71" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>67</v>
       </c>
@@ -11250,11 +11302,11 @@
       <c r="M72" t="s">
         <v>36</v>
       </c>
-      <c r="P72" s="7" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P72" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
@@ -11300,11 +11352,11 @@
       <c r="O73">
         <v>0.79</v>
       </c>
-      <c r="P73" s="7" t="s">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P73" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
@@ -11350,11 +11402,11 @@
       <c r="O74">
         <v>0.79</v>
       </c>
-      <c r="P74" s="7" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P74" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>70</v>
       </c>
@@ -11400,11 +11452,11 @@
       <c r="O75">
         <v>0.79</v>
       </c>
-      <c r="P75" s="7" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P75" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>289</v>
       </c>
@@ -11444,11 +11496,11 @@
       <c r="M76" t="s">
         <v>36</v>
       </c>
-      <c r="P76" s="7" t="s">
-        <v>2183</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P76" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>71</v>
       </c>
@@ -11494,11 +11546,11 @@
       <c r="O77">
         <v>0.79</v>
       </c>
-      <c r="P77" s="7" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P77" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>72</v>
       </c>
@@ -11544,11 +11596,11 @@
       <c r="O78">
         <v>0.79</v>
       </c>
-      <c r="P78" s="7" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P78" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>313</v>
       </c>
@@ -11588,11 +11640,11 @@
       <c r="M79" t="s">
         <v>36</v>
       </c>
-      <c r="P79" s="7" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P79" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>73</v>
       </c>
@@ -11635,11 +11687,11 @@
       <c r="O80">
         <v>0.79</v>
       </c>
-      <c r="P80" s="7" t="s">
-        <v>2187</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P80" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>75</v>
       </c>
@@ -11682,11 +11734,11 @@
       <c r="O81">
         <v>0.7</v>
       </c>
-      <c r="P81" s="7" t="s">
-        <v>2188</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P81" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>76</v>
       </c>
@@ -11732,11 +11784,11 @@
       <c r="O82">
         <v>0.87</v>
       </c>
-      <c r="P82" s="7" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P82" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>77</v>
       </c>
@@ -11782,11 +11834,11 @@
       <c r="O83">
         <v>0.86</v>
       </c>
-      <c r="P83" s="7" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P83" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>314</v>
       </c>
@@ -11829,11 +11881,11 @@
       <c r="N84">
         <v>0.35</v>
       </c>
-      <c r="P84" s="7" t="s">
-        <v>2191</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P84" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>78</v>
       </c>
@@ -11879,11 +11931,11 @@
       <c r="O85">
         <v>0.86</v>
       </c>
-      <c r="P85" s="7" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P85" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>79</v>
       </c>
@@ -11929,11 +11981,11 @@
       <c r="O86">
         <v>0.86</v>
       </c>
-      <c r="P86" s="7" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P86" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>80</v>
       </c>
@@ -11979,11 +12031,11 @@
       <c r="O87">
         <v>0.86</v>
       </c>
-      <c r="P87" s="7" t="s">
+      <c r="P87" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>81</v>
       </c>
@@ -12029,11 +12081,11 @@
       <c r="O88">
         <v>0.86</v>
       </c>
-      <c r="P88" s="7" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P88" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>82</v>
       </c>
@@ -12079,11 +12131,11 @@
       <c r="O89">
         <v>0.86</v>
       </c>
-      <c r="P89" s="7" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P89" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>83</v>
       </c>
@@ -12129,11 +12181,11 @@
       <c r="O90">
         <v>0.85</v>
       </c>
-      <c r="P90" s="7" t="s">
-        <v>2197</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P90" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>84</v>
       </c>
@@ -12179,11 +12231,11 @@
       <c r="O91">
         <v>0.86</v>
       </c>
-      <c r="P91" s="7" t="s">
-        <v>2198</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P91" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>85</v>
       </c>
@@ -12226,11 +12278,11 @@
       <c r="O92">
         <v>0.86</v>
       </c>
-      <c r="P92" s="7" t="s">
-        <v>2199</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P92" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>86</v>
       </c>
@@ -12276,11 +12328,11 @@
       <c r="O93">
         <v>0.79</v>
       </c>
-      <c r="P93" s="7" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P93" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>87</v>
       </c>
@@ -12323,11 +12375,11 @@
       <c r="O94">
         <v>0.7</v>
       </c>
-      <c r="P94" s="7" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P94" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>88</v>
       </c>
@@ -12373,11 +12425,11 @@
       <c r="O95">
         <v>0.79</v>
       </c>
-      <c r="P95" s="7" t="s">
-        <v>2202</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P95" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>89</v>
       </c>
@@ -12423,11 +12475,11 @@
       <c r="O96">
         <v>0.79</v>
       </c>
-      <c r="P96" s="7" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P96" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>90</v>
       </c>
@@ -12473,11 +12525,11 @@
       <c r="O97">
         <v>0.79</v>
       </c>
-      <c r="P97" s="7" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P97" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>91</v>
       </c>
@@ -12523,11 +12575,11 @@
       <c r="O98">
         <v>0.79</v>
       </c>
-      <c r="P98" s="7" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P98" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>92</v>
       </c>
@@ -12570,11 +12622,11 @@
       <c r="O99">
         <v>0.79</v>
       </c>
-      <c r="P99" s="7" t="s">
-        <v>2206</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P99" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>93</v>
       </c>
@@ -12620,11 +12672,11 @@
       <c r="O100">
         <v>0.79</v>
       </c>
-      <c r="P100" s="7" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P100" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>94</v>
       </c>
@@ -12670,11 +12722,11 @@
       <c r="O101">
         <v>0.79</v>
       </c>
-      <c r="P101" s="7" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P101" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>95</v>
       </c>
@@ -12714,11 +12766,11 @@
       <c r="M102" t="s">
         <v>36</v>
       </c>
-      <c r="P102" s="7" t="s">
-        <v>2209</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P102" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>96</v>
       </c>
@@ -12764,11 +12816,11 @@
       <c r="O103">
         <v>0.81</v>
       </c>
-      <c r="P103" s="7" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P103" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>97</v>
       </c>
@@ -12814,11 +12866,11 @@
       <c r="O104">
         <v>0.79</v>
       </c>
-      <c r="P104" s="7" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P104" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>98</v>
       </c>
@@ -12864,11 +12916,11 @@
       <c r="O105">
         <v>0.79</v>
       </c>
-      <c r="P105" s="7" t="s">
-        <v>2212</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P105" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>99</v>
       </c>
@@ -12914,11 +12966,11 @@
       <c r="O106">
         <v>0.88</v>
       </c>
-      <c r="P106" s="7" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P106" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>100</v>
       </c>
@@ -12964,11 +13016,11 @@
       <c r="O107">
         <v>0.88</v>
       </c>
-      <c r="P107" s="7" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P107" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>101</v>
       </c>
@@ -13014,11 +13066,11 @@
       <c r="O108">
         <v>0.88</v>
       </c>
-      <c r="P108" s="7" t="s">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P108" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>102</v>
       </c>
@@ -13064,11 +13116,11 @@
       <c r="O109">
         <v>0.86</v>
       </c>
-      <c r="P109" s="7" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P109" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>103</v>
       </c>
@@ -13114,11 +13166,11 @@
       <c r="O110">
         <v>0.89</v>
       </c>
-      <c r="P110" s="7" t="s">
-        <v>2217</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P110" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>290</v>
       </c>
@@ -13158,11 +13210,11 @@
       <c r="M111" t="s">
         <v>36</v>
       </c>
-      <c r="P111" s="7" t="s">
-        <v>2218</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P111" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>104</v>
       </c>
@@ -13208,11 +13260,11 @@
       <c r="O112">
         <v>0.88</v>
       </c>
-      <c r="P112" s="7" t="s">
-        <v>2219</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P112" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>105</v>
       </c>
@@ -13255,11 +13307,11 @@
       <c r="O113">
         <v>0.88</v>
       </c>
-      <c r="P113" s="7" t="s">
-        <v>2220</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P113" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>106</v>
       </c>
@@ -13305,11 +13357,11 @@
       <c r="O114">
         <v>0.79</v>
       </c>
-      <c r="P114" s="7" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P114" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>107</v>
       </c>
@@ -13355,11 +13407,11 @@
       <c r="O115">
         <v>0.79</v>
       </c>
-      <c r="P115" s="7" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P115" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>108</v>
       </c>
@@ -13405,11 +13457,11 @@
       <c r="O116">
         <v>0.79</v>
       </c>
-      <c r="P116" s="7" t="s">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P116" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>109</v>
       </c>
@@ -13446,11 +13498,11 @@
       <c r="M117" t="s">
         <v>36</v>
       </c>
-      <c r="P117" s="7" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P117" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>110</v>
       </c>
@@ -13496,11 +13548,11 @@
       <c r="O118">
         <v>0.79</v>
       </c>
-      <c r="P118" s="7" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P118" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>111</v>
       </c>
@@ -13546,11 +13598,11 @@
       <c r="O119">
         <v>0.77</v>
       </c>
-      <c r="P119" s="7" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P119" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>112</v>
       </c>
@@ -13596,11 +13648,11 @@
       <c r="O120">
         <v>0.77</v>
       </c>
-      <c r="P120" s="7" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P120" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>113</v>
       </c>
@@ -13646,11 +13698,11 @@
       <c r="O121">
         <v>0.77</v>
       </c>
-      <c r="P121" s="7" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P121" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>114</v>
       </c>
@@ -13696,11 +13748,11 @@
       <c r="O122">
         <v>0.77</v>
       </c>
-      <c r="P122" s="7" t="s">
-        <v>2229</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P122" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>115</v>
       </c>
@@ -13743,11 +13795,11 @@
       <c r="O123">
         <v>0.77</v>
       </c>
-      <c r="P123" s="7" t="s">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P123" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>116</v>
       </c>
@@ -13787,11 +13839,11 @@
       <c r="M124" t="s">
         <v>36</v>
       </c>
-      <c r="P124" s="7" t="s">
-        <v>2231</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P124" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>300</v>
       </c>
@@ -13831,11 +13883,11 @@
       <c r="M125" t="s">
         <v>36</v>
       </c>
-      <c r="P125" s="7" t="s">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P125" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>117</v>
       </c>
@@ -13875,11 +13927,11 @@
       <c r="M126" t="s">
         <v>36</v>
       </c>
-      <c r="P126" s="7" t="s">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P126" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>118</v>
       </c>
@@ -13925,11 +13977,11 @@
       <c r="O127">
         <v>0.79</v>
       </c>
-      <c r="P127" s="7" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P127" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>119</v>
       </c>
@@ -13975,11 +14027,11 @@
       <c r="O128">
         <v>0.88</v>
       </c>
-      <c r="P128" s="7" t="s">
-        <v>2235</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P128" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>120</v>
       </c>
@@ -14025,11 +14077,11 @@
       <c r="O129">
         <v>0.79</v>
       </c>
-      <c r="P129" s="7" t="s">
-        <v>2236</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P129" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>121</v>
       </c>
@@ -14075,11 +14127,11 @@
       <c r="O130">
         <v>0.88</v>
       </c>
-      <c r="P130" s="7" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P130" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>122</v>
       </c>
@@ -14119,11 +14171,11 @@
       <c r="M131" t="s">
         <v>36</v>
       </c>
-      <c r="P131" s="7" t="s">
-        <v>2238</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P131" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>123</v>
       </c>
@@ -14169,11 +14221,11 @@
       <c r="O132">
         <v>0.8</v>
       </c>
-      <c r="P132" s="7" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P132" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>124</v>
       </c>
@@ -14219,11 +14271,11 @@
       <c r="O133">
         <v>0.79</v>
       </c>
-      <c r="P133" s="7" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P133" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>304</v>
       </c>
@@ -14263,11 +14315,11 @@
       <c r="M134" t="s">
         <v>36</v>
       </c>
-      <c r="P134" s="7" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P134" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>125</v>
       </c>
@@ -14313,11 +14365,11 @@
       <c r="O135">
         <v>0.79</v>
       </c>
-      <c r="P135" s="7" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P135" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>301</v>
       </c>
@@ -14357,11 +14409,11 @@
       <c r="M136" t="s">
         <v>36</v>
       </c>
-      <c r="P136" s="7" t="s">
-        <v>2243</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P136" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>302</v>
       </c>
@@ -14401,11 +14453,11 @@
       <c r="M137" t="s">
         <v>36</v>
       </c>
-      <c r="P137" s="7" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P137" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126</v>
       </c>
@@ -14451,11 +14503,11 @@
       <c r="O138">
         <v>0.79</v>
       </c>
-      <c r="P138" s="7" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P138" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>127</v>
       </c>
@@ -14498,11 +14550,11 @@
       <c r="O139">
         <v>0.79</v>
       </c>
-      <c r="P139" s="7" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P139" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>128</v>
       </c>
@@ -14548,11 +14600,11 @@
       <c r="O140">
         <v>0.79</v>
       </c>
-      <c r="P140" s="7" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P140" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>129</v>
       </c>
@@ -14598,11 +14650,11 @@
       <c r="O141">
         <v>0.79</v>
       </c>
-      <c r="P141" s="7" t="s">
-        <v>2248</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P141" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>130</v>
       </c>
@@ -14648,11 +14700,11 @@
       <c r="O142">
         <v>0.79</v>
       </c>
-      <c r="P142" s="7" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P142" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>131</v>
       </c>
@@ -14698,11 +14750,11 @@
       <c r="O143">
         <v>0.79</v>
       </c>
-      <c r="P143" s="7" t="s">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P143" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>132</v>
       </c>
@@ -14745,11 +14797,11 @@
       <c r="O144">
         <v>0.79</v>
       </c>
-      <c r="P144" s="7" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P144" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>133</v>
       </c>
@@ -14795,11 +14847,11 @@
       <c r="O145">
         <v>0.79</v>
       </c>
-      <c r="P145" s="7" t="s">
-        <v>2252</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P145" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>134</v>
       </c>
@@ -14845,11 +14897,11 @@
       <c r="O146">
         <v>0.79</v>
       </c>
-      <c r="P146" s="7" t="s">
-        <v>2253</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P146" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>135</v>
       </c>
@@ -14892,11 +14944,11 @@
       <c r="O147">
         <v>0.79</v>
       </c>
-      <c r="P147" s="7" t="s">
-        <v>2252</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P147" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>136</v>
       </c>
@@ -14942,11 +14994,11 @@
       <c r="O148">
         <v>0.88</v>
       </c>
-      <c r="P148" s="7" t="s">
-        <v>2253</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P148" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>137</v>
       </c>
@@ -14992,11 +15044,11 @@
       <c r="O149">
         <v>0.88</v>
       </c>
-      <c r="P149" s="7" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P149" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>138</v>
       </c>
@@ -15042,11 +15094,11 @@
       <c r="O150">
         <v>0.88</v>
       </c>
-      <c r="P150" s="7" t="s">
+      <c r="P150" t="s">
         <v>2110</v>
       </c>
     </row>
-    <row r="151" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>139</v>
       </c>
@@ -15092,11 +15144,11 @@
       <c r="O151">
         <v>0.88</v>
       </c>
-      <c r="P151" s="12" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P151" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>140</v>
       </c>
@@ -15142,11 +15194,11 @@
       <c r="O152">
         <v>0.88</v>
       </c>
-      <c r="P152" s="7" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P152" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>141</v>
       </c>
@@ -15189,11 +15241,11 @@
       <c r="O153">
         <v>0.88</v>
       </c>
-      <c r="P153" s="7" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P153" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>142</v>
       </c>
@@ -15239,11 +15291,11 @@
       <c r="O154">
         <v>0.79</v>
       </c>
-      <c r="P154" s="7" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P154" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>143</v>
       </c>
@@ -15289,11 +15341,11 @@
       <c r="O155">
         <v>0.67</v>
       </c>
-      <c r="P155" s="7" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P155" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>144</v>
       </c>
@@ -15339,11 +15391,11 @@
       <c r="O156">
         <v>0.79</v>
       </c>
-      <c r="P156" s="7" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P156" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>145</v>
       </c>
@@ -15386,11 +15438,11 @@
       <c r="O157">
         <v>0.79</v>
       </c>
-      <c r="P157" s="7" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P157" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>146</v>
       </c>
@@ -15436,11 +15488,11 @@
       <c r="O158">
         <v>0.79</v>
       </c>
-      <c r="P158" s="7" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P158" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>147</v>
       </c>
@@ -15486,11 +15538,11 @@
       <c r="O159">
         <v>0.79</v>
       </c>
-      <c r="P159" s="7" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P159" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>148</v>
       </c>
@@ -15536,11 +15588,11 @@
       <c r="O160">
         <v>0.91</v>
       </c>
-      <c r="P160" s="7" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P160" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>149</v>
       </c>
@@ -15586,11 +15638,11 @@
       <c r="O161">
         <v>0.86</v>
       </c>
-      <c r="P161" s="7" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P161" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>150</v>
       </c>
@@ -15636,11 +15688,11 @@
       <c r="O162">
         <v>0.86</v>
       </c>
-      <c r="P162" s="7" t="s">
-        <v>2122</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P162" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>151</v>
       </c>
@@ -15686,11 +15738,11 @@
       <c r="O163">
         <v>0.86</v>
       </c>
-      <c r="P163" s="7" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P163" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>152</v>
       </c>
@@ -15736,11 +15788,11 @@
       <c r="O164">
         <v>0.86</v>
       </c>
-      <c r="P164" s="7" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P164" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>153</v>
       </c>
@@ -15786,11 +15838,11 @@
       <c r="O165">
         <v>0.86</v>
       </c>
-      <c r="P165" s="7" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P165" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>154</v>
       </c>
@@ -15836,11 +15888,11 @@
       <c r="O166">
         <v>0.86</v>
       </c>
-      <c r="P166" s="7" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P166" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>155</v>
       </c>
@@ -15886,11 +15938,11 @@
       <c r="O167">
         <v>0.88</v>
       </c>
-      <c r="P167" s="7" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P167" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>303</v>
       </c>
@@ -15933,11 +15985,11 @@
       <c r="N168">
         <v>0.65</v>
       </c>
-      <c r="P168" s="7" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P168" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>156</v>
       </c>
@@ -15983,11 +16035,11 @@
       <c r="O169">
         <v>0.83</v>
       </c>
-      <c r="P169" s="7" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P169" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>157</v>
       </c>
@@ -16033,11 +16085,11 @@
       <c r="O170">
         <v>0.83</v>
       </c>
-      <c r="P170" s="7" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P170" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>158</v>
       </c>
@@ -16080,11 +16132,11 @@
       <c r="O171">
         <v>0.86</v>
       </c>
-      <c r="P171" s="7" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P171" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>159</v>
       </c>
@@ -16130,11 +16182,11 @@
       <c r="O172">
         <v>0.86</v>
       </c>
-      <c r="P172" s="7" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P172" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>160</v>
       </c>
@@ -16180,11 +16232,11 @@
       <c r="O173">
         <v>0.84</v>
       </c>
-      <c r="P173" s="7" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P173" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>161</v>
       </c>
@@ -16230,11 +16282,11 @@
       <c r="O174">
         <v>0.86</v>
       </c>
-      <c r="P174" s="7" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P174" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>162</v>
       </c>
@@ -16280,11 +16332,11 @@
       <c r="O175">
         <v>0.86</v>
       </c>
-      <c r="P175" s="7" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P175" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>163</v>
       </c>
@@ -16330,11 +16382,11 @@
       <c r="O176">
         <v>0.79</v>
       </c>
-      <c r="P176" s="7" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P176" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>164</v>
       </c>
@@ -16380,11 +16432,11 @@
       <c r="O177">
         <v>0.79</v>
       </c>
-      <c r="P177" s="7" t="s">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P177" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>165</v>
       </c>
@@ -16430,11 +16482,11 @@
       <c r="O178">
         <v>0.79</v>
       </c>
-      <c r="P178" s="7" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P178" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>166</v>
       </c>
@@ -16480,11 +16532,11 @@
       <c r="O179">
         <v>0.79</v>
       </c>
-      <c r="P179" s="7" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P179" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>167</v>
       </c>
@@ -16530,11 +16582,11 @@
       <c r="O180">
         <v>0.79</v>
       </c>
-      <c r="P180" s="7" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P180" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>168</v>
       </c>
@@ -16580,11 +16632,11 @@
       <c r="O181">
         <v>0.79</v>
       </c>
-      <c r="P181" s="7" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P181" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>169</v>
       </c>
@@ -16630,11 +16682,11 @@
       <c r="O182">
         <v>0.79</v>
       </c>
-      <c r="P182" s="7" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P182" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>170</v>
       </c>
@@ -16677,11 +16729,11 @@
       <c r="O183">
         <v>0.79</v>
       </c>
-      <c r="P183" s="7" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P183" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>171</v>
       </c>
@@ -16727,11 +16779,11 @@
       <c r="O184">
         <v>0.79</v>
       </c>
-      <c r="P184" s="7" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P184" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>172</v>
       </c>
@@ -16777,11 +16829,11 @@
       <c r="O185">
         <v>0.79</v>
       </c>
-      <c r="P185" s="7" t="s">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P185" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>173</v>
       </c>
@@ -16827,11 +16879,11 @@
       <c r="O186">
         <v>0.79</v>
       </c>
-      <c r="P186" s="7" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P186" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>174</v>
       </c>
@@ -16874,11 +16926,11 @@
       <c r="O187">
         <v>0.79</v>
       </c>
-      <c r="P187" s="7" t="s">
-        <v>2147</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P187" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>175</v>
       </c>
@@ -16924,11 +16976,11 @@
       <c r="O188">
         <v>0.79</v>
       </c>
-      <c r="P188" s="7" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P188" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>176</v>
       </c>
@@ -16974,11 +17026,11 @@
       <c r="O189">
         <v>0.79</v>
       </c>
-      <c r="P189" s="7" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P189" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>177</v>
       </c>
@@ -17024,11 +17076,11 @@
       <c r="O190">
         <v>0.79</v>
       </c>
-      <c r="P190" s="7" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P190" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>178</v>
       </c>
@@ -17074,11 +17126,11 @@
       <c r="O191">
         <v>0.79</v>
       </c>
-      <c r="P191" s="7" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P191" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>179</v>
       </c>
@@ -17124,11 +17176,11 @@
       <c r="O192">
         <v>0.79</v>
       </c>
-      <c r="P192" s="7" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P192" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>180</v>
       </c>
@@ -17174,11 +17226,11 @@
       <c r="O193">
         <v>0.81</v>
       </c>
-      <c r="P193" s="7" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P193" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>181</v>
       </c>
@@ -17224,11 +17276,11 @@
       <c r="O194">
         <v>0.79</v>
       </c>
-      <c r="P194" s="7" t="s">
+      <c r="P194" t="s">
         <v>2154</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>182</v>
       </c>
@@ -17274,11 +17326,11 @@
       <c r="O195">
         <v>0.79</v>
       </c>
-      <c r="P195" s="7" t="s">
+      <c r="P195" t="s">
         <v>2155</v>
       </c>
     </row>
-    <row r="196" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>284</v>
       </c>
@@ -17318,11 +17370,11 @@
       <c r="M196" t="s">
         <v>36</v>
       </c>
-      <c r="P196" s="7" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P196" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>183</v>
       </c>
@@ -17368,11 +17420,11 @@
       <c r="O197">
         <v>0.77</v>
       </c>
-      <c r="P197" s="7" t="s">
-        <v>2157</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P197" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>184</v>
       </c>
@@ -17418,11 +17470,11 @@
       <c r="O198">
         <v>0.81</v>
       </c>
-      <c r="P198" s="7" t="s">
-        <v>2158</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P198" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>185</v>
       </c>
@@ -17468,11 +17520,11 @@
       <c r="O199">
         <v>0.79</v>
       </c>
-      <c r="P199" s="7" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P199" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>186</v>
       </c>
@@ -17518,11 +17570,11 @@
       <c r="O200">
         <v>0.79</v>
       </c>
-      <c r="P200" s="7" t="s">
+      <c r="P200" t="s">
         <v>2160</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>187</v>
       </c>
@@ -17568,11 +17620,11 @@
       <c r="O201">
         <v>0.79</v>
       </c>
-      <c r="P201" s="7" t="s">
+      <c r="P201" t="s">
         <v>2161</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>188</v>
       </c>
@@ -17615,11 +17667,11 @@
       <c r="O202">
         <v>0.79</v>
       </c>
-      <c r="P202" s="7" t="s">
-        <v>2162</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P202" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>189</v>
       </c>
@@ -17665,11 +17717,11 @@
       <c r="O203">
         <v>0.79</v>
       </c>
-      <c r="P203" s="7" t="s">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P203" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>190</v>
       </c>
@@ -17715,11 +17767,11 @@
       <c r="O204">
         <v>0.75</v>
       </c>
-      <c r="P204" s="7" t="s">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P204" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>191</v>
       </c>
@@ -17765,11 +17817,11 @@
       <c r="O205">
         <v>0.87</v>
       </c>
-      <c r="P205" s="7" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P205" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>192</v>
       </c>
@@ -17815,11 +17867,11 @@
       <c r="O206">
         <v>0.79</v>
       </c>
-      <c r="P206" s="7" t="s">
+      <c r="P206" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="207" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>308</v>
       </c>
@@ -17859,11 +17911,11 @@
       <c r="M207" t="s">
         <v>36</v>
       </c>
-      <c r="P207" s="7" t="s">
+      <c r="P207" t="s">
         <v>2167</v>
       </c>
     </row>
-    <row r="208" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>193</v>
       </c>
@@ -17909,11 +17961,11 @@
       <c r="O208">
         <v>0.79</v>
       </c>
-      <c r="P208" s="7" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P208" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>281</v>
       </c>
@@ -17953,11 +18005,11 @@
       <c r="M209" t="s">
         <v>36</v>
       </c>
-      <c r="P209" s="7" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P209" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>194</v>
       </c>
@@ -18003,11 +18055,11 @@
       <c r="O210">
         <v>0.8</v>
       </c>
-      <c r="P210" s="7" t="s">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P210" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>195</v>
       </c>
@@ -18053,11 +18105,11 @@
       <c r="O211">
         <v>0.8</v>
       </c>
-      <c r="P211" s="7" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P211" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>196</v>
       </c>
@@ -18103,11 +18155,11 @@
       <c r="O212">
         <v>0.8</v>
       </c>
-      <c r="P212" s="7" t="s">
+      <c r="P212" t="s">
         <v>2172</v>
       </c>
     </row>
-    <row r="213" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>197</v>
       </c>
@@ -18153,11 +18205,11 @@
       <c r="O213">
         <v>0.8</v>
       </c>
-      <c r="P213" s="7" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P213" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>198</v>
       </c>
@@ -18203,11 +18255,11 @@
       <c r="O214">
         <v>0.79</v>
       </c>
-      <c r="P214" s="7" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P214" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>199</v>
       </c>
@@ -18253,11 +18305,11 @@
       <c r="O215">
         <v>0.79</v>
       </c>
-      <c r="P215" s="7" t="s">
+      <c r="P215" t="s">
         <v>2175</v>
       </c>
     </row>
-    <row r="216" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>200</v>
       </c>
@@ -18303,11 +18355,11 @@
       <c r="O216">
         <v>0.79</v>
       </c>
-      <c r="P216" s="7" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P216" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>201</v>
       </c>
@@ -18353,11 +18405,11 @@
       <c r="O217">
         <v>0.79</v>
       </c>
-      <c r="P217" s="7" t="s">
+      <c r="P217" t="s">
         <v>2177</v>
       </c>
     </row>
-    <row r="218" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>305</v>
       </c>
@@ -18397,11 +18449,11 @@
       <c r="M218" t="s">
         <v>36</v>
       </c>
-      <c r="P218" s="7" t="s">
+      <c r="P218" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="219" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>202</v>
       </c>
@@ -18447,11 +18499,11 @@
       <c r="O219">
         <v>0.79</v>
       </c>
-      <c r="P219" s="7" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P219" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>306</v>
       </c>
@@ -18491,11 +18543,11 @@
       <c r="M220" t="s">
         <v>36</v>
       </c>
-      <c r="P220" s="7" t="s">
+      <c r="P220" t="s">
         <v>2180</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>203</v>
       </c>
@@ -18541,11 +18593,11 @@
       <c r="O221">
         <v>0.79</v>
       </c>
-      <c r="P221" s="7" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P221" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>204</v>
       </c>
@@ -18591,11 +18643,11 @@
       <c r="O222">
         <v>0.79</v>
       </c>
-      <c r="P222" s="7" t="s">
+      <c r="P222" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="223" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>205</v>
       </c>
@@ -18641,11 +18693,11 @@
       <c r="O223">
         <v>0.79</v>
       </c>
-      <c r="P223" s="7" t="s">
+      <c r="P223" t="s">
         <v>2183</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>206</v>
       </c>
@@ -18691,11 +18743,11 @@
       <c r="O224">
         <v>0.79</v>
       </c>
-      <c r="P224" s="7" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P224" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>208</v>
       </c>
@@ -18741,11 +18793,11 @@
       <c r="O225">
         <v>0.79</v>
       </c>
-      <c r="P225" s="7" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P225" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>209</v>
       </c>
@@ -18788,11 +18840,11 @@
       <c r="O226">
         <v>0.79</v>
       </c>
-      <c r="P226" s="7" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P226" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>311</v>
       </c>
@@ -18835,11 +18887,11 @@
       <c r="O227">
         <v>0.79</v>
       </c>
-      <c r="P227" s="7" t="s">
+      <c r="P227" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>210</v>
       </c>
@@ -18885,11 +18937,11 @@
       <c r="O228">
         <v>0.79</v>
       </c>
-      <c r="P228" s="7" t="s">
-        <v>2188</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P228" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>211</v>
       </c>
@@ -18935,11 +18987,11 @@
       <c r="O229">
         <v>0.86</v>
       </c>
-      <c r="P229" s="7" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P229" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>213</v>
       </c>
@@ -18982,11 +19034,11 @@
       <c r="O230">
         <v>0.86</v>
       </c>
-      <c r="P230" s="7" t="s">
+      <c r="P230" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="231" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>214</v>
       </c>
@@ -19032,11 +19084,11 @@
       <c r="O231">
         <v>0.79</v>
       </c>
-      <c r="P231" s="7" t="s">
-        <v>2191</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P231" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>215</v>
       </c>
@@ -19082,11 +19134,11 @@
       <c r="O232">
         <v>0.79</v>
       </c>
-      <c r="P232" s="7" t="s">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P232" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>216</v>
       </c>
@@ -19132,11 +19184,11 @@
       <c r="O233">
         <v>0.79</v>
       </c>
-      <c r="P233" s="7" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P233" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>287</v>
       </c>
@@ -19176,11 +19228,11 @@
       <c r="M234" t="s">
         <v>36</v>
       </c>
-      <c r="P234" s="7" t="s">
+      <c r="P234" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="235" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>217</v>
       </c>
@@ -19226,11 +19278,11 @@
       <c r="O235">
         <v>0.8</v>
       </c>
-      <c r="P235" s="7" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P235" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>218</v>
       </c>
@@ -19276,11 +19328,11 @@
       <c r="O236">
         <v>0.8</v>
       </c>
-      <c r="P236" s="7" t="s">
+      <c r="P236" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="237" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>219</v>
       </c>
@@ -19326,11 +19378,11 @@
       <c r="O237">
         <v>0.8</v>
       </c>
-      <c r="P237" s="7" t="s">
+      <c r="P237" t="s">
         <v>2197</v>
       </c>
     </row>
-    <row r="238" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>220</v>
       </c>
@@ -19373,11 +19425,11 @@
       <c r="O238">
         <v>0.8</v>
       </c>
-      <c r="P238" s="7" t="s">
-        <v>2198</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P238" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>221</v>
       </c>
@@ -19423,11 +19475,11 @@
       <c r="O239">
         <v>0.8</v>
       </c>
-      <c r="P239" s="7" t="s">
-        <v>2199</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P239" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>222</v>
       </c>
@@ -19470,11 +19522,11 @@
       <c r="O240">
         <v>0.79</v>
       </c>
-      <c r="P240" s="7" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P240" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>223</v>
       </c>
@@ -19520,11 +19572,11 @@
       <c r="O241">
         <v>0.81</v>
       </c>
-      <c r="P241" s="7" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P241" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>224</v>
       </c>
@@ -19570,11 +19622,11 @@
       <c r="O242">
         <v>0.79</v>
       </c>
-      <c r="P242" s="7" t="s">
-        <v>2202</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P242" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>225</v>
       </c>
@@ -19620,11 +19672,11 @@
       <c r="O243">
         <v>0.79</v>
       </c>
-      <c r="P243" s="7" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P243" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>286</v>
       </c>
@@ -19664,11 +19716,11 @@
       <c r="M244" t="s">
         <v>36</v>
       </c>
-      <c r="P244" s="7" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P244" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>227</v>
       </c>
@@ -19708,11 +19760,11 @@
       <c r="M245" t="s">
         <v>36</v>
       </c>
-      <c r="P245" s="7" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P245" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>228</v>
       </c>
@@ -19752,11 +19804,11 @@
       <c r="M246" t="s">
         <v>36</v>
       </c>
-      <c r="P246" s="7" t="s">
-        <v>2206</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P246" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>229</v>
       </c>
@@ -19802,11 +19854,11 @@
       <c r="O247">
         <v>0.79</v>
       </c>
-      <c r="P247" s="7" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P247" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>231</v>
       </c>
@@ -19852,11 +19904,11 @@
       <c r="O248">
         <v>0.77</v>
       </c>
-      <c r="P248" s="7" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P248" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>232</v>
       </c>
@@ -19902,11 +19954,11 @@
       <c r="O249">
         <v>0.77</v>
       </c>
-      <c r="P249" s="7" t="s">
-        <v>2209</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P249" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>233</v>
       </c>
@@ -19949,11 +20001,11 @@
       <c r="O250">
         <v>0.77</v>
       </c>
-      <c r="P250" s="7" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P250" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>230</v>
       </c>
@@ -19999,11 +20051,11 @@
       <c r="O251">
         <v>0.77</v>
       </c>
-      <c r="P251" s="7" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P251" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>234</v>
       </c>
@@ -20049,11 +20101,11 @@
       <c r="O252">
         <v>0.79</v>
       </c>
-      <c r="P252" s="7" t="s">
+      <c r="P252" t="s">
         <v>2212</v>
       </c>
     </row>
-    <row r="253" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>235</v>
       </c>
@@ -20099,11 +20151,11 @@
       <c r="O253">
         <v>0.79</v>
       </c>
-      <c r="P253" s="7" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P253" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>236</v>
       </c>
@@ -20140,11 +20192,11 @@
       <c r="M254" t="s">
         <v>36</v>
       </c>
-      <c r="P254" s="7" t="s">
+      <c r="P254" t="s">
         <v>2214</v>
       </c>
     </row>
-    <row r="255" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>237</v>
       </c>
@@ -20190,11 +20242,11 @@
       <c r="O255">
         <v>0.79</v>
       </c>
-      <c r="P255" s="7" t="s">
-        <v>2215</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P255" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>238</v>
       </c>
@@ -20240,11 +20292,11 @@
       <c r="O256">
         <v>0.79</v>
       </c>
-      <c r="P256" s="7" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P256" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>239</v>
       </c>
@@ -20290,11 +20342,11 @@
       <c r="O257">
         <v>0.79</v>
       </c>
-      <c r="P257" s="7" t="s">
+      <c r="P257" t="s">
         <v>2217</v>
       </c>
     </row>
-    <row r="258" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>240</v>
       </c>
@@ -20340,11 +20392,11 @@
       <c r="O258">
         <v>0.79</v>
       </c>
-      <c r="P258" s="7" t="s">
-        <v>2218</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P258" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>241</v>
       </c>
@@ -20390,11 +20442,11 @@
       <c r="O259">
         <v>0.79</v>
       </c>
-      <c r="P259" s="7" t="s">
-        <v>2219</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P259" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>242</v>
       </c>
@@ -20440,11 +20492,11 @@
       <c r="O260">
         <v>0.79</v>
       </c>
-      <c r="P260" s="7" t="s">
-        <v>2220</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P260" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>243</v>
       </c>
@@ -20487,11 +20539,11 @@
       <c r="O261">
         <v>0.79</v>
       </c>
-      <c r="P261" s="7" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P261" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>244</v>
       </c>
@@ -20537,11 +20589,11 @@
       <c r="O262">
         <v>0.79</v>
       </c>
-      <c r="P262" s="7" t="s">
-        <v>2222</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P262" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>283</v>
       </c>
@@ -20581,11 +20633,11 @@
       <c r="M263" t="s">
         <v>36</v>
       </c>
-      <c r="P263" s="7" t="s">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P263" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>246</v>
       </c>
@@ -20631,11 +20683,11 @@
       <c r="O264">
         <v>0.79</v>
       </c>
-      <c r="P264" s="7" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P264" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>247</v>
       </c>
@@ -20678,11 +20730,11 @@
       <c r="O265">
         <v>0.7</v>
       </c>
-      <c r="P265" s="7" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P265" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>248</v>
       </c>
@@ -20728,11 +20780,11 @@
       <c r="O266">
         <v>0.82</v>
       </c>
-      <c r="P266" s="7" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P266" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>249</v>
       </c>
@@ -20778,11 +20830,11 @@
       <c r="O267">
         <v>0.86</v>
       </c>
-      <c r="P267" s="7" t="s">
-        <v>2227</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P267" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>250</v>
       </c>
@@ -20828,11 +20880,11 @@
       <c r="O268">
         <v>0.79</v>
       </c>
-      <c r="P268" s="7" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P268" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>252</v>
       </c>
@@ -20878,11 +20930,11 @@
       <c r="O269">
         <v>0.79</v>
       </c>
-      <c r="P269" s="7" t="s">
-        <v>2229</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P269" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>253</v>
       </c>
@@ -20928,11 +20980,11 @@
       <c r="O270">
         <v>0.9</v>
       </c>
-      <c r="P270" s="7" t="s">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P270" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>254</v>
       </c>
@@ -20972,11 +21024,11 @@
       <c r="M271" t="s">
         <v>36</v>
       </c>
-      <c r="P271" s="7" t="s">
-        <v>2231</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P271" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>255</v>
       </c>
@@ -21019,11 +21071,11 @@
       <c r="O272">
         <v>0.7</v>
       </c>
-      <c r="P272" s="7" t="s">
-        <v>2232</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P272" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>256</v>
       </c>
@@ -21069,11 +21121,11 @@
       <c r="O273">
         <v>0.91</v>
       </c>
-      <c r="P273" s="7" t="s">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P273" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>257</v>
       </c>
@@ -21119,11 +21171,11 @@
       <c r="O274">
         <v>0.91</v>
       </c>
-      <c r="P274" s="7" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P274" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>310</v>
       </c>
@@ -21163,11 +21215,11 @@
       <c r="M275" t="s">
         <v>36</v>
       </c>
-      <c r="P275" s="7" t="s">
+      <c r="P275" t="s">
         <v>2235</v>
       </c>
     </row>
-    <row r="276" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>258</v>
       </c>
@@ -21210,11 +21262,11 @@
       <c r="O276">
         <v>0.91</v>
       </c>
-      <c r="P276" s="7" t="s">
-        <v>2236</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P276" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>285</v>
       </c>
@@ -21254,11 +21306,11 @@
       <c r="M277" t="s">
         <v>36</v>
       </c>
-      <c r="P277" s="7" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P277" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>226</v>
       </c>
@@ -21304,11 +21356,11 @@
       <c r="O278">
         <v>0.7</v>
       </c>
-      <c r="P278" s="7" t="s">
+      <c r="P278" t="s">
         <v>2238</v>
       </c>
     </row>
-    <row r="279" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>259</v>
       </c>
@@ -21354,11 +21406,11 @@
       <c r="O279">
         <v>0.79</v>
       </c>
-      <c r="P279" s="7" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P279" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>316</v>
       </c>
@@ -21398,11 +21450,11 @@
       <c r="M280" t="s">
         <v>36</v>
       </c>
-      <c r="P280" s="7" t="s">
+      <c r="P280" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="281" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>260</v>
       </c>
@@ -21448,11 +21500,11 @@
       <c r="O281">
         <v>0.79</v>
       </c>
-      <c r="P281" s="7" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P281" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>315</v>
       </c>
@@ -21492,11 +21544,11 @@
       <c r="M282" t="s">
         <v>36</v>
       </c>
-      <c r="P282" s="7" t="s">
+      <c r="P282" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="283" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>261</v>
       </c>
@@ -21542,11 +21594,11 @@
       <c r="O283">
         <v>0.79</v>
       </c>
-      <c r="P283" s="7" t="s">
+      <c r="P283" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="284" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>262</v>
       </c>
@@ -21592,11 +21644,11 @@
       <c r="O284">
         <v>0.79</v>
       </c>
-      <c r="P284" s="7" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P284" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>263</v>
       </c>
@@ -21642,11 +21694,11 @@
       <c r="O285">
         <v>0.79</v>
       </c>
-      <c r="P285" s="7" t="s">
+      <c r="P285" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="286" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>317</v>
       </c>
@@ -21686,11 +21738,11 @@
       <c r="M286" t="s">
         <v>36</v>
       </c>
-      <c r="P286" s="7" t="s">
+      <c r="P286" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="287" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>264</v>
       </c>
@@ -21736,11 +21788,11 @@
       <c r="O287">
         <v>0.79</v>
       </c>
-      <c r="P287" s="7" t="s">
+      <c r="P287" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="288" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>265</v>
       </c>
@@ -21786,11 +21838,11 @@
       <c r="O288">
         <v>0.79</v>
       </c>
-      <c r="P288" s="7" t="s">
+      <c r="P288" t="s">
         <v>2248</v>
       </c>
     </row>
-    <row r="289" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>266</v>
       </c>
@@ -21836,11 +21888,11 @@
       <c r="O289">
         <v>0.79</v>
       </c>
-      <c r="P289" s="7" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P289" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>267</v>
       </c>
@@ -21886,11 +21938,11 @@
       <c r="O290">
         <v>0.79</v>
       </c>
-      <c r="P290" s="7" t="s">
+      <c r="P290" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="291" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>269</v>
       </c>
@@ -21933,11 +21985,11 @@
       <c r="O291">
         <v>0.79</v>
       </c>
-      <c r="P291" s="7" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P291" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>270</v>
       </c>
@@ -21983,11 +22035,11 @@
       <c r="O292">
         <v>0.79</v>
       </c>
-      <c r="P292" s="7" t="s">
-        <v>2252</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P292" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>271</v>
       </c>
@@ -22033,11 +22085,11 @@
       <c r="O293">
         <v>0.79</v>
       </c>
-      <c r="P293" s="7" t="s">
-        <v>2253</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P293" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>272</v>
       </c>
@@ -22083,11 +22135,11 @@
       <c r="O294">
         <v>0.79</v>
       </c>
-      <c r="P294" s="7" t="s">
+      <c r="P294" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="295" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>212</v>
       </c>
@@ -22127,11 +22179,11 @@
       <c r="M295" t="s">
         <v>36</v>
       </c>
-      <c r="P295" s="7" t="s">
-        <v>2253</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P295" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>274</v>
       </c>
@@ -22177,11 +22229,11 @@
       <c r="O296">
         <v>0.79</v>
       </c>
-      <c r="P296" s="7" t="s">
+      <c r="P296" t="s">
         <v>2109</v>
       </c>
     </row>
-    <row r="297" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>275</v>
       </c>
@@ -22227,11 +22279,11 @@
       <c r="O297">
         <v>0.79</v>
       </c>
-      <c r="P297" s="7" t="s">
-        <v>2110</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P297" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>276</v>
       </c>
@@ -22277,11 +22329,11 @@
       <c r="O298">
         <v>0.79</v>
       </c>
-      <c r="P298" s="12" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P298" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>277</v>
       </c>
@@ -22327,11 +22379,11 @@
       <c r="O299">
         <v>0.79</v>
       </c>
-      <c r="P299" s="7" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P299" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>278</v>
       </c>
@@ -22374,11 +22426,11 @@
       <c r="O300">
         <v>0.79</v>
       </c>
-      <c r="P300" s="7" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="P300" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>309</v>
       </c>
@@ -22418,432 +22470,9 @@
       <c r="M301" t="s">
         <v>36</v>
       </c>
-      <c r="P301" s="7" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="302" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P302" s="7"/>
-    </row>
-    <row r="303" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P303" s="7"/>
-    </row>
-    <row r="304" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P304" s="7"/>
-    </row>
-    <row r="305" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P305" s="7"/>
-    </row>
-    <row r="306" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P306" s="7"/>
-    </row>
-    <row r="307" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P307" s="7"/>
-    </row>
-    <row r="308" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P308" s="7"/>
-    </row>
-    <row r="309" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P309" s="7"/>
-    </row>
-    <row r="310" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P310" s="7"/>
-    </row>
-    <row r="311" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P311" s="7"/>
-    </row>
-    <row r="312" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P312" s="7"/>
-    </row>
-    <row r="313" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P313" s="7"/>
-    </row>
-    <row r="314" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P314" s="7"/>
-    </row>
-    <row r="315" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P315" s="7"/>
-    </row>
-    <row r="316" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P316" s="7"/>
-    </row>
-    <row r="317" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P317" s="7"/>
-    </row>
-    <row r="318" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P318" s="7"/>
-    </row>
-    <row r="319" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P319" s="7"/>
-    </row>
-    <row r="320" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P320" s="7"/>
-    </row>
-    <row r="321" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P321" s="7"/>
-    </row>
-    <row r="322" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P322" s="7"/>
-    </row>
-    <row r="323" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P323" s="7"/>
-    </row>
-    <row r="324" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P324" s="7"/>
-    </row>
-    <row r="325" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P325" s="7"/>
-    </row>
-    <row r="326" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P326" s="7"/>
-    </row>
-    <row r="327" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P327" s="7"/>
-    </row>
-    <row r="328" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P328" s="7"/>
-    </row>
-    <row r="329" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P329" s="7"/>
-    </row>
-    <row r="330" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P330" s="7"/>
-    </row>
-    <row r="331" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P331" s="7"/>
-    </row>
-    <row r="332" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P332" s="7"/>
-    </row>
-    <row r="333" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P333" s="7"/>
-    </row>
-    <row r="334" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P334" s="7"/>
-    </row>
-    <row r="335" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P335" s="7"/>
-    </row>
-    <row r="336" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P336" s="7"/>
-    </row>
-    <row r="337" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P337" s="7"/>
-    </row>
-    <row r="338" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P338" s="7"/>
-    </row>
-    <row r="339" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P339" s="7"/>
-    </row>
-    <row r="340" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P340" s="7"/>
-    </row>
-    <row r="341" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P341" s="7"/>
-    </row>
-    <row r="342" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P342" s="7"/>
-    </row>
-    <row r="343" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P343" s="7"/>
-    </row>
-    <row r="344" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P344" s="7"/>
-    </row>
-    <row r="345" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P345" s="7"/>
-    </row>
-    <row r="346" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P346" s="7"/>
-    </row>
-    <row r="347" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P347" s="7"/>
-    </row>
-    <row r="348" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P348" s="7"/>
-    </row>
-    <row r="349" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P349" s="7"/>
-    </row>
-    <row r="350" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P350" s="7"/>
-    </row>
-    <row r="351" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P351" s="7"/>
-    </row>
-    <row r="352" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P352" s="7"/>
-    </row>
-    <row r="353" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P353" s="7"/>
-    </row>
-    <row r="354" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P354" s="7"/>
-    </row>
-    <row r="355" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P355" s="7"/>
-    </row>
-    <row r="356" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P356" s="7"/>
-    </row>
-    <row r="357" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P357" s="7"/>
-    </row>
-    <row r="358" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P358" s="7"/>
-    </row>
-    <row r="359" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P359" s="7"/>
-    </row>
-    <row r="360" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P360" s="7"/>
-    </row>
-    <row r="361" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P361" s="7"/>
-    </row>
-    <row r="362" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P362" s="7"/>
-    </row>
-    <row r="363" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P363" s="7"/>
-    </row>
-    <row r="364" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P364" s="7"/>
-    </row>
-    <row r="365" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P365" s="7"/>
-    </row>
-    <row r="366" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P366" s="7"/>
-    </row>
-    <row r="367" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P367" s="7"/>
-    </row>
-    <row r="368" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P368" s="7"/>
-    </row>
-    <row r="369" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P369" s="7"/>
-    </row>
-    <row r="370" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P370" s="7"/>
-    </row>
-    <row r="371" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P371" s="7"/>
-    </row>
-    <row r="372" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P372" s="7"/>
-    </row>
-    <row r="373" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P373" s="7"/>
-    </row>
-    <row r="374" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P374" s="7"/>
-    </row>
-    <row r="375" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P375" s="7"/>
-    </row>
-    <row r="376" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P376" s="7"/>
-    </row>
-    <row r="377" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P377" s="7"/>
-    </row>
-    <row r="378" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P378" s="7"/>
-    </row>
-    <row r="379" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P379" s="7"/>
-    </row>
-    <row r="380" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P380" s="7"/>
-    </row>
-    <row r="381" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P381" s="7"/>
-    </row>
-    <row r="382" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P382" s="7"/>
-    </row>
-    <row r="383" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P383" s="7"/>
-    </row>
-    <row r="384" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P384" s="7"/>
-    </row>
-    <row r="385" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P385" s="7"/>
-    </row>
-    <row r="386" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P386" s="7"/>
-    </row>
-    <row r="387" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P387" s="7"/>
-    </row>
-    <row r="388" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P388" s="7"/>
-    </row>
-    <row r="389" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P389" s="7"/>
-    </row>
-    <row r="390" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P390" s="7"/>
-    </row>
-    <row r="391" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P391" s="7"/>
-    </row>
-    <row r="392" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P392" s="7"/>
-    </row>
-    <row r="393" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P393" s="7"/>
-    </row>
-    <row r="394" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P394" s="7"/>
-    </row>
-    <row r="395" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P395" s="7"/>
-    </row>
-    <row r="396" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P396" s="7"/>
-    </row>
-    <row r="397" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P397" s="7"/>
-    </row>
-    <row r="398" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P398" s="7"/>
-    </row>
-    <row r="399" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P399" s="7"/>
-    </row>
-    <row r="400" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P400" s="7"/>
-    </row>
-    <row r="401" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P401" s="7"/>
-    </row>
-    <row r="402" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P402" s="7"/>
-    </row>
-    <row r="403" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P403" s="7"/>
-    </row>
-    <row r="404" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P404" s="7"/>
-    </row>
-    <row r="405" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P405" s="7"/>
-    </row>
-    <row r="406" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P406" s="7"/>
-    </row>
-    <row r="407" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P407" s="7"/>
-    </row>
-    <row r="408" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P408" s="7"/>
-    </row>
-    <row r="409" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P409" s="7"/>
-    </row>
-    <row r="410" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P410" s="7"/>
-    </row>
-    <row r="411" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P411" s="7"/>
-    </row>
-    <row r="412" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P412" s="7"/>
-    </row>
-    <row r="413" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P413" s="7"/>
-    </row>
-    <row r="414" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P414" s="7"/>
-    </row>
-    <row r="415" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P415" s="7"/>
-    </row>
-    <row r="416" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P416" s="7"/>
-    </row>
-    <row r="417" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P417" s="7"/>
-    </row>
-    <row r="418" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P418" s="7"/>
-    </row>
-    <row r="419" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P419" s="7"/>
-    </row>
-    <row r="420" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P420" s="7"/>
-    </row>
-    <row r="421" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P421" s="7"/>
-    </row>
-    <row r="422" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P422" s="7"/>
-    </row>
-    <row r="423" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P423" s="7"/>
-    </row>
-    <row r="424" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P424" s="7"/>
-    </row>
-    <row r="425" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P425" s="7"/>
-    </row>
-    <row r="426" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P426" s="7"/>
-    </row>
-    <row r="427" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P427" s="7"/>
-    </row>
-    <row r="428" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P428" s="7"/>
-    </row>
-    <row r="429" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P429" s="7"/>
-    </row>
-    <row r="430" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P430" s="7"/>
-    </row>
-    <row r="431" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P431" s="7"/>
-    </row>
-    <row r="432" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P432" s="7"/>
-    </row>
-    <row r="433" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P433" s="7"/>
-    </row>
-    <row r="434" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P434" s="7"/>
-    </row>
-    <row r="435" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P435" s="7"/>
-    </row>
-    <row r="436" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P436" s="7"/>
-    </row>
-    <row r="437" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P437" s="7"/>
-    </row>
-    <row r="438" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P438" s="7"/>
-    </row>
-    <row r="439" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P439" s="7"/>
-    </row>
-    <row r="440" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P440" s="7"/>
-    </row>
-    <row r="441" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P441" s="7"/>
-    </row>
-    <row r="442" spans="16:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="P442" s="7"/>
+      <c r="P301" t="s">
+        <v>2224</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O301">
@@ -22855,6 +22484,2701 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD6E05B-A504-41A1-A180-3AD461BC2AC3}">
+  <dimension ref="A1:B335"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>697</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>973</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>560</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>860</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>745</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>983</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>818</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>935</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>742</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>776</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>835</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>966</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>896</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
+        <v>733</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
+        <v>717</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
+        <v>839</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="14" t="s">
+        <v>824</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="14" t="s">
+        <v>362</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="14" t="s">
+        <v>857</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
+        <v>913</v>
+      </c>
+      <c r="B81" s="13" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="14" t="s">
+        <v>344</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="B83" s="13" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="B85" s="13" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
+        <v>711</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="B87" s="13" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="B91" s="13" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="B93" s="13" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
+        <v>938</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B97" s="13" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B99" s="13" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="B101" s="13" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="14" t="s">
+        <v>573</v>
+      </c>
+      <c r="B107" s="13" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="14" t="s">
+        <v>930</v>
+      </c>
+      <c r="B109" s="13" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="14" t="s">
+        <v>886</v>
+      </c>
+      <c r="B111" s="13" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="s">
+        <v>864</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
+        <v>677</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
+        <v>990</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A118" s="14" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A119" s="14" t="s">
+        <v>987</v>
+      </c>
+      <c r="B119" s="13" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="14" t="s">
+        <v>790</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="14" t="s">
+        <v>958</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A123" s="14" t="s">
+        <v>739</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A124" s="14" t="s">
+        <v>708</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A125" s="14" t="s">
+        <v>851</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A126" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B127" s="13" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A128" s="14" t="s">
+        <v>714</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A129" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A130" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A131" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A132" s="14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A133" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="14" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A135" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A136" s="14" t="s">
+        <v>993</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="14" t="s">
+        <v>752</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A138" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A139" s="14" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A140" s="14" t="s">
+        <v>876</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A141" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="B141" s="13" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A142" s="14" t="s">
+        <v>909</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A143" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A144" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A146" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A147" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A148" s="14" t="s">
+        <v>807</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A149" s="14" t="s">
+        <v>929</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A150" s="14" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B151" s="13" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="14" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A153" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B153" s="13" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A154" s="14" t="s">
+        <v>918</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="14" t="s">
+        <v>607</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="14" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A157" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A158" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="B159" s="13" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A160" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A161" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A162" s="14" t="s">
+        <v>598</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B163" s="13" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A164" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A165" s="14" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A166" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="B166" s="13" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A167" s="14" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B167" s="13" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A168" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A169" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="B169" s="13" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A170" s="14" t="s">
+        <v>980</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A171" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A172" s="14" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A173" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B173" s="13" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A174" s="14" t="s">
+        <v>976</v>
+      </c>
+      <c r="B174" s="13" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A175" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="B175" s="13" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A176" s="14" t="s">
+        <v>692</v>
+      </c>
+      <c r="B176" s="13" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A177" s="14" t="s">
+        <v>689</v>
+      </c>
+      <c r="B177" s="13" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A178" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A179" s="14" t="s">
+        <v>649</v>
+      </c>
+      <c r="B179" s="13" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A181" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A182" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A183" s="14" t="s">
+        <v>832</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A184" s="14" t="s">
+        <v>994</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A185" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="B185" s="13" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A186" s="14" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A187" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A188" s="14" t="s">
+        <v>868</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A189" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="B189" s="13" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A190" s="14" t="s">
+        <v>736</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A191" s="14" t="s">
+        <v>872</v>
+      </c>
+      <c r="B191" s="13" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A192" s="14" t="s">
+        <v>580</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A193" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="B193" s="13" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A194" s="14" t="s">
+        <v>893</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="14" t="s">
+        <v>883</v>
+      </c>
+      <c r="B195" s="13" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A196" s="14" t="s">
+        <v>904</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A197" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B197" s="13" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A198" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A199" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B199" s="13" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A200" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A201" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="B201" s="13" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A202" s="14" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A203" s="14" t="s">
+        <v>962</v>
+      </c>
+      <c r="B203" s="13" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A204" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A205" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="B205" s="13" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A206" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A207" s="14" t="s">
+        <v>478</v>
+      </c>
+      <c r="B207" s="13" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A208" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A209" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="B209" s="13" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A210" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="B210" s="13" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A211" s="14" t="s">
+        <v>720</v>
+      </c>
+      <c r="B211" s="13" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A212" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A213" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B213" s="13" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A214" s="14" t="s">
+        <v>772</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A215" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B215" s="13" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A216" s="14" t="s">
+        <v>900</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A217" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B217" s="13" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A218" s="14" t="s">
+        <v>680</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A219" s="14" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B219" s="13" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A220" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A221" s="14" t="s">
+        <v>606</v>
+      </c>
+      <c r="B221" s="13" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A222" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A223" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="B223" s="13" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A224" s="14" t="s">
+        <v>965</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A225" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="B225" s="13" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A226" s="14" t="s">
+        <v>696</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A227" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B227" s="13" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A228" s="14" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A229" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="B229" s="13" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A230" s="14" t="s">
+        <v>710</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A231" s="14" t="s">
+        <v>556</v>
+      </c>
+      <c r="B231" s="13" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A232" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A233" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B233" s="13" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A234" s="14" t="s">
+        <v>802</v>
+      </c>
+      <c r="B234" s="13" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A235" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="B235" s="13" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A236" s="14" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B236" s="13" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A237" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B237" s="13" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A238" s="14" t="s">
+        <v>496</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A239" s="14" t="s">
+        <v>929</v>
+      </c>
+      <c r="B239" s="13" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A240" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B240" s="13" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A241" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B241" s="13" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A242" s="14" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A243" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="B243" s="13" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A244" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A245" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="B245" s="13" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A246" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A247" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="B247" s="13" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A248" s="14" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A249" s="14" t="s">
+        <v>896</v>
+      </c>
+      <c r="B249" s="13" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A250" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A251" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B251" s="13" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A252" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A253" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B253" s="13" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A254" s="14" t="s">
+        <v>482</v>
+      </c>
+      <c r="B254" s="13" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A255" s="14" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B255" s="13" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A256" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B256" s="13" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A257" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B257" s="13" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A258" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="B258" s="13" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A259" s="14" t="s">
+        <v>850</v>
+      </c>
+      <c r="B259" s="13" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A260" s="14" t="s">
+        <v>863</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A261" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="B261" s="13" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A262" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A263" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="B263" s="13" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A264" s="14" t="s">
+        <v>913</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A265" s="14" t="s">
+        <v>947</v>
+      </c>
+      <c r="B265" s="13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A266" s="14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A267" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="B267" s="13" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A268" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A269" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B269" s="13" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A270" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A271" s="14" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B271" s="13" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A272" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A273" s="14" t="s">
+        <v>957</v>
+      </c>
+      <c r="B273" s="13" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A274" s="14" t="s">
+        <v>993</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A275" s="14" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B275" s="13" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A276" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A277" s="14" t="s">
+        <v>900</v>
+      </c>
+      <c r="B277" s="13" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A278" s="14" t="s">
+        <v>909</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A279" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B279" s="13" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A280" s="14" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B280" s="13" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A281" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="B281" s="13" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A282" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A283" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B283" s="13" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A284" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B284" s="13" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A285" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="B285" s="13" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A286" s="14" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A287" s="14" t="s">
+        <v>464</v>
+      </c>
+      <c r="B287" s="13" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A288" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A289" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="B289" s="13" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A290" s="14" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A291" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B291" s="13" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A292" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A293" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B293" s="13" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A294" s="14" t="s">
+        <v>771</v>
+      </c>
+      <c r="B294" s="13" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A295" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="B295" s="13" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A296" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A297" s="14" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A298" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A299" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B299" s="13" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A300" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A301" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B301" s="13" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A302" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B302" s="13" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A303" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="B303" s="13" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A304" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A305" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B305" s="13" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A306" s="14" t="s">
+        <v>695</v>
+      </c>
+      <c r="B306" s="13" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A307" s="14" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B307" s="13" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A308" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B308" s="13" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A309" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="B309" s="13" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A310" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B310" s="13" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A311" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="B311" s="13" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A312" s="14" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B312" s="13" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A313" s="14" t="s">
+        <v>386</v>
+      </c>
+      <c r="B313" s="13" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A314" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="B314" s="13" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A315" s="14" t="s">
+        <v>862</v>
+      </c>
+      <c r="B315" s="13" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A316" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="B316" s="13" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A317" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B317" s="13" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A318" s="14" t="s">
+        <v>849</v>
+      </c>
+      <c r="B318" s="13" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A319" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="B319" s="13" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A320" s="14" t="s">
+        <v>946</v>
+      </c>
+      <c r="B320" s="13" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A321" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="B321" s="13" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A322" s="14" t="s">
+        <v>912</v>
+      </c>
+      <c r="B322" s="13" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A323" s="14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B323" s="13" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A324" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B324" s="13" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A325" s="14" t="s">
+        <v>956</v>
+      </c>
+      <c r="B325" s="13" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A326" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="B326" s="13" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A327" s="14" t="s">
+        <v>908</v>
+      </c>
+      <c r="B327" s="13" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A328" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="B328" s="13" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A329" s="14" t="s">
+        <v>916</v>
+      </c>
+      <c r="B329" s="13" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A330" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="B330" s="13" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A331" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="B331" s="13" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A332" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="B332" s="13" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A333" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="B333" s="13" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A334" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="B334" s="13" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A335" s="14" t="s">
+        <v>767</v>
+      </c>
+      <c r="B335" s="13" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A335" xr:uid="{1CD6E05B-A504-41A1-A180-3AD461BC2AC3}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE3CAE1-1B5F-4863-823F-5189904396D1}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AN253"/>
@@ -53741,7 +56065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB12233-FEF6-4F0C-8883-72C83F851833}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:R5"/>
@@ -53981,7 +56305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:BK300"/>

--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E77CFDA3-4B1B-4157-BC58-79DE505FAE38}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{572C582A-EEF0-4D97-BB9E-96A60D4F4A3F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19616" uniqueCount="2267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19616" uniqueCount="2268">
   <si>
     <t>ID</t>
   </si>
@@ -6853,6 +6853,9 @@
   </si>
   <si>
     <t>Sambucus</t>
+  </si>
+  <si>
+    <t>Nanny Berry</t>
   </si>
 </sst>
 </file>
@@ -7767,8 +7770,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:P301"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:O301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
@@ -7782,10 +7785,9 @@
     <col min="12" max="13" width="16.85546875" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7831,11 +7833,8 @@
       <c r="O1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="7" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7881,11 +7880,8 @@
       <c r="O2">
         <v>0.79</v>
       </c>
-      <c r="P2" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7931,11 +7927,8 @@
       <c r="O3">
         <v>0.79</v>
       </c>
-      <c r="P3" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7978,11 +7971,8 @@
       <c r="O4">
         <v>0.79</v>
       </c>
-      <c r="P4" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8028,11 +8018,8 @@
       <c r="O5">
         <v>0.79</v>
       </c>
-      <c r="P5" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>318</v>
       </c>
@@ -8072,11 +8059,8 @@
       <c r="M6" t="s">
         <v>36</v>
       </c>
-      <c r="P6" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8116,11 +8100,8 @@
       <c r="M7" t="s">
         <v>36</v>
       </c>
-      <c r="P7" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8166,11 +8147,8 @@
       <c r="O8">
         <v>0.85</v>
       </c>
-      <c r="P8" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8210,11 +8188,8 @@
       <c r="M9" t="s">
         <v>36</v>
       </c>
-      <c r="P9" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>282</v>
       </c>
@@ -8254,11 +8229,8 @@
       <c r="M10" t="s">
         <v>36</v>
       </c>
-      <c r="P10" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8304,11 +8276,8 @@
       <c r="O11">
         <v>0.84</v>
       </c>
-      <c r="P11" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -8354,11 +8323,8 @@
       <c r="O12">
         <v>0.84</v>
       </c>
-      <c r="P12" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -8404,11 +8370,8 @@
       <c r="O13">
         <v>0.85</v>
       </c>
-      <c r="P13" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -8454,11 +8417,8 @@
       <c r="O14">
         <v>0.83</v>
       </c>
-      <c r="P14" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -8504,11 +8464,8 @@
       <c r="O15">
         <v>0.84</v>
       </c>
-      <c r="P15" t="s">
-        <v>2161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -8551,11 +8508,8 @@
       <c r="O16">
         <v>0.84</v>
       </c>
-      <c r="P16" t="s">
-        <v>2163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -8601,11 +8555,8 @@
       <c r="O17">
         <v>0.84</v>
       </c>
-      <c r="P17" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -8651,11 +8602,8 @@
       <c r="O18">
         <v>0.8</v>
       </c>
-      <c r="P18" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -8701,11 +8649,8 @@
       <c r="O19">
         <v>0.74</v>
       </c>
-      <c r="P19" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -8751,11 +8696,8 @@
       <c r="O20">
         <v>0.88</v>
       </c>
-      <c r="P20" t="s">
-        <v>2184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -8801,11 +8743,8 @@
       <c r="O21">
         <v>0.88</v>
       </c>
-      <c r="P21" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -8851,11 +8790,8 @@
       <c r="O22">
         <v>0.79</v>
       </c>
-      <c r="P22" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -8901,11 +8837,8 @@
       <c r="O23">
         <v>0.88</v>
       </c>
-      <c r="P23" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -8948,11 +8881,8 @@
       <c r="O24">
         <v>0.88</v>
       </c>
-      <c r="P24" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>312</v>
       </c>
@@ -8995,11 +8925,8 @@
       <c r="O25">
         <v>0.82</v>
       </c>
-      <c r="P25" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -9045,11 +8972,8 @@
       <c r="O26">
         <v>0.82</v>
       </c>
-      <c r="P26" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -9095,11 +9019,8 @@
       <c r="O27">
         <v>0.82</v>
       </c>
-      <c r="P27" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -9145,11 +9066,8 @@
       <c r="O28">
         <v>0.82</v>
       </c>
-      <c r="P28" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -9195,11 +9113,8 @@
       <c r="O29">
         <v>0.82</v>
       </c>
-      <c r="P29" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -9245,11 +9160,8 @@
       <c r="O30">
         <v>0.82</v>
       </c>
-      <c r="P30" t="s">
-        <v>2217</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -9292,11 +9204,8 @@
       <c r="O31">
         <v>0.82</v>
       </c>
-      <c r="P31" t="s">
-        <v>2218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -9342,11 +9251,8 @@
       <c r="O32">
         <v>0.82</v>
       </c>
-      <c r="P32" t="s">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -9392,11 +9298,8 @@
       <c r="O33">
         <v>0.82</v>
       </c>
-      <c r="P33" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -9442,11 +9345,8 @@
       <c r="O34">
         <v>0.79</v>
       </c>
-      <c r="P34" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -9492,11 +9392,8 @@
       <c r="O35">
         <v>0.88</v>
       </c>
-      <c r="P35" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -9542,11 +9439,8 @@
       <c r="O36">
         <v>0.88</v>
       </c>
-      <c r="P36" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -9589,11 +9483,8 @@
       <c r="O37">
         <v>0.7</v>
       </c>
-      <c r="P37" t="s">
-        <v>2243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -9639,11 +9530,8 @@
       <c r="O38">
         <v>0.88</v>
       </c>
-      <c r="P38" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>319</v>
       </c>
@@ -9686,11 +9574,8 @@
       <c r="O39">
         <v>0.88</v>
       </c>
-      <c r="P39" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>320</v>
       </c>
@@ -9727,11 +9612,8 @@
       <c r="M40" t="s">
         <v>36</v>
       </c>
-      <c r="P40" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>36</v>
       </c>
@@ -9777,11 +9659,8 @@
       <c r="O41">
         <v>0.91</v>
       </c>
-      <c r="P41" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -9827,11 +9706,8 @@
       <c r="O42">
         <v>0.76</v>
       </c>
-      <c r="P42" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>38</v>
       </c>
@@ -9877,11 +9753,8 @@
       <c r="O43">
         <v>0.76</v>
       </c>
-      <c r="P43" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>39</v>
       </c>
@@ -9927,11 +9800,8 @@
       <c r="O44">
         <v>0.76</v>
       </c>
-      <c r="P44" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -9974,11 +9844,8 @@
       <c r="O45">
         <v>0.76</v>
       </c>
-      <c r="P45" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>41</v>
       </c>
@@ -10024,11 +9891,8 @@
       <c r="O46">
         <v>0.79</v>
       </c>
-      <c r="P46" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>42</v>
       </c>
@@ -10074,11 +9938,8 @@
       <c r="O47">
         <v>0.79</v>
       </c>
-      <c r="P47" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>43</v>
       </c>
@@ -10124,11 +9985,8 @@
       <c r="O48">
         <v>0.79</v>
       </c>
-      <c r="P48" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -10171,11 +10029,8 @@
       <c r="O49">
         <v>0.7</v>
       </c>
-      <c r="P49" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>307</v>
       </c>
@@ -10215,11 +10070,8 @@
       <c r="M50" t="s">
         <v>36</v>
       </c>
-      <c r="P50" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>45</v>
       </c>
@@ -10265,11 +10117,8 @@
       <c r="O51">
         <v>0.79</v>
       </c>
-      <c r="P51" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>46</v>
       </c>
@@ -10315,11 +10164,8 @@
       <c r="O52">
         <v>0.79</v>
       </c>
-      <c r="P52" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>47</v>
       </c>
@@ -10365,11 +10211,8 @@
       <c r="O53">
         <v>0.79</v>
       </c>
-      <c r="P53" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>48</v>
       </c>
@@ -10415,11 +10258,8 @@
       <c r="O54">
         <v>0.79</v>
       </c>
-      <c r="P54" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>49</v>
       </c>
@@ -10465,11 +10305,8 @@
       <c r="O55">
         <v>0.79</v>
       </c>
-      <c r="P55" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>50</v>
       </c>
@@ -10515,11 +10352,8 @@
       <c r="O56">
         <v>0.79</v>
       </c>
-      <c r="P56" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>51</v>
       </c>
@@ -10565,11 +10399,8 @@
       <c r="O57">
         <v>0.79</v>
       </c>
-      <c r="P57" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>52</v>
       </c>
@@ -10615,11 +10446,8 @@
       <c r="O58">
         <v>0.79</v>
       </c>
-      <c r="P58" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>53</v>
       </c>
@@ -10665,11 +10493,8 @@
       <c r="O59">
         <v>0.79</v>
       </c>
-      <c r="P59" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>54</v>
       </c>
@@ -10715,11 +10540,8 @@
       <c r="O60">
         <v>0.79</v>
       </c>
-      <c r="P60" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>55</v>
       </c>
@@ -10765,11 +10587,8 @@
       <c r="O61">
         <v>0.79</v>
       </c>
-      <c r="P61" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>56</v>
       </c>
@@ -10815,11 +10634,8 @@
       <c r="O62">
         <v>0.79</v>
       </c>
-      <c r="P62" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>57</v>
       </c>
@@ -10865,11 +10681,8 @@
       <c r="O63">
         <v>0.79</v>
       </c>
-      <c r="P63" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>58</v>
       </c>
@@ -10909,11 +10722,8 @@
       <c r="M64" t="s">
         <v>36</v>
       </c>
-      <c r="P64" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>59</v>
       </c>
@@ -10956,11 +10766,8 @@
       <c r="O65">
         <v>0.79</v>
       </c>
-      <c r="P65" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>60</v>
       </c>
@@ -11006,11 +10813,8 @@
       <c r="O66">
         <v>0.86</v>
       </c>
-      <c r="P66" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>61</v>
       </c>
@@ -11056,11 +10860,8 @@
       <c r="O67">
         <v>0.79</v>
       </c>
-      <c r="P67" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>62</v>
       </c>
@@ -11106,11 +10907,8 @@
       <c r="O68">
         <v>0.85</v>
       </c>
-      <c r="P68" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
@@ -11156,11 +10954,8 @@
       <c r="O69">
         <v>0.85</v>
       </c>
-      <c r="P69" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
@@ -11206,11 +11001,8 @@
       <c r="O70">
         <v>0.85</v>
       </c>
-      <c r="P70" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
@@ -11256,11 +11048,8 @@
       <c r="O71">
         <v>0.79</v>
       </c>
-      <c r="P71" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>67</v>
       </c>
@@ -11300,11 +11089,8 @@
       <c r="M72" t="s">
         <v>36</v>
       </c>
-      <c r="P72" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
@@ -11350,11 +11136,8 @@
       <c r="O73">
         <v>0.79</v>
       </c>
-      <c r="P73" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
@@ -11400,11 +11183,8 @@
       <c r="O74">
         <v>0.79</v>
       </c>
-      <c r="P74" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>70</v>
       </c>
@@ -11450,11 +11230,8 @@
       <c r="O75">
         <v>0.79</v>
       </c>
-      <c r="P75" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>289</v>
       </c>
@@ -11494,11 +11271,8 @@
       <c r="M76" t="s">
         <v>36</v>
       </c>
-      <c r="P76" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>71</v>
       </c>
@@ -11544,11 +11318,8 @@
       <c r="O77">
         <v>0.79</v>
       </c>
-      <c r="P77" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>72</v>
       </c>
@@ -11594,11 +11365,8 @@
       <c r="O78">
         <v>0.79</v>
       </c>
-      <c r="P78" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>313</v>
       </c>
@@ -11638,11 +11406,8 @@
       <c r="M79" t="s">
         <v>36</v>
       </c>
-      <c r="P79" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>73</v>
       </c>
@@ -11685,11 +11450,8 @@
       <c r="O80">
         <v>0.79</v>
       </c>
-      <c r="P80" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>75</v>
       </c>
@@ -11732,11 +11494,8 @@
       <c r="O81">
         <v>0.7</v>
       </c>
-      <c r="P81" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>76</v>
       </c>
@@ -11782,11 +11541,8 @@
       <c r="O82">
         <v>0.87</v>
       </c>
-      <c r="P82" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>77</v>
       </c>
@@ -11832,11 +11588,8 @@
       <c r="O83">
         <v>0.86</v>
       </c>
-      <c r="P83" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>314</v>
       </c>
@@ -11879,11 +11632,8 @@
       <c r="N84">
         <v>0.35</v>
       </c>
-      <c r="P84" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>78</v>
       </c>
@@ -11929,11 +11679,8 @@
       <c r="O85">
         <v>0.86</v>
       </c>
-      <c r="P85" t="s">
-        <v>2231</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>79</v>
       </c>
@@ -11979,11 +11726,8 @@
       <c r="O86">
         <v>0.86</v>
       </c>
-      <c r="P86" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>80</v>
       </c>
@@ -12029,11 +11773,8 @@
       <c r="O87">
         <v>0.86</v>
       </c>
-      <c r="P87" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>81</v>
       </c>
@@ -12079,11 +11820,8 @@
       <c r="O88">
         <v>0.86</v>
       </c>
-      <c r="P88" t="s">
-        <v>2203</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>82</v>
       </c>
@@ -12129,11 +11867,8 @@
       <c r="O89">
         <v>0.86</v>
       </c>
-      <c r="P89" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>83</v>
       </c>
@@ -12179,11 +11914,8 @@
       <c r="O90">
         <v>0.85</v>
       </c>
-      <c r="P90" t="s">
-        <v>2208</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>84</v>
       </c>
@@ -12229,11 +11961,8 @@
       <c r="O91">
         <v>0.86</v>
       </c>
-      <c r="P91" t="s">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>85</v>
       </c>
@@ -12276,11 +12005,8 @@
       <c r="O92">
         <v>0.86</v>
       </c>
-      <c r="P92" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>86</v>
       </c>
@@ -12326,11 +12052,8 @@
       <c r="O93">
         <v>0.79</v>
       </c>
-      <c r="P93" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>87</v>
       </c>
@@ -12373,11 +12096,8 @@
       <c r="O94">
         <v>0.7</v>
       </c>
-      <c r="P94" t="s">
-        <v>2217</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>88</v>
       </c>
@@ -12423,11 +12143,8 @@
       <c r="O95">
         <v>0.79</v>
       </c>
-      <c r="P95" t="s">
-        <v>2218</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>89</v>
       </c>
@@ -12473,11 +12190,8 @@
       <c r="O96">
         <v>0.79</v>
       </c>
-      <c r="P96" t="s">
-        <v>2223</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>90</v>
       </c>
@@ -12523,11 +12237,8 @@
       <c r="O97">
         <v>0.79</v>
       </c>
-      <c r="P97" t="s">
-        <v>2225</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>91</v>
       </c>
@@ -12573,11 +12284,8 @@
       <c r="O98">
         <v>0.79</v>
       </c>
-      <c r="P98" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>92</v>
       </c>
@@ -12620,11 +12328,8 @@
       <c r="O99">
         <v>0.79</v>
       </c>
-      <c r="P99" t="s">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>93</v>
       </c>
@@ -12670,11 +12375,8 @@
       <c r="O100">
         <v>0.79</v>
       </c>
-      <c r="P100" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>94</v>
       </c>
@@ -12720,11 +12422,8 @@
       <c r="O101">
         <v>0.79</v>
       </c>
-      <c r="P101" t="s">
-        <v>2243</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>95</v>
       </c>
@@ -12764,11 +12463,8 @@
       <c r="M102" t="s">
         <v>36</v>
       </c>
-      <c r="P102" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>96</v>
       </c>
@@ -12814,11 +12510,8 @@
       <c r="O103">
         <v>0.81</v>
       </c>
-      <c r="P103" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>97</v>
       </c>
@@ -12864,11 +12557,8 @@
       <c r="O104">
         <v>0.79</v>
       </c>
-      <c r="P104" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>98</v>
       </c>
@@ -12914,11 +12604,8 @@
       <c r="O105">
         <v>0.79</v>
       </c>
-      <c r="P105" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>99</v>
       </c>
@@ -12964,11 +12651,8 @@
       <c r="O106">
         <v>0.88</v>
       </c>
-      <c r="P106" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>100</v>
       </c>
@@ -13014,11 +12698,8 @@
       <c r="O107">
         <v>0.88</v>
       </c>
-      <c r="P107" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>101</v>
       </c>
@@ -13064,11 +12745,8 @@
       <c r="O108">
         <v>0.88</v>
       </c>
-      <c r="P108" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>102</v>
       </c>
@@ -13114,11 +12792,8 @@
       <c r="O109">
         <v>0.86</v>
       </c>
-      <c r="P109" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>103</v>
       </c>
@@ -13164,11 +12839,8 @@
       <c r="O110">
         <v>0.89</v>
       </c>
-      <c r="P110" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>290</v>
       </c>
@@ -13208,11 +12880,8 @@
       <c r="M111" t="s">
         <v>36</v>
       </c>
-      <c r="P111" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>104</v>
       </c>
@@ -13258,11 +12927,8 @@
       <c r="O112">
         <v>0.88</v>
       </c>
-      <c r="P112" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>105</v>
       </c>
@@ -13305,11 +12971,8 @@
       <c r="O113">
         <v>0.88</v>
       </c>
-      <c r="P113" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>106</v>
       </c>
@@ -13355,11 +13018,8 @@
       <c r="O114">
         <v>0.79</v>
       </c>
-      <c r="P114" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>107</v>
       </c>
@@ -13405,11 +13065,8 @@
       <c r="O115">
         <v>0.79</v>
       </c>
-      <c r="P115" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>108</v>
       </c>
@@ -13455,11 +13112,8 @@
       <c r="O116">
         <v>0.79</v>
       </c>
-      <c r="P116" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>109</v>
       </c>
@@ -13496,11 +13150,8 @@
       <c r="M117" t="s">
         <v>36</v>
       </c>
-      <c r="P117" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>110</v>
       </c>
@@ -13546,11 +13197,8 @@
       <c r="O118">
         <v>0.79</v>
       </c>
-      <c r="P118" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>111</v>
       </c>
@@ -13596,11 +13244,8 @@
       <c r="O119">
         <v>0.77</v>
       </c>
-      <c r="P119" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>112</v>
       </c>
@@ -13646,11 +13291,8 @@
       <c r="O120">
         <v>0.77</v>
       </c>
-      <c r="P120" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>113</v>
       </c>
@@ -13696,11 +13338,8 @@
       <c r="O121">
         <v>0.77</v>
       </c>
-      <c r="P121" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>114</v>
       </c>
@@ -13746,11 +13385,8 @@
       <c r="O122">
         <v>0.77</v>
       </c>
-      <c r="P122" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>115</v>
       </c>
@@ -13793,11 +13429,8 @@
       <c r="O123">
         <v>0.77</v>
       </c>
-      <c r="P123" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>116</v>
       </c>
@@ -13837,11 +13470,8 @@
       <c r="M124" t="s">
         <v>36</v>
       </c>
-      <c r="P124" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>300</v>
       </c>
@@ -13881,11 +13511,8 @@
       <c r="M125" t="s">
         <v>36</v>
       </c>
-      <c r="P125" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>117</v>
       </c>
@@ -13925,11 +13552,8 @@
       <c r="M126" t="s">
         <v>36</v>
       </c>
-      <c r="P126" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>118</v>
       </c>
@@ -13975,11 +13599,8 @@
       <c r="O127">
         <v>0.79</v>
       </c>
-      <c r="P127" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>119</v>
       </c>
@@ -14025,11 +13646,8 @@
       <c r="O128">
         <v>0.88</v>
       </c>
-      <c r="P128" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>120</v>
       </c>
@@ -14075,11 +13693,8 @@
       <c r="O129">
         <v>0.79</v>
       </c>
-      <c r="P129" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>121</v>
       </c>
@@ -14125,11 +13740,8 @@
       <c r="O130">
         <v>0.88</v>
       </c>
-      <c r="P130" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>122</v>
       </c>
@@ -14169,11 +13781,8 @@
       <c r="M131" t="s">
         <v>36</v>
       </c>
-      <c r="P131" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>123</v>
       </c>
@@ -14219,11 +13828,8 @@
       <c r="O132">
         <v>0.8</v>
       </c>
-      <c r="P132" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>124</v>
       </c>
@@ -14269,11 +13875,8 @@
       <c r="O133">
         <v>0.79</v>
       </c>
-      <c r="P133" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>304</v>
       </c>
@@ -14313,11 +13916,8 @@
       <c r="M134" t="s">
         <v>36</v>
       </c>
-      <c r="P134" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>125</v>
       </c>
@@ -14363,11 +13963,8 @@
       <c r="O135">
         <v>0.79</v>
       </c>
-      <c r="P135" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>301</v>
       </c>
@@ -14407,11 +14004,8 @@
       <c r="M136" t="s">
         <v>36</v>
       </c>
-      <c r="P136" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>302</v>
       </c>
@@ -14451,11 +14045,8 @@
       <c r="M137" t="s">
         <v>36</v>
       </c>
-      <c r="P137" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126</v>
       </c>
@@ -14501,11 +14092,8 @@
       <c r="O138">
         <v>0.79</v>
       </c>
-      <c r="P138" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>127</v>
       </c>
@@ -14548,11 +14136,8 @@
       <c r="O139">
         <v>0.79</v>
       </c>
-      <c r="P139" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>128</v>
       </c>
@@ -14598,11 +14183,8 @@
       <c r="O140">
         <v>0.79</v>
       </c>
-      <c r="P140" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>129</v>
       </c>
@@ -14648,11 +14230,8 @@
       <c r="O141">
         <v>0.79</v>
       </c>
-      <c r="P141" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>130</v>
       </c>
@@ -14698,11 +14277,8 @@
       <c r="O142">
         <v>0.79</v>
       </c>
-      <c r="P142" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>131</v>
       </c>
@@ -14748,11 +14324,8 @@
       <c r="O143">
         <v>0.79</v>
       </c>
-      <c r="P143" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>132</v>
       </c>
@@ -14795,11 +14368,8 @@
       <c r="O144">
         <v>0.79</v>
       </c>
-      <c r="P144" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>133</v>
       </c>
@@ -14845,11 +14415,8 @@
       <c r="O145">
         <v>0.79</v>
       </c>
-      <c r="P145" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>134</v>
       </c>
@@ -14895,11 +14462,8 @@
       <c r="O146">
         <v>0.79</v>
       </c>
-      <c r="P146" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>135</v>
       </c>
@@ -14942,11 +14506,8 @@
       <c r="O147">
         <v>0.79</v>
       </c>
-      <c r="P147" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>136</v>
       </c>
@@ -14992,11 +14553,8 @@
       <c r="O148">
         <v>0.88</v>
       </c>
-      <c r="P148" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>137</v>
       </c>
@@ -15042,11 +14600,8 @@
       <c r="O149">
         <v>0.88</v>
       </c>
-      <c r="P149" t="s">
-        <v>2212</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>138</v>
       </c>
@@ -15092,11 +14647,8 @@
       <c r="O150">
         <v>0.88</v>
       </c>
-      <c r="P150" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>139</v>
       </c>
@@ -15142,11 +14694,8 @@
       <c r="O151">
         <v>0.88</v>
       </c>
-      <c r="P151" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>140</v>
       </c>
@@ -15192,11 +14741,8 @@
       <c r="O152">
         <v>0.88</v>
       </c>
-      <c r="P152" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>141</v>
       </c>
@@ -15239,11 +14785,8 @@
       <c r="O153">
         <v>0.88</v>
       </c>
-      <c r="P153" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>142</v>
       </c>
@@ -15289,11 +14832,8 @@
       <c r="O154">
         <v>0.79</v>
       </c>
-      <c r="P154" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>143</v>
       </c>
@@ -15339,11 +14879,8 @@
       <c r="O155">
         <v>0.67</v>
       </c>
-      <c r="P155" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>144</v>
       </c>
@@ -15389,11 +14926,8 @@
       <c r="O156">
         <v>0.79</v>
       </c>
-      <c r="P156" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>145</v>
       </c>
@@ -15436,11 +14970,8 @@
       <c r="O157">
         <v>0.79</v>
       </c>
-      <c r="P157" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>146</v>
       </c>
@@ -15486,11 +15017,8 @@
       <c r="O158">
         <v>0.79</v>
       </c>
-      <c r="P158" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>147</v>
       </c>
@@ -15536,11 +15064,8 @@
       <c r="O159">
         <v>0.79</v>
       </c>
-      <c r="P159" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>148</v>
       </c>
@@ -15586,11 +15111,8 @@
       <c r="O160">
         <v>0.91</v>
       </c>
-      <c r="P160" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>149</v>
       </c>
@@ -15636,11 +15158,8 @@
       <c r="O161">
         <v>0.86</v>
       </c>
-      <c r="P161" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>150</v>
       </c>
@@ -15686,11 +15205,8 @@
       <c r="O162">
         <v>0.86</v>
       </c>
-      <c r="P162" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>151</v>
       </c>
@@ -15736,11 +15252,8 @@
       <c r="O163">
         <v>0.86</v>
       </c>
-      <c r="P163" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>152</v>
       </c>
@@ -15786,11 +15299,8 @@
       <c r="O164">
         <v>0.86</v>
       </c>
-      <c r="P164" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>153</v>
       </c>
@@ -15836,11 +15346,8 @@
       <c r="O165">
         <v>0.86</v>
       </c>
-      <c r="P165" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>154</v>
       </c>
@@ -15886,11 +15393,8 @@
       <c r="O166">
         <v>0.86</v>
       </c>
-      <c r="P166" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>155</v>
       </c>
@@ -15936,11 +15440,8 @@
       <c r="O167">
         <v>0.88</v>
       </c>
-      <c r="P167" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>303</v>
       </c>
@@ -15983,11 +15484,8 @@
       <c r="N168">
         <v>0.65</v>
       </c>
-      <c r="P168" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>156</v>
       </c>
@@ -16033,11 +15531,8 @@
       <c r="O169">
         <v>0.83</v>
       </c>
-      <c r="P169" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>157</v>
       </c>
@@ -16083,11 +15578,8 @@
       <c r="O170">
         <v>0.83</v>
       </c>
-      <c r="P170" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>158</v>
       </c>
@@ -16130,11 +15622,8 @@
       <c r="O171">
         <v>0.86</v>
       </c>
-      <c r="P171" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>159</v>
       </c>
@@ -16180,11 +15669,8 @@
       <c r="O172">
         <v>0.86</v>
       </c>
-      <c r="P172" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>160</v>
       </c>
@@ -16230,11 +15716,8 @@
       <c r="O173">
         <v>0.84</v>
       </c>
-      <c r="P173" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>161</v>
       </c>
@@ -16280,11 +15763,8 @@
       <c r="O174">
         <v>0.86</v>
       </c>
-      <c r="P174" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>162</v>
       </c>
@@ -16330,11 +15810,8 @@
       <c r="O175">
         <v>0.86</v>
       </c>
-      <c r="P175" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>163</v>
       </c>
@@ -16380,11 +15857,8 @@
       <c r="O176">
         <v>0.79</v>
       </c>
-      <c r="P176" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>164</v>
       </c>
@@ -16430,11 +15904,8 @@
       <c r="O177">
         <v>0.79</v>
       </c>
-      <c r="P177" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>165</v>
       </c>
@@ -16480,11 +15951,8 @@
       <c r="O178">
         <v>0.79</v>
       </c>
-      <c r="P178" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>166</v>
       </c>
@@ -16530,11 +15998,8 @@
       <c r="O179">
         <v>0.79</v>
       </c>
-      <c r="P179" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>167</v>
       </c>
@@ -16580,11 +16045,8 @@
       <c r="O180">
         <v>0.79</v>
       </c>
-      <c r="P180" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>168</v>
       </c>
@@ -16630,11 +16092,8 @@
       <c r="O181">
         <v>0.79</v>
       </c>
-      <c r="P181" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>169</v>
       </c>
@@ -16680,11 +16139,8 @@
       <c r="O182">
         <v>0.79</v>
       </c>
-      <c r="P182" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>170</v>
       </c>
@@ -16727,11 +16183,8 @@
       <c r="O183">
         <v>0.79</v>
       </c>
-      <c r="P183" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>171</v>
       </c>
@@ -16777,11 +16230,8 @@
       <c r="O184">
         <v>0.79</v>
       </c>
-      <c r="P184" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>172</v>
       </c>
@@ -16827,11 +16277,8 @@
       <c r="O185">
         <v>0.79</v>
       </c>
-      <c r="P185" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>173</v>
       </c>
@@ -16877,11 +16324,8 @@
       <c r="O186">
         <v>0.79</v>
       </c>
-      <c r="P186" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>174</v>
       </c>
@@ -16924,11 +16368,8 @@
       <c r="O187">
         <v>0.79</v>
       </c>
-      <c r="P187" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>175</v>
       </c>
@@ -16974,11 +16415,8 @@
       <c r="O188">
         <v>0.79</v>
       </c>
-      <c r="P188" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>176</v>
       </c>
@@ -16992,7 +16430,7 @@
         <v>1017</v>
       </c>
       <c r="E189" t="s">
-        <v>1021</v>
+        <v>2267</v>
       </c>
       <c r="F189" t="s">
         <v>1022</v>
@@ -17024,11 +16462,8 @@
       <c r="O189">
         <v>0.79</v>
       </c>
-      <c r="P189" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>177</v>
       </c>
@@ -17074,11 +16509,8 @@
       <c r="O190">
         <v>0.79</v>
       </c>
-      <c r="P190" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>178</v>
       </c>
@@ -17124,11 +16556,8 @@
       <c r="O191">
         <v>0.79</v>
       </c>
-      <c r="P191" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>179</v>
       </c>
@@ -17174,11 +16603,8 @@
       <c r="O192">
         <v>0.79</v>
       </c>
-      <c r="P192" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>180</v>
       </c>
@@ -17224,11 +16650,8 @@
       <c r="O193">
         <v>0.81</v>
       </c>
-      <c r="P193" t="s">
-        <v>2149</v>
-      </c>
-    </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>181</v>
       </c>
@@ -17274,11 +16697,8 @@
       <c r="O194">
         <v>0.79</v>
       </c>
-      <c r="P194" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>182</v>
       </c>
@@ -17324,11 +16744,8 @@
       <c r="O195">
         <v>0.79</v>
       </c>
-      <c r="P195" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>284</v>
       </c>
@@ -17368,11 +16785,8 @@
       <c r="M196" t="s">
         <v>36</v>
       </c>
-      <c r="P196" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>183</v>
       </c>
@@ -17418,11 +16832,8 @@
       <c r="O197">
         <v>0.77</v>
       </c>
-      <c r="P197" t="s">
-        <v>2228</v>
-      </c>
-    </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>184</v>
       </c>
@@ -17468,11 +16879,8 @@
       <c r="O198">
         <v>0.81</v>
       </c>
-      <c r="P198" t="s">
-        <v>2124</v>
-      </c>
-    </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>185</v>
       </c>
@@ -17518,11 +16926,8 @@
       <c r="O199">
         <v>0.79</v>
       </c>
-      <c r="P199" t="s">
-        <v>2261</v>
-      </c>
-    </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>186</v>
       </c>
@@ -17568,11 +16973,8 @@
       <c r="O200">
         <v>0.79</v>
       </c>
-      <c r="P200" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>187</v>
       </c>
@@ -17618,11 +17020,8 @@
       <c r="O201">
         <v>0.79</v>
       </c>
-      <c r="P201" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>188</v>
       </c>
@@ -17665,11 +17064,8 @@
       <c r="O202">
         <v>0.79</v>
       </c>
-      <c r="P202" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>189</v>
       </c>
@@ -17715,11 +17111,8 @@
       <c r="O203">
         <v>0.79</v>
       </c>
-      <c r="P203" t="s">
-        <v>2233</v>
-      </c>
-    </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>190</v>
       </c>
@@ -17765,11 +17158,8 @@
       <c r="O204">
         <v>0.75</v>
       </c>
-      <c r="P204" t="s">
-        <v>2191</v>
-      </c>
-    </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>191</v>
       </c>
@@ -17815,11 +17205,8 @@
       <c r="O205">
         <v>0.87</v>
       </c>
-      <c r="P205" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>192</v>
       </c>
@@ -17865,11 +17252,8 @@
       <c r="O206">
         <v>0.79</v>
       </c>
-      <c r="P206" t="s">
-        <v>2165</v>
-      </c>
-    </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>308</v>
       </c>
@@ -17909,11 +17293,8 @@
       <c r="M207" t="s">
         <v>36</v>
       </c>
-      <c r="P207" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>193</v>
       </c>
@@ -17959,11 +17340,8 @@
       <c r="O208">
         <v>0.79</v>
       </c>
-      <c r="P208" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>281</v>
       </c>
@@ -18003,11 +17381,8 @@
       <c r="M209" t="s">
         <v>36</v>
       </c>
-      <c r="P209" t="s">
-        <v>2172</v>
-      </c>
-    </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>194</v>
       </c>
@@ -18053,11 +17428,8 @@
       <c r="O210">
         <v>0.8</v>
       </c>
-      <c r="P210" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>195</v>
       </c>
@@ -18103,11 +17475,8 @@
       <c r="O211">
         <v>0.8</v>
       </c>
-      <c r="P211" t="s">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>196</v>
       </c>
@@ -18153,11 +17522,8 @@
       <c r="O212">
         <v>0.8</v>
       </c>
-      <c r="P212" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>197</v>
       </c>
@@ -18203,11 +17569,8 @@
       <c r="O213">
         <v>0.8</v>
       </c>
-      <c r="P213" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>198</v>
       </c>
@@ -18253,11 +17616,8 @@
       <c r="O214">
         <v>0.79</v>
       </c>
-      <c r="P214" t="s">
-        <v>2226</v>
-      </c>
-    </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>199</v>
       </c>
@@ -18303,11 +17663,8 @@
       <c r="O215">
         <v>0.79</v>
       </c>
-      <c r="P215" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>200</v>
       </c>
@@ -18353,11 +17710,8 @@
       <c r="O216">
         <v>0.79</v>
       </c>
-      <c r="P216" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>201</v>
       </c>
@@ -18403,11 +17757,8 @@
       <c r="O217">
         <v>0.79</v>
       </c>
-      <c r="P217" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>305</v>
       </c>
@@ -18447,11 +17798,8 @@
       <c r="M218" t="s">
         <v>36</v>
       </c>
-      <c r="P218" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>202</v>
       </c>
@@ -18497,11 +17845,8 @@
       <c r="O219">
         <v>0.79</v>
       </c>
-      <c r="P219" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>306</v>
       </c>
@@ -18541,11 +17886,8 @@
       <c r="M220" t="s">
         <v>36</v>
       </c>
-      <c r="P220" t="s">
-        <v>2179</v>
-      </c>
-    </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>203</v>
       </c>
@@ -18591,11 +17933,8 @@
       <c r="O221">
         <v>0.79</v>
       </c>
-      <c r="P221" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>204</v>
       </c>
@@ -18641,11 +17980,8 @@
       <c r="O222">
         <v>0.79</v>
       </c>
-      <c r="P222" t="s">
-        <v>2181</v>
-      </c>
-    </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>205</v>
       </c>
@@ -18691,11 +18027,8 @@
       <c r="O223">
         <v>0.79</v>
       </c>
-      <c r="P223" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>206</v>
       </c>
@@ -18741,11 +18074,8 @@
       <c r="O224">
         <v>0.79</v>
       </c>
-      <c r="P224" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>208</v>
       </c>
@@ -18791,11 +18121,8 @@
       <c r="O225">
         <v>0.79</v>
       </c>
-      <c r="P225" t="s">
-        <v>2173</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>209</v>
       </c>
@@ -18838,11 +18165,8 @@
       <c r="O226">
         <v>0.79</v>
       </c>
-      <c r="P226" t="s">
-        <v>2141</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>311</v>
       </c>
@@ -18885,11 +18209,8 @@
       <c r="O227">
         <v>0.79</v>
       </c>
-      <c r="P227" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>210</v>
       </c>
@@ -18935,11 +18256,8 @@
       <c r="O228">
         <v>0.79</v>
       </c>
-      <c r="P228" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>211</v>
       </c>
@@ -18985,11 +18303,8 @@
       <c r="O229">
         <v>0.86</v>
       </c>
-      <c r="P229" t="s">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>213</v>
       </c>
@@ -19032,11 +18347,8 @@
       <c r="O230">
         <v>0.86</v>
       </c>
-      <c r="P230" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>214</v>
       </c>
@@ -19082,11 +18394,8 @@
       <c r="O231">
         <v>0.79</v>
       </c>
-      <c r="P231" t="s">
-        <v>2194</v>
-      </c>
-    </row>
-    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>215</v>
       </c>
@@ -19132,11 +18441,8 @@
       <c r="O232">
         <v>0.79</v>
       </c>
-      <c r="P232" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>216</v>
       </c>
@@ -19182,11 +18488,8 @@
       <c r="O233">
         <v>0.79</v>
       </c>
-      <c r="P233" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>287</v>
       </c>
@@ -19226,11 +18529,8 @@
       <c r="M234" t="s">
         <v>36</v>
       </c>
-      <c r="P234" t="s">
-        <v>2193</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>217</v>
       </c>
@@ -19276,11 +18576,8 @@
       <c r="O235">
         <v>0.8</v>
       </c>
-      <c r="P235" t="s">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>218</v>
       </c>
@@ -19326,11 +18623,8 @@
       <c r="O236">
         <v>0.8</v>
       </c>
-      <c r="P236" t="s">
-        <v>2195</v>
-      </c>
-    </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>219</v>
       </c>
@@ -19376,11 +18670,8 @@
       <c r="O237">
         <v>0.8</v>
       </c>
-      <c r="P237" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>220</v>
       </c>
@@ -19423,11 +18714,8 @@
       <c r="O238">
         <v>0.8</v>
       </c>
-      <c r="P238" t="s">
-        <v>2153</v>
-      </c>
-    </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>221</v>
       </c>
@@ -19473,11 +18761,8 @@
       <c r="O239">
         <v>0.8</v>
       </c>
-      <c r="P239" t="s">
-        <v>2217</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>222</v>
       </c>
@@ -19520,11 +18805,8 @@
       <c r="O240">
         <v>0.79</v>
       </c>
-      <c r="P240" t="s">
-        <v>2207</v>
-      </c>
-    </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>223</v>
       </c>
@@ -19570,11 +18852,8 @@
       <c r="O241">
         <v>0.81</v>
       </c>
-      <c r="P241" t="s">
-        <v>2118</v>
-      </c>
-    </row>
-    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>224</v>
       </c>
@@ -19620,11 +18899,8 @@
       <c r="O242">
         <v>0.79</v>
       </c>
-      <c r="P242" t="s">
-        <v>2156</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>225</v>
       </c>
@@ -19670,11 +18946,8 @@
       <c r="O243">
         <v>0.79</v>
       </c>
-      <c r="P243" t="s">
-        <v>2243</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>286</v>
       </c>
@@ -19714,11 +18987,8 @@
       <c r="M244" t="s">
         <v>36</v>
       </c>
-      <c r="P244" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>227</v>
       </c>
@@ -19758,11 +19028,8 @@
       <c r="M245" t="s">
         <v>36</v>
       </c>
-      <c r="P245" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>228</v>
       </c>
@@ -19802,11 +19069,8 @@
       <c r="M246" t="s">
         <v>36</v>
       </c>
-      <c r="P246" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>229</v>
       </c>
@@ -19852,11 +19116,8 @@
       <c r="O247">
         <v>0.79</v>
       </c>
-      <c r="P247" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>231</v>
       </c>
@@ -19902,11 +19163,8 @@
       <c r="O248">
         <v>0.77</v>
       </c>
-      <c r="P248" t="s">
-        <v>2214</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>232</v>
       </c>
@@ -19952,11 +19210,8 @@
       <c r="O249">
         <v>0.77</v>
       </c>
-      <c r="P249" t="s">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>233</v>
       </c>
@@ -19999,11 +19254,8 @@
       <c r="O250">
         <v>0.77</v>
       </c>
-      <c r="P250" t="s">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>230</v>
       </c>
@@ -20049,11 +19301,8 @@
       <c r="O251">
         <v>0.77</v>
       </c>
-      <c r="P251" t="s">
-        <v>2252</v>
-      </c>
-    </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>234</v>
       </c>
@@ -20099,11 +19348,8 @@
       <c r="O252">
         <v>0.79</v>
       </c>
-      <c r="P252" t="s">
-        <v>2211</v>
-      </c>
-    </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>235</v>
       </c>
@@ -20149,11 +19395,8 @@
       <c r="O253">
         <v>0.79</v>
       </c>
-      <c r="P253" t="s">
-        <v>2196</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>236</v>
       </c>
@@ -20190,11 +19433,8 @@
       <c r="M254" t="s">
         <v>36</v>
       </c>
-      <c r="P254" t="s">
-        <v>2213</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>237</v>
       </c>
@@ -20240,11 +19480,8 @@
       <c r="O255">
         <v>0.79</v>
       </c>
-      <c r="P255" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>238</v>
       </c>
@@ -20290,11 +19527,8 @@
       <c r="O256">
         <v>0.79</v>
       </c>
-      <c r="P256" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>239</v>
       </c>
@@ -20340,11 +19574,8 @@
       <c r="O257">
         <v>0.79</v>
       </c>
-      <c r="P257" t="s">
-        <v>2216</v>
-      </c>
-    </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>240</v>
       </c>
@@ -20390,11 +19621,8 @@
       <c r="O258">
         <v>0.79</v>
       </c>
-      <c r="P258" t="s">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>241</v>
       </c>
@@ -20440,11 +19668,8 @@
       <c r="O259">
         <v>0.79</v>
       </c>
-      <c r="P259" t="s">
-        <v>2224</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>242</v>
       </c>
@@ -20490,11 +19715,8 @@
       <c r="O260">
         <v>0.79</v>
       </c>
-      <c r="P260" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>243</v>
       </c>
@@ -20537,11 +19759,8 @@
       <c r="O261">
         <v>0.79</v>
       </c>
-      <c r="P261" t="s">
-        <v>2221</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>244</v>
       </c>
@@ -20587,11 +19806,8 @@
       <c r="O262">
         <v>0.79</v>
       </c>
-      <c r="P262" t="s">
-        <v>2256</v>
-      </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>283</v>
       </c>
@@ -20631,11 +19847,8 @@
       <c r="M263" t="s">
         <v>36</v>
       </c>
-      <c r="P263" t="s">
-        <v>2229</v>
-      </c>
-    </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>246</v>
       </c>
@@ -20681,11 +19894,8 @@
       <c r="O264">
         <v>0.79</v>
       </c>
-      <c r="P264" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>247</v>
       </c>
@@ -20728,11 +19938,8 @@
       <c r="O265">
         <v>0.7</v>
       </c>
-      <c r="P265" t="s">
-        <v>2142</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>248</v>
       </c>
@@ -20778,11 +19985,8 @@
       <c r="O266">
         <v>0.82</v>
       </c>
-      <c r="P266" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>249</v>
       </c>
@@ -20828,11 +20032,8 @@
       <c r="O267">
         <v>0.86</v>
       </c>
-      <c r="P267" t="s">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>250</v>
       </c>
@@ -20878,11 +20079,8 @@
       <c r="O268">
         <v>0.79</v>
       </c>
-      <c r="P268" t="s">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>252</v>
       </c>
@@ -20928,11 +20126,8 @@
       <c r="O269">
         <v>0.79</v>
       </c>
-      <c r="P269" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>253</v>
       </c>
@@ -20978,11 +20173,8 @@
       <c r="O270">
         <v>0.9</v>
       </c>
-      <c r="P270" t="s">
-        <v>2169</v>
-      </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>254</v>
       </c>
@@ -21022,11 +20214,8 @@
       <c r="M271" t="s">
         <v>36</v>
       </c>
-      <c r="P271" t="s">
-        <v>2128</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>255</v>
       </c>
@@ -21069,11 +20258,8 @@
       <c r="O272">
         <v>0.7</v>
       </c>
-      <c r="P272" t="s">
-        <v>2204</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>256</v>
       </c>
@@ -21119,11 +20305,8 @@
       <c r="O273">
         <v>0.91</v>
       </c>
-      <c r="P273" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>257</v>
       </c>
@@ -21169,11 +20352,8 @@
       <c r="O274">
         <v>0.91</v>
       </c>
-      <c r="P274" t="s">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>310</v>
       </c>
@@ -21213,11 +20393,8 @@
       <c r="M275" t="s">
         <v>36</v>
       </c>
-      <c r="P275" t="s">
-        <v>2234</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>258</v>
       </c>
@@ -21260,11 +20437,8 @@
       <c r="O276">
         <v>0.91</v>
       </c>
-      <c r="P276" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>285</v>
       </c>
@@ -21304,11 +20478,8 @@
       <c r="M277" t="s">
         <v>36</v>
       </c>
-      <c r="P277" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>226</v>
       </c>
@@ -21354,11 +20525,8 @@
       <c r="O278">
         <v>0.7</v>
       </c>
-      <c r="P278" t="s">
-        <v>2237</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>259</v>
       </c>
@@ -21404,11 +20572,8 @@
       <c r="O279">
         <v>0.79</v>
       </c>
-      <c r="P279" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>316</v>
       </c>
@@ -21448,11 +20613,8 @@
       <c r="M280" t="s">
         <v>36</v>
       </c>
-      <c r="P280" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>260</v>
       </c>
@@ -21498,11 +20660,8 @@
       <c r="O281">
         <v>0.79</v>
       </c>
-      <c r="P281" t="s">
-        <v>2114</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>315</v>
       </c>
@@ -21542,11 +20701,8 @@
       <c r="M282" t="s">
         <v>36</v>
       </c>
-      <c r="P282" t="s">
-        <v>2241</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>261</v>
       </c>
@@ -21592,11 +20748,8 @@
       <c r="O283">
         <v>0.79</v>
       </c>
-      <c r="P283" t="s">
-        <v>2242</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>262</v>
       </c>
@@ -21642,11 +20795,8 @@
       <c r="O284">
         <v>0.79</v>
       </c>
-      <c r="P284" t="s">
-        <v>2239</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>263</v>
       </c>
@@ -21692,11 +20842,8 @@
       <c r="O285">
         <v>0.79</v>
       </c>
-      <c r="P285" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>317</v>
       </c>
@@ -21736,11 +20883,8 @@
       <c r="M286" t="s">
         <v>36</v>
       </c>
-      <c r="P286" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>264</v>
       </c>
@@ -21786,11 +20930,8 @@
       <c r="O287">
         <v>0.79</v>
       </c>
-      <c r="P287" t="s">
-        <v>2246</v>
-      </c>
-    </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>265</v>
       </c>
@@ -21836,11 +20977,8 @@
       <c r="O288">
         <v>0.79</v>
       </c>
-      <c r="P288" t="s">
-        <v>2247</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>266</v>
       </c>
@@ -21886,11 +21024,8 @@
       <c r="O289">
         <v>0.79</v>
       </c>
-      <c r="P289" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>267</v>
       </c>
@@ -21936,11 +21071,8 @@
       <c r="O290">
         <v>0.79</v>
       </c>
-      <c r="P290" t="s">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>269</v>
       </c>
@@ -21983,11 +21115,8 @@
       <c r="O291">
         <v>0.79</v>
       </c>
-      <c r="P291" t="s">
-        <v>2201</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>270</v>
       </c>
@@ -22033,11 +21162,8 @@
       <c r="O292">
         <v>0.79</v>
       </c>
-      <c r="P292" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>271</v>
       </c>
@@ -22083,11 +21209,8 @@
       <c r="O293">
         <v>0.79</v>
       </c>
-      <c r="P293" t="s">
-        <v>2144</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>272</v>
       </c>
@@ -22133,11 +21256,8 @@
       <c r="O294">
         <v>0.79</v>
       </c>
-      <c r="P294" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>212</v>
       </c>
@@ -22177,11 +21297,8 @@
       <c r="M295" t="s">
         <v>36</v>
       </c>
-      <c r="P295" t="s">
-        <v>2177</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>274</v>
       </c>
@@ -22227,11 +21344,8 @@
       <c r="O296">
         <v>0.79</v>
       </c>
-      <c r="P296" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>275</v>
       </c>
@@ -22277,11 +21391,8 @@
       <c r="O297">
         <v>0.79</v>
       </c>
-      <c r="P297" t="s">
-        <v>2164</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>276</v>
       </c>
@@ -22327,11 +21438,8 @@
       <c r="O298">
         <v>0.79</v>
       </c>
-      <c r="P298" t="s">
-        <v>2189</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>277</v>
       </c>
@@ -22377,11 +21485,8 @@
       <c r="O299">
         <v>0.79</v>
       </c>
-      <c r="P299" t="s">
-        <v>2251</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>278</v>
       </c>
@@ -22424,11 +21529,8 @@
       <c r="O300">
         <v>0.79</v>
       </c>
-      <c r="P300" t="s">
-        <v>2168</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>309</v>
       </c>
@@ -22468,18 +21570,8 @@
       <c r="M301" t="s">
         <v>36</v>
       </c>
-      <c r="P301" t="s">
-        <v>2223</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="L1:L301" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="other"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O301">
     <sortCondition ref="B2:B301"/>
   </sortState>
@@ -56313,7 +55405,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:BK300"/>
+  <dimension ref="A1:BM301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -56323,9 +55415,10 @@
     <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:63" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -56506,8 +55599,11 @@
       <c r="BK1" s="1" t="s">
         <v>1170</v>
       </c>
-    </row>
-    <row r="2" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM1" s="7" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -56644,8 +55740,11 @@
       <c r="BK2" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM2" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -56784,8 +55883,11 @@
       <c r="BK3" s="6">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM3" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -56914,8 +56016,11 @@
       <c r="BK4" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM4" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -57060,8 +56165,11 @@
       <c r="BK5" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM5" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>318</v>
       </c>
@@ -57174,8 +56282,11 @@
       <c r="BK6" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="7" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM6" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -57308,8 +56419,11 @@
       <c r="BK7" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="8" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -57452,8 +56566,11 @@
       <c r="BK8" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="9" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM8" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -57576,8 +56693,11 @@
       <c r="BK9" s="6">
         <v>65</v>
       </c>
-    </row>
-    <row r="10" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM9" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>282</v>
       </c>
@@ -57706,8 +56826,11 @@
       <c r="BK10" s="6">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM10" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -57850,8 +56973,11 @@
       <c r="BK11" s="6">
         <v>102</v>
       </c>
-    </row>
-    <row r="12" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM11" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -57988,8 +57114,11 @@
       <c r="BK12" s="6">
         <v>46</v>
       </c>
-    </row>
-    <row r="13" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM12" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -58128,8 +57257,11 @@
       <c r="BK13" s="6">
         <v>139.4</v>
       </c>
-    </row>
-    <row r="14" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -58268,8 +57400,11 @@
       <c r="BK14" s="6">
         <v>129</v>
       </c>
-    </row>
-    <row r="15" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM14" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -58404,8 +57539,11 @@
       <c r="BK15" s="6">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM15" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -58534,8 +57672,11 @@
       <c r="BK16" s="6">
         <v>159</v>
       </c>
-    </row>
-    <row r="17" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM16" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -58676,8 +57817,11 @@
       <c r="BK17" s="6">
         <v>186</v>
       </c>
-    </row>
-    <row r="18" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM17" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -58818,8 +57962,11 @@
       <c r="BK18" s="6">
         <v>147</v>
       </c>
-    </row>
-    <row r="19" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM18" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -58960,8 +58107,11 @@
       <c r="BK19" s="6">
         <v>193</v>
       </c>
-    </row>
-    <row r="20" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM19" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -59102,8 +58252,11 @@
       <c r="BK20" s="6">
         <v>175</v>
       </c>
-    </row>
-    <row r="21" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM20" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -59242,8 +58395,11 @@
       <c r="BK21" s="6">
         <v>113</v>
       </c>
-    </row>
-    <row r="22" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM21" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -59382,8 +58538,11 @@
       <c r="BK22" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM22" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -59520,8 +58679,11 @@
       <c r="BK23" s="6">
         <v>100.01</v>
       </c>
-    </row>
-    <row r="24" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM23" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -59650,8 +58812,11 @@
       <c r="BK24" s="6">
         <v>73</v>
       </c>
-    </row>
-    <row r="25" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM24" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>312</v>
       </c>
@@ -59782,8 +58947,11 @@
       <c r="BK25" s="6">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM25" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -59920,8 +59088,11 @@
       <c r="BK26" s="6">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM26" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -60064,8 +59235,11 @@
       <c r="BK27" s="6">
         <v>60.8</v>
       </c>
-    </row>
-    <row r="28" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM27" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -60204,8 +59378,11 @@
       <c r="BK28" s="6">
         <v>145</v>
       </c>
-    </row>
-    <row r="29" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM28" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -60342,8 +59519,11 @@
       <c r="BK29" s="6">
         <v>45</v>
       </c>
-    </row>
-    <row r="30" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM29" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -60480,8 +59660,11 @@
       <c r="BK30" s="6">
         <v>16</v>
       </c>
-    </row>
-    <row r="31" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM30" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -60610,8 +59793,11 @@
       <c r="BK31" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM31" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -60752,8 +59938,11 @@
       <c r="BK32" s="6">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM32" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -60894,8 +60083,11 @@
       <c r="BK33" s="6">
         <v>74</v>
       </c>
-    </row>
-    <row r="34" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM33" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -61034,8 +60226,11 @@
       <c r="BK34" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="35" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM34" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -61176,8 +60371,11 @@
       <c r="BK35" s="6">
         <v>80</v>
       </c>
-    </row>
-    <row r="36" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM35" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -61314,8 +60512,11 @@
       <c r="BK36" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="37" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM36" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -61444,8 +60645,11 @@
       <c r="BK37" s="6">
         <v>27</v>
       </c>
-    </row>
-    <row r="38" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM37" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -61586,8 +60790,11 @@
       <c r="BK38" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="39" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM38" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -61728,8 +60935,11 @@
       <c r="BK39" s="6">
         <v>96</v>
       </c>
-    </row>
-    <row r="40" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM39" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -61866,8 +61076,11 @@
       <c r="BK40" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="41" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM40" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -62006,8 +61219,11 @@
       <c r="BK41" s="6">
         <v>143</v>
       </c>
-    </row>
-    <row r="42" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM41" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -62152,8 +61368,11 @@
       <c r="BK42" s="6">
         <v>97</v>
       </c>
-    </row>
-    <row r="43" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM42" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -62280,8 +61499,11 @@
       <c r="BK43" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="44" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM43" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -62418,8 +61640,11 @@
       <c r="BK44" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="45" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM44" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -62554,8 +61779,11 @@
       <c r="BK45" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="46" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM45" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -62694,8 +61922,11 @@
       <c r="BK46" s="6">
         <v>51</v>
       </c>
-    </row>
-    <row r="47" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM46" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -62824,8 +62055,11 @@
       <c r="BK47" s="6">
         <v>61</v>
       </c>
-    </row>
-    <row r="48" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM47" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>307</v>
       </c>
@@ -62948,8 +62182,11 @@
       <c r="BK48" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="49" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM48" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>45</v>
       </c>
@@ -63090,8 +62327,11 @@
       <c r="BK49" s="6">
         <v>144</v>
       </c>
-    </row>
-    <row r="50" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM49" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>46</v>
       </c>
@@ -63230,8 +62470,11 @@
       <c r="BK50" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="51" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM50" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>47</v>
       </c>
@@ -63370,8 +62613,11 @@
       <c r="BK51" s="6">
         <v>89</v>
       </c>
-    </row>
-    <row r="52" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM51" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>48</v>
       </c>
@@ -63512,8 +62758,11 @@
       <c r="BK52" s="6">
         <v>81</v>
       </c>
-    </row>
-    <row r="53" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM52" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>49</v>
       </c>
@@ -63650,8 +62899,11 @@
       <c r="BK53" s="6">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM53" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>50</v>
       </c>
@@ -63790,8 +63042,11 @@
       <c r="BK54" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="55" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM54" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>51</v>
       </c>
@@ -63930,8 +63185,11 @@
       <c r="BK55" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="56" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM55" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>52</v>
       </c>
@@ -64074,8 +63332,11 @@
       <c r="BK56" s="6">
         <v>68.5</v>
       </c>
-    </row>
-    <row r="57" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM56" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>53</v>
       </c>
@@ -64210,8 +63471,11 @@
       <c r="BK57" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="58" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM57" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>54</v>
       </c>
@@ -64348,8 +63612,11 @@
       <c r="BK58" s="6">
         <v>74</v>
       </c>
-    </row>
-    <row r="59" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM58" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>55</v>
       </c>
@@ -64490,8 +63757,11 @@
       <c r="BK59" s="6">
         <v>64</v>
       </c>
-    </row>
-    <row r="60" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM59" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>56</v>
       </c>
@@ -64628,8 +63898,11 @@
       <c r="BK60" s="6">
         <v>85</v>
       </c>
-    </row>
-    <row r="61" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM60" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>57</v>
       </c>
@@ -64764,8 +64037,11 @@
       <c r="BK61" s="6">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="62" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM61" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>58</v>
       </c>
@@ -64890,8 +64166,11 @@
       <c r="BK62" s="6">
         <v>91</v>
       </c>
-    </row>
-    <row r="63" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM62" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>59</v>
       </c>
@@ -65020,8 +64299,11 @@
       <c r="BK63" s="6">
         <v>72.400001525878906</v>
       </c>
-    </row>
-    <row r="64" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM63" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="64" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>60</v>
       </c>
@@ -65162,8 +64444,11 @@
       <c r="BK64" s="6">
         <v>109</v>
       </c>
-    </row>
-    <row r="65" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM64" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>61</v>
       </c>
@@ -65300,8 +64585,11 @@
       <c r="BK65" s="6">
         <v>70.010000000000005</v>
       </c>
-    </row>
-    <row r="66" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM65" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="66" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>62</v>
       </c>
@@ -65454,8 +64742,11 @@
       <c r="BK66" s="6">
         <v>198</v>
       </c>
-    </row>
-    <row r="67" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM66" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -65590,8 +64881,11 @@
       <c r="BK67" s="6">
         <v>90</v>
       </c>
-    </row>
-    <row r="68" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM67" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -65728,8 +65022,11 @@
       <c r="BK68" s="6">
         <v>85</v>
       </c>
-    </row>
-    <row r="69" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM68" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -65876,8 +65173,11 @@
       <c r="BK69" s="6">
         <v>113</v>
       </c>
-    </row>
-    <row r="70" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM69" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -65986,8 +65286,11 @@
       <c r="BI70" s="6"/>
       <c r="BJ70" s="6"/>
       <c r="BK70" s="6"/>
-    </row>
-    <row r="71" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM70" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="71" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -66124,8 +65427,11 @@
       <c r="BK71" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="72" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM71" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -66270,8 +65576,11 @@
       <c r="BK72" s="6">
         <v>47</v>
       </c>
-    </row>
-    <row r="73" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM72" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -66408,8 +65717,11 @@
       <c r="BK73" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM73" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>289</v>
       </c>
@@ -66518,8 +65830,11 @@
       <c r="BK74" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="75" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM74" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>71</v>
       </c>
@@ -66670,8 +65985,11 @@
       <c r="BK75" s="6">
         <v>11</v>
       </c>
-    </row>
-    <row r="76" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM75" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>72</v>
       </c>
@@ -66810,8 +66128,11 @@
       <c r="BK76" s="6">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="77" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM76" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>313</v>
       </c>
@@ -66942,8 +66263,11 @@
       <c r="BK77" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM77" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>73</v>
       </c>
@@ -67072,8 +66396,11 @@
       <c r="BK78" s="6">
         <v>29</v>
       </c>
-    </row>
-    <row r="79" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM78" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>75</v>
       </c>
@@ -67202,8 +66529,11 @@
       <c r="BK79" s="6">
         <v>28</v>
       </c>
-    </row>
-    <row r="80" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM79" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>76</v>
       </c>
@@ -67356,8 +66686,11 @@
       <c r="BK80" s="6">
         <v>174</v>
       </c>
-    </row>
-    <row r="81" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM80" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>77</v>
       </c>
@@ -67494,8 +66827,11 @@
       <c r="BK81" s="6">
         <v>34</v>
       </c>
-    </row>
-    <row r="82" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM81" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>314</v>
       </c>
@@ -67626,8 +66962,11 @@
       <c r="BK82" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="83" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM82" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="83" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>78</v>
       </c>
@@ -67762,8 +67101,11 @@
       <c r="BK83" s="6">
         <v>130</v>
       </c>
-    </row>
-    <row r="84" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM83" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>79</v>
       </c>
@@ -67908,8 +67250,11 @@
       <c r="BK84" s="6">
         <v>139.1</v>
       </c>
-    </row>
-    <row r="85" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM84" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="85" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>80</v>
       </c>
@@ -68048,8 +67393,11 @@
       <c r="BK85" s="6">
         <v>78</v>
       </c>
-    </row>
-    <row r="86" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM85" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>81</v>
       </c>
@@ -68204,8 +67552,11 @@
       <c r="BK86" s="6">
         <v>73</v>
       </c>
-    </row>
-    <row r="87" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM86" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>82</v>
       </c>
@@ -68342,8 +67693,11 @@
       <c r="BK87" s="6">
         <v>131</v>
       </c>
-    </row>
-    <row r="88" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM87" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>83</v>
       </c>
@@ -68479,8 +67833,11 @@
       <c r="BK88" s="6">
         <v>141</v>
       </c>
-    </row>
-    <row r="89" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM88" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>84</v>
       </c>
@@ -68635,8 +67992,11 @@
       <c r="BK89" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="90" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM89" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="90" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>85</v>
       </c>
@@ -68765,8 +68125,11 @@
       <c r="BK90" s="6">
         <v>132</v>
       </c>
-    </row>
-    <row r="91" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM90" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="91" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>86</v>
       </c>
@@ -68903,8 +68266,11 @@
       <c r="BK91" s="6">
         <v>15</v>
       </c>
-    </row>
-    <row r="92" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM91" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="92" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>87</v>
       </c>
@@ -69033,8 +68399,11 @@
       <c r="BK92" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="93" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM92" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="93" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>88</v>
       </c>
@@ -69187,8 +68556,11 @@
       <c r="BK93" s="6">
         <v>59</v>
       </c>
-    </row>
-    <row r="94" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM93" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="94" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>89</v>
       </c>
@@ -69333,8 +68705,11 @@
       <c r="BK94" s="6">
         <v>59.299999237060497</v>
       </c>
-    </row>
-    <row r="95" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM94" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>90</v>
       </c>
@@ -69471,8 +68846,11 @@
       <c r="BK95" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="96" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM95" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="96" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>91</v>
       </c>
@@ -69617,8 +68995,11 @@
       <c r="BK96" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="97" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM96" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="97" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>92</v>
       </c>
@@ -69747,8 +69128,11 @@
       <c r="BK97" s="6">
         <v>76.599999999999994</v>
       </c>
-    </row>
-    <row r="98" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM97" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>93</v>
       </c>
@@ -69882,8 +69266,11 @@
       <c r="BK98" s="6">
         <v>68</v>
       </c>
-    </row>
-    <row r="99" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM98" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>94</v>
       </c>
@@ -70018,8 +69405,11 @@
       <c r="BK99" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="100" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM99" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>95</v>
       </c>
@@ -70126,8 +69516,11 @@
       <c r="BI100" s="6"/>
       <c r="BJ100" s="6"/>
       <c r="BK100" s="6"/>
-    </row>
-    <row r="101" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM100" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="101" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>96</v>
       </c>
@@ -70270,8 +69663,11 @@
       <c r="BK101" s="6">
         <v>95</v>
       </c>
-    </row>
-    <row r="102" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM101" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="102" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>97</v>
       </c>
@@ -70406,8 +69802,11 @@
       <c r="BK102" s="6">
         <v>22</v>
       </c>
-    </row>
-    <row r="103" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM102" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="103" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>98</v>
       </c>
@@ -70544,8 +69943,11 @@
       <c r="BK103" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="104" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM103" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>99</v>
       </c>
@@ -70690,8 +70092,11 @@
       <c r="BK104" s="6">
         <v>72</v>
       </c>
-    </row>
-    <row r="105" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM104" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="105" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>100</v>
       </c>
@@ -70828,8 +70233,11 @@
       <c r="BK105" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM105" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="106" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>101</v>
       </c>
@@ -70966,8 +70374,11 @@
       <c r="BK106" s="6">
         <v>18.7</v>
       </c>
-    </row>
-    <row r="107" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM106" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="107" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>102</v>
       </c>
@@ -71104,8 +70515,11 @@
       <c r="BK107" s="6">
         <v>30.549999237060501</v>
       </c>
-    </row>
-    <row r="108" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM107" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="108" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>103</v>
       </c>
@@ -71240,8 +70654,11 @@
       <c r="BK108" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="109" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM108" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>290</v>
       </c>
@@ -71350,8 +70767,11 @@
       <c r="BK109" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="110" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM109" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="110" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>104</v>
       </c>
@@ -71488,8 +70908,11 @@
       <c r="BK110" s="6">
         <v>37.9</v>
       </c>
-    </row>
-    <row r="111" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM110" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>105</v>
       </c>
@@ -71618,8 +71041,11 @@
       <c r="BK111" s="6">
         <v>64</v>
       </c>
-    </row>
-    <row r="112" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM111" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>106</v>
       </c>
@@ -71756,8 +71182,11 @@
       <c r="BK112" s="6">
         <v>45</v>
       </c>
-    </row>
-    <row r="113" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM112" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>107</v>
       </c>
@@ -71894,8 +71323,11 @@
       <c r="BK113" s="6">
         <v>69</v>
       </c>
-    </row>
-    <row r="114" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM113" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>108</v>
       </c>
@@ -72032,8 +71464,11 @@
       <c r="BK114" s="6">
         <v>15</v>
       </c>
-    </row>
-    <row r="115" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM114" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="115" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>109</v>
       </c>
@@ -72142,8 +71577,11 @@
       <c r="BI115" s="6"/>
       <c r="BJ115" s="6"/>
       <c r="BK115" s="6"/>
-    </row>
-    <row r="116" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM115" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>110</v>
       </c>
@@ -72282,8 +71720,11 @@
       <c r="BK116" s="6">
         <v>56</v>
       </c>
-    </row>
-    <row r="117" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM116" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="117" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>111</v>
       </c>
@@ -72422,8 +71863,11 @@
       <c r="BK117" s="6">
         <v>102</v>
       </c>
-    </row>
-    <row r="118" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM117" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="118" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>112</v>
       </c>
@@ -72560,8 +72004,11 @@
       <c r="BK118" s="6">
         <v>79</v>
       </c>
-    </row>
-    <row r="119" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM118" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="119" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>113</v>
       </c>
@@ -72700,8 +72147,11 @@
       <c r="BK119" s="6">
         <v>90</v>
       </c>
-    </row>
-    <row r="120" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM119" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="120" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>114</v>
       </c>
@@ -72840,8 +72290,11 @@
       <c r="BK120" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="121" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM120" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>115</v>
       </c>
@@ -72970,8 +72423,11 @@
       <c r="BK121" s="6">
         <v>71</v>
       </c>
-    </row>
-    <row r="122" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM121" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="122" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>116</v>
       </c>
@@ -73096,8 +72552,11 @@
       <c r="BK122" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="123" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM122" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>300</v>
       </c>
@@ -73206,8 +72665,11 @@
       <c r="BK123" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="124" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM123" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="124" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>117</v>
       </c>
@@ -73330,8 +72792,11 @@
       <c r="BK124" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="125" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM124" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
         <v>118</v>
       </c>
@@ -73468,8 +72933,11 @@
       <c r="BK125" s="6">
         <v>17.2</v>
       </c>
-    </row>
-    <row r="126" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM125" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="126" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
         <v>119</v>
       </c>
@@ -73608,8 +73076,11 @@
       <c r="BK126" s="6">
         <v>117</v>
       </c>
-    </row>
-    <row r="127" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM126" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>120</v>
       </c>
@@ -73746,8 +73217,11 @@
       <c r="BK127" s="6">
         <v>59</v>
       </c>
-    </row>
-    <row r="128" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM127" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="128" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>121</v>
       </c>
@@ -73884,8 +73358,11 @@
       <c r="BK128" s="6">
         <v>14</v>
       </c>
-    </row>
-    <row r="129" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM128" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="129" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
         <v>122</v>
       </c>
@@ -74008,8 +73485,11 @@
       <c r="BK129" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="130" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM129" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="130" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
         <v>123</v>
       </c>
@@ -74144,8 +73624,11 @@
       <c r="BK130" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="131" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM130" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="131" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>124</v>
       </c>
@@ -74282,8 +73765,11 @@
       <c r="BK131" s="6">
         <v>86</v>
       </c>
-    </row>
-    <row r="132" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM131" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="132" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
         <v>304</v>
       </c>
@@ -74392,8 +73878,11 @@
       <c r="BK132" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="133" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM132" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="133" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
         <v>125</v>
       </c>
@@ -74530,8 +74019,11 @@
       <c r="BK133" s="6">
         <v>29</v>
       </c>
-    </row>
-    <row r="134" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM133" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="134" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
         <v>301</v>
       </c>
@@ -74640,8 +74132,11 @@
       <c r="BK134" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="135" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM134" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
         <v>302</v>
       </c>
@@ -74750,8 +74245,11 @@
       <c r="BK135" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="136" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM135" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="136" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
         <v>126</v>
       </c>
@@ -74886,8 +74384,11 @@
       <c r="BK136" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="137" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM136" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="137" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
         <v>127</v>
       </c>
@@ -75012,8 +74513,11 @@
       <c r="BK137" s="6">
         <v>55</v>
       </c>
-    </row>
-    <row r="138" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM137" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="138" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
         <v>128</v>
       </c>
@@ -75150,8 +74654,11 @@
       <c r="BK138" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="139" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM138" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="139" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
         <v>129</v>
       </c>
@@ -75288,8 +74795,11 @@
       <c r="BK139" s="6">
         <v>79</v>
       </c>
-    </row>
-    <row r="140" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM139" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="140" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
         <v>130</v>
       </c>
@@ -75426,8 +74936,11 @@
       <c r="BK140" s="6">
         <v>43</v>
       </c>
-    </row>
-    <row r="141" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM140" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="141" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
         <v>131</v>
       </c>
@@ -75562,8 +75075,11 @@
       <c r="BK141" s="6">
         <v>55</v>
       </c>
-    </row>
-    <row r="142" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM141" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="142" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
         <v>132</v>
       </c>
@@ -75688,8 +75204,11 @@
       <c r="BK142" s="6">
         <v>82</v>
       </c>
-    </row>
-    <row r="143" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM142" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="143" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
         <v>133</v>
       </c>
@@ -75826,8 +75345,11 @@
       <c r="BK143" s="6">
         <v>47.9</v>
       </c>
-    </row>
-    <row r="144" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM143" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="144" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
         <v>134</v>
       </c>
@@ -75976,8 +75498,11 @@
       <c r="BK144" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="145" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM144" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="145" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
         <v>135</v>
       </c>
@@ -76102,8 +75627,11 @@
       <c r="BK145" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="146" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM145" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="146" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
         <v>136</v>
       </c>
@@ -76240,8 +75768,11 @@
       <c r="BK146" s="6">
         <v>51</v>
       </c>
-    </row>
-    <row r="147" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM146" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="147" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
         <v>137</v>
       </c>
@@ -76376,8 +75907,11 @@
       <c r="BK147" s="6">
         <v>53</v>
       </c>
-    </row>
-    <row r="148" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM147" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
         <v>138</v>
       </c>
@@ -76512,8 +76046,11 @@
       <c r="BK148" s="6">
         <v>51</v>
       </c>
-    </row>
-    <row r="149" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM148" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
         <v>139</v>
       </c>
@@ -76650,8 +76187,11 @@
       <c r="BK149" s="6">
         <v>198</v>
       </c>
-    </row>
-    <row r="150" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM149" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="150" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
         <v>140</v>
       </c>
@@ -76788,8 +76328,11 @@
       <c r="BK150" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="151" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM150" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="151" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
         <v>141</v>
       </c>
@@ -76914,8 +76457,11 @@
       <c r="BK151" s="6">
         <v>110</v>
       </c>
-    </row>
-    <row r="152" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM151" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
         <v>142</v>
       </c>
@@ -77056,8 +76602,11 @@
       <c r="BK152" s="6">
         <v>125</v>
       </c>
-    </row>
-    <row r="153" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM152" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="153" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
         <v>143</v>
       </c>
@@ -77202,8 +76751,11 @@
       <c r="BK153" s="6">
         <v>105</v>
       </c>
-    </row>
-    <row r="154" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM153" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="154" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
         <v>144</v>
       </c>
@@ -77338,8 +76890,11 @@
       <c r="BK154" s="6">
         <v>90</v>
       </c>
-    </row>
-    <row r="155" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM154" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="155" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
         <v>145</v>
       </c>
@@ -77462,8 +77017,11 @@
       <c r="BK155" s="6">
         <v>80</v>
       </c>
-    </row>
-    <row r="156" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM155" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="156" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
         <v>146</v>
       </c>
@@ -77600,8 +77158,11 @@
       <c r="BK156" s="6">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="157" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM156" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="157" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
         <v>147</v>
       </c>
@@ -77738,8 +77299,11 @@
       <c r="BK157" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="158" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM157" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="158" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
         <v>148</v>
       </c>
@@ -77884,8 +77448,11 @@
       <c r="BK158" s="6">
         <v>150</v>
       </c>
-    </row>
-    <row r="159" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM158" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="159" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
         <v>149</v>
       </c>
@@ -78024,8 +77591,11 @@
       <c r="BK159" s="6">
         <v>108</v>
       </c>
-    </row>
-    <row r="160" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM159" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="160" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
         <v>150</v>
       </c>
@@ -78162,8 +77732,11 @@
       <c r="BK160" s="6">
         <v>110</v>
       </c>
-    </row>
-    <row r="161" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM160" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="161" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
         <v>151</v>
       </c>
@@ -78300,8 +77873,11 @@
       <c r="BK161" s="6">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="162" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM161" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="162" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
         <v>152</v>
       </c>
@@ -78438,8 +78014,11 @@
       <c r="BK162" s="6">
         <v>85</v>
       </c>
-    </row>
-    <row r="163" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM162" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
         <v>153</v>
       </c>
@@ -78584,8 +78163,11 @@
       <c r="BK163" s="6">
         <v>180</v>
       </c>
-    </row>
-    <row r="164" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM163" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
         <v>154</v>
       </c>
@@ -78722,8 +78304,11 @@
       <c r="BK164" s="6">
         <v>66</v>
       </c>
-    </row>
-    <row r="165" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM164" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
         <v>155</v>
       </c>
@@ -78862,8 +78447,11 @@
       <c r="BK165" s="6">
         <v>193</v>
       </c>
-    </row>
-    <row r="166" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM165" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
         <v>303</v>
       </c>
@@ -78974,8 +78562,11 @@
       <c r="BK166" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="167" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM166" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="167" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
         <v>156</v>
       </c>
@@ -79120,8 +78711,11 @@
       <c r="BK167" s="6">
         <v>176</v>
       </c>
-    </row>
-    <row r="168" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM167" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
         <v>157</v>
       </c>
@@ -79268,8 +78862,11 @@
       <c r="BK168" s="6">
         <v>198</v>
       </c>
-    </row>
-    <row r="169" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM168" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="169" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
         <v>158</v>
       </c>
@@ -79394,8 +78991,11 @@
       <c r="BK169" s="6">
         <v>121.8</v>
       </c>
-    </row>
-    <row r="170" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM169" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="170" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
         <v>159</v>
       </c>
@@ -79534,8 +79134,11 @@
       <c r="BK170" s="6">
         <v>80</v>
       </c>
-    </row>
-    <row r="171" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM170" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
         <v>160</v>
       </c>
@@ -79680,8 +79283,11 @@
       <c r="BK171" s="6">
         <v>181</v>
       </c>
-    </row>
-    <row r="172" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM171" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="172" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
         <v>161</v>
       </c>
@@ -79818,8 +79424,11 @@
       <c r="BK172" s="6">
         <v>79.5</v>
       </c>
-    </row>
-    <row r="173" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM172" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="173" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
         <v>162</v>
       </c>
@@ -79954,8 +79563,11 @@
       <c r="BK173" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="174" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM173" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="174" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
         <v>163</v>
       </c>
@@ -80092,8 +79704,11 @@
       <c r="BK174" s="6">
         <v>61</v>
       </c>
-    </row>
-    <row r="175" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM174" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="175" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
         <v>164</v>
       </c>
@@ -80228,8 +79843,11 @@
       <c r="BK175" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="176" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM175" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="176" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
         <v>165</v>
       </c>
@@ -80364,8 +79982,11 @@
       <c r="BK176" s="6">
         <v>76</v>
       </c>
-    </row>
-    <row r="177" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM176" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="177" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
         <v>166</v>
       </c>
@@ -80502,8 +80123,11 @@
       <c r="BK177" s="6">
         <v>81</v>
       </c>
-    </row>
-    <row r="178" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM177" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="178" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
         <v>167</v>
       </c>
@@ -80638,8 +80262,11 @@
       <c r="BK178" s="6">
         <v>61</v>
       </c>
-    </row>
-    <row r="179" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM178" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="179" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
         <v>168</v>
       </c>
@@ -80776,8 +80403,11 @@
       <c r="BK179" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="180" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM179" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="180" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
         <v>169</v>
       </c>
@@ -80912,8 +80542,11 @@
       <c r="BK180" s="6">
         <v>150</v>
       </c>
-    </row>
-    <row r="181" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM180" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="181" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
         <v>170</v>
       </c>
@@ -81038,8 +80671,11 @@
       <c r="BK181" s="6">
         <v>64</v>
       </c>
-    </row>
-    <row r="182" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM181" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="182" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
         <v>171</v>
       </c>
@@ -81174,8 +80810,11 @@
       <c r="BK182" s="6">
         <v>15</v>
       </c>
-    </row>
-    <row r="183" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM182" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="183" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
         <v>172</v>
       </c>
@@ -81310,8 +80949,11 @@
       <c r="BK183" s="6">
         <v>14</v>
       </c>
-    </row>
-    <row r="184" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM183" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="184" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
         <v>173</v>
       </c>
@@ -81446,8 +81088,11 @@
       <c r="BK184" s="6">
         <v>115</v>
       </c>
-    </row>
-    <row r="185" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM184" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="185" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
         <v>174</v>
       </c>
@@ -81572,8 +81217,11 @@
       <c r="BK185" s="6">
         <v>140</v>
       </c>
-    </row>
-    <row r="186" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM185" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="186" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
         <v>175</v>
       </c>
@@ -81710,8 +81358,11 @@
       <c r="BK186" s="6">
         <v>145</v>
       </c>
-    </row>
-    <row r="187" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM186" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="187" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
         <v>176</v>
       </c>
@@ -81848,8 +81499,11 @@
       <c r="BK187" s="6">
         <v>12.8999996185303</v>
       </c>
-    </row>
-    <row r="188" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM187" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="188" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
         <v>177</v>
       </c>
@@ -81988,8 +81642,11 @@
       <c r="BK188" s="6">
         <v>89.9</v>
       </c>
-    </row>
-    <row r="189" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM188" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="189" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
         <v>178</v>
       </c>
@@ -82136,8 +81793,11 @@
       <c r="BK189" s="6">
         <v>156</v>
       </c>
-    </row>
-    <row r="190" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM189" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="190" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
         <v>179</v>
       </c>
@@ -82274,8 +81934,11 @@
       <c r="BK190" s="6">
         <v>135</v>
       </c>
-    </row>
-    <row r="191" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM190" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="191" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
         <v>180</v>
       </c>
@@ -82414,8 +82077,11 @@
       <c r="BK191" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="192" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM191" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="192" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
         <v>181</v>
       </c>
@@ -82554,8 +82220,11 @@
       <c r="BK192" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="193" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM192" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
         <v>182</v>
       </c>
@@ -82690,8 +82359,11 @@
       <c r="BK193" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="194" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM193" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="194" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
         <v>284</v>
       </c>
@@ -82818,8 +82490,11 @@
       <c r="BK194" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="195" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM194" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
         <v>183</v>
       </c>
@@ -82964,8 +82639,11 @@
       <c r="BK195" s="6">
         <v>136</v>
       </c>
-    </row>
-    <row r="196" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM195" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="196" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
         <v>184</v>
       </c>
@@ -83112,8 +82790,11 @@
       <c r="BK196" s="6">
         <v>166</v>
       </c>
-    </row>
-    <row r="197" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM196" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="197" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
         <v>185</v>
       </c>
@@ -83250,8 +82931,11 @@
       <c r="BK197" s="6">
         <v>22</v>
       </c>
-    </row>
-    <row r="198" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM197" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="198" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
         <v>186</v>
       </c>
@@ -83384,8 +83068,11 @@
       <c r="BK198" s="6">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="199" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM198" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="199" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
         <v>187</v>
       </c>
@@ -83522,8 +83209,11 @@
       <c r="BK199" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="200" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM199" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="200" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
         <v>188</v>
       </c>
@@ -83648,8 +83338,11 @@
       <c r="BK200" s="6">
         <v>101</v>
       </c>
-    </row>
-    <row r="201" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM200" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="201" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
         <v>189</v>
       </c>
@@ -83788,8 +83481,11 @@
       <c r="BK201" s="6">
         <v>113.5</v>
       </c>
-    </row>
-    <row r="202" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM201" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="202" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
         <v>190</v>
       </c>
@@ -83930,8 +83626,11 @@
       <c r="BK202" s="6">
         <v>180</v>
       </c>
-    </row>
-    <row r="203" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM202" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="203" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
         <v>191</v>
       </c>
@@ -84068,8 +83767,11 @@
       <c r="BK203" s="6">
         <v>74</v>
       </c>
-    </row>
-    <row r="204" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM203" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="204" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
         <v>192</v>
       </c>
@@ -84206,8 +83908,11 @@
       <c r="BK204" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="205" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM204" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="205" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
         <v>308</v>
       </c>
@@ -84316,8 +84021,11 @@
       <c r="BK205" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="206" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM205" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="206" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
         <v>193</v>
       </c>
@@ -84452,8 +84160,11 @@
       <c r="BK206" s="6">
         <v>5.9</v>
       </c>
-    </row>
-    <row r="207" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM206" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="207" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
         <v>281</v>
       </c>
@@ -84580,8 +84291,11 @@
       <c r="BK207" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="208" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM207" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="208" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
         <v>194</v>
       </c>
@@ -84716,8 +84430,11 @@
       <c r="BK208" s="6">
         <v>69</v>
       </c>
-    </row>
-    <row r="209" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM208" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
         <v>195</v>
       </c>
@@ -84852,8 +84569,11 @@
       <c r="BK209" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="210" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM209" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="210" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
         <v>196</v>
       </c>
@@ -84990,8 +84710,11 @@
       <c r="BK210" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="211" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM210" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="211" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
         <v>197</v>
       </c>
@@ -85126,8 +84849,11 @@
       <c r="BK211" s="6">
         <v>54</v>
       </c>
-    </row>
-    <row r="212" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM211" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="212" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
         <v>198</v>
       </c>
@@ -85264,8 +84990,11 @@
       <c r="BK212" s="6">
         <v>39</v>
       </c>
-    </row>
-    <row r="213" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM212" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="213" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
         <v>199</v>
       </c>
@@ -85402,8 +85131,11 @@
       <c r="BK213" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="214" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM213" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="214" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
         <v>200</v>
       </c>
@@ -85539,8 +85271,11 @@
       <c r="BK214" s="6">
         <v>138.39999389648401</v>
       </c>
-    </row>
-    <row r="215" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM214" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="215" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
         <v>201</v>
       </c>
@@ -85679,8 +85414,11 @@
       <c r="BK215" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="216" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM215" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="216" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
         <v>305</v>
       </c>
@@ -85789,8 +85527,11 @@
       <c r="BK216" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="217" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM216" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="217" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
         <v>202</v>
       </c>
@@ -85929,8 +85670,11 @@
       <c r="BK217" s="6">
         <v>63</v>
       </c>
-    </row>
-    <row r="218" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM217" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="218" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
         <v>306</v>
       </c>
@@ -86039,8 +85783,11 @@
       <c r="BK218" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="219" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM218" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="219" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
         <v>203</v>
       </c>
@@ -86177,8 +85924,11 @@
       <c r="BK219" s="6">
         <v>58</v>
       </c>
-    </row>
-    <row r="220" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM219" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="220" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
         <v>204</v>
       </c>
@@ -86317,8 +86067,11 @@
       <c r="BK220" s="6">
         <v>37</v>
       </c>
-    </row>
-    <row r="221" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM220" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="221" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
         <v>205</v>
       </c>
@@ -86457,8 +86210,11 @@
       <c r="BK221" s="6">
         <v>54</v>
       </c>
-    </row>
-    <row r="222" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM221" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="222" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
         <v>206</v>
       </c>
@@ -86611,8 +86367,11 @@
       <c r="BK222" s="6">
         <v>99</v>
       </c>
-    </row>
-    <row r="223" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM222" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="223" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
         <v>208</v>
       </c>
@@ -86753,8 +86512,11 @@
       <c r="BK223" s="6">
         <v>82</v>
       </c>
-    </row>
-    <row r="224" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM223" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="224" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
         <v>209</v>
       </c>
@@ -86879,8 +86641,11 @@
       <c r="BK224" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="225" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM224" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="225" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
         <v>311</v>
       </c>
@@ -87007,8 +86772,11 @@
       <c r="BK225" s="6">
         <v>47</v>
       </c>
-    </row>
-    <row r="226" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM225" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="226" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
         <v>210</v>
       </c>
@@ -87153,8 +86921,11 @@
       <c r="BK226" s="6">
         <v>120</v>
       </c>
-    </row>
-    <row r="227" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM226" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="227" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
         <v>211</v>
       </c>
@@ -87289,8 +87060,11 @@
       <c r="BK227" s="6">
         <v>80</v>
       </c>
-    </row>
-    <row r="228" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM227" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="228" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
         <v>213</v>
       </c>
@@ -87415,8 +87189,11 @@
       <c r="BK228" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="229" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM228" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="229" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
         <v>214</v>
       </c>
@@ -87553,8 +87330,11 @@
       <c r="BK229" s="6">
         <v>54</v>
       </c>
-    </row>
-    <row r="230" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM229" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="230" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
         <v>215</v>
       </c>
@@ -87691,8 +87471,11 @@
       <c r="BK230" s="6">
         <v>46</v>
       </c>
-    </row>
-    <row r="231" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM230" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="231" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
         <v>216</v>
       </c>
@@ -87827,8 +87610,11 @@
       <c r="BK231" s="6">
         <v>39.5</v>
       </c>
-    </row>
-    <row r="232" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM231" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="232" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
         <v>287</v>
       </c>
@@ -87937,8 +87723,11 @@
       <c r="BK232" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="233" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM232" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="233" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
         <v>217</v>
       </c>
@@ -88077,8 +87866,11 @@
       <c r="BK233" s="6">
         <v>125</v>
       </c>
-    </row>
-    <row r="234" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM233" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="234" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
         <v>218</v>
       </c>
@@ -88217,8 +88009,11 @@
       <c r="BK234" s="6">
         <v>132</v>
       </c>
-    </row>
-    <row r="235" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM234" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="235" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
         <v>219</v>
       </c>
@@ -88353,8 +88148,11 @@
       <c r="BK235" s="6">
         <v>86</v>
       </c>
-    </row>
-    <row r="236" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM235" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="236" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
         <v>220</v>
       </c>
@@ -88479,8 +88277,11 @@
       <c r="BK236" s="6">
         <v>160</v>
       </c>
-    </row>
-    <row r="237" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM236" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="237" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
         <v>221</v>
       </c>
@@ -88619,8 +88420,11 @@
       <c r="BK237" s="6">
         <v>153</v>
       </c>
-    </row>
-    <row r="238" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM237" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="238" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
         <v>222</v>
       </c>
@@ -88745,8 +88549,11 @@
       <c r="BK238" s="6">
         <v>108</v>
       </c>
-    </row>
-    <row r="239" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM238" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="239" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
         <v>223</v>
       </c>
@@ -88883,8 +88690,11 @@
       <c r="BK239" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="240" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM239" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="240" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
         <v>224</v>
       </c>
@@ -89021,8 +88831,11 @@
       <c r="BK240" s="6">
         <v>50.3</v>
       </c>
-    </row>
-    <row r="241" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM240" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="241" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
         <v>225</v>
       </c>
@@ -89159,8 +88972,11 @@
       <c r="BK241" s="6">
         <v>52.5</v>
       </c>
-    </row>
-    <row r="242" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM241" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="242" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
         <v>286</v>
       </c>
@@ -89291,8 +89107,11 @@
       <c r="BK242" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="243" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM242" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="243" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
         <v>227</v>
       </c>
@@ -89419,8 +89238,11 @@
       <c r="BK243" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="244" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM243" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
         <v>228</v>
       </c>
@@ -89547,8 +89369,11 @@
       <c r="BK244" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="245" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM244" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="245" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
         <v>229</v>
       </c>
@@ -89685,8 +89510,11 @@
       <c r="BK245" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="246" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM245" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="246" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
         <v>231</v>
       </c>
@@ -89823,8 +89651,11 @@
       <c r="BK246" s="6">
         <v>30</v>
       </c>
-    </row>
-    <row r="247" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM246" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="247" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
         <v>232</v>
       </c>
@@ -89961,8 +89792,11 @@
       <c r="BK247" s="6">
         <v>43</v>
       </c>
-    </row>
-    <row r="248" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM247" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="248" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
         <v>233</v>
       </c>
@@ -90087,8 +89921,11 @@
       <c r="BK248" s="6">
         <v>22</v>
       </c>
-    </row>
-    <row r="249" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM248" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="249" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
         <v>230</v>
       </c>
@@ -90225,8 +90062,11 @@
       <c r="BK249" s="6">
         <v>70</v>
       </c>
-    </row>
-    <row r="250" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM249" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="250" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
         <v>234</v>
       </c>
@@ -90363,8 +90203,11 @@
       <c r="BK250" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="251" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM250" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="251" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
         <v>235</v>
       </c>
@@ -90501,8 +90344,11 @@
       <c r="BK251" s="6">
         <v>34</v>
       </c>
-    </row>
-    <row r="252" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM251" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="252" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
         <v>236</v>
       </c>
@@ -90609,8 +90455,11 @@
       <c r="BI252" s="6"/>
       <c r="BJ252" s="6"/>
       <c r="BK252" s="6"/>
-    </row>
-    <row r="253" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM252" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="253" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
         <v>237</v>
       </c>
@@ -90747,8 +90596,11 @@
       <c r="BK253" s="6">
         <v>62</v>
       </c>
-    </row>
-    <row r="254" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM253" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="254" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
         <v>238</v>
       </c>
@@ -90893,8 +90745,11 @@
       <c r="BK254" s="6">
         <v>105</v>
       </c>
-    </row>
-    <row r="255" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM254" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="255" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
         <v>239</v>
       </c>
@@ -91033,8 +90888,11 @@
       <c r="BK255" s="6">
         <v>50</v>
       </c>
-    </row>
-    <row r="256" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM255" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="256" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
         <v>240</v>
       </c>
@@ -91177,8 +91035,11 @@
       <c r="BK256" s="6">
         <v>112</v>
       </c>
-    </row>
-    <row r="257" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM256" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="257" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
         <v>241</v>
       </c>
@@ -91315,8 +91176,11 @@
       <c r="BK257" s="6">
         <v>80</v>
       </c>
-    </row>
-    <row r="258" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM257" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="258" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
         <v>242</v>
       </c>
@@ -91451,8 +91315,11 @@
       <c r="BK258" s="6">
         <v>52</v>
       </c>
-    </row>
-    <row r="259" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM258" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="259" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
         <v>243</v>
       </c>
@@ -91577,8 +91444,11 @@
       <c r="BK259" s="6">
         <v>85.5</v>
       </c>
-    </row>
-    <row r="260" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM259" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="260" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
         <v>244</v>
       </c>
@@ -91723,8 +91593,11 @@
       <c r="BK260" s="6">
         <v>115</v>
       </c>
-    </row>
-    <row r="261" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM260" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="261" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
         <v>283</v>
       </c>
@@ -91829,8 +91702,11 @@
       <c r="BI261" s="6"/>
       <c r="BJ261" s="6"/>
       <c r="BK261" s="6"/>
-    </row>
-    <row r="262" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM261" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="262" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
         <v>246</v>
       </c>
@@ -91969,8 +91845,11 @@
       <c r="BK262" s="6">
         <v>58</v>
       </c>
-    </row>
-    <row r="263" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM262" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="263" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
         <v>247</v>
       </c>
@@ -92095,8 +91974,11 @@
       <c r="BK263" s="6">
         <v>20</v>
       </c>
-    </row>
-    <row r="264" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM263" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="264" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
         <v>248</v>
       </c>
@@ -92233,8 +92115,11 @@
       <c r="BK264" s="6">
         <v>20.010000000000002</v>
       </c>
-    </row>
-    <row r="265" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM264" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="265" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
         <v>249</v>
       </c>
@@ -92373,8 +92258,11 @@
       <c r="BK265" s="6">
         <v>86.5</v>
       </c>
-    </row>
-    <row r="266" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM265" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="266" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
         <v>250</v>
       </c>
@@ -92513,8 +92401,11 @@
       <c r="BK266" s="6">
         <v>63</v>
       </c>
-    </row>
-    <row r="267" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM266" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="267" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
         <v>251</v>
       </c>
@@ -92626,8 +92517,11 @@
       <c r="BI267" s="6"/>
       <c r="BJ267" s="6"/>
       <c r="BK267" s="6"/>
-    </row>
-    <row r="268" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM267" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="268" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
         <v>252</v>
       </c>
@@ -92772,8 +92666,11 @@
       <c r="BK268" s="6">
         <v>120</v>
       </c>
-    </row>
-    <row r="269" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM268" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="269" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
         <v>253</v>
       </c>
@@ -92918,8 +92815,11 @@
       <c r="BK269" s="6">
         <v>152</v>
       </c>
-    </row>
-    <row r="270" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM269" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="270" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
         <v>254</v>
       </c>
@@ -93026,8 +92926,11 @@
       <c r="BI270" s="6"/>
       <c r="BJ270" s="6"/>
       <c r="BK270" s="6"/>
-    </row>
-    <row r="271" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM270" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="271" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
         <v>255</v>
       </c>
@@ -93152,8 +93055,11 @@
       <c r="BK271" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="272" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM271" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="272" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
         <v>256</v>
       </c>
@@ -93298,8 +93204,11 @@
       <c r="BK272" s="6">
         <v>124</v>
       </c>
-    </row>
-    <row r="273" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM272" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="273" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
         <v>257</v>
       </c>
@@ -93436,8 +93345,11 @@
       <c r="BK273" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="274" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM273" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="274" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
         <v>310</v>
       </c>
@@ -93546,8 +93458,11 @@
       <c r="BK274" s="6">
         <v>37</v>
       </c>
-    </row>
-    <row r="275" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM274" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="275" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
         <v>258</v>
       </c>
@@ -93672,8 +93587,11 @@
       <c r="BK275" s="6">
         <v>92.5</v>
       </c>
-    </row>
-    <row r="276" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM275" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="276" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
         <v>285</v>
       </c>
@@ -93800,8 +93718,11 @@
       <c r="BK276" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="277" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM276" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="277" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
         <v>226</v>
       </c>
@@ -93936,8 +93857,11 @@
       <c r="BK277" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="278" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM277" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="278" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
         <v>259</v>
       </c>
@@ -94074,8 +93998,11 @@
       <c r="BK278" s="6">
         <v>45</v>
       </c>
-    </row>
-    <row r="279" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM278" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="279" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
         <v>316</v>
       </c>
@@ -94202,8 +94129,11 @@
       <c r="BK279" s="6">
         <v>13</v>
       </c>
-    </row>
-    <row r="280" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM279" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="280" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
         <v>260</v>
       </c>
@@ -94340,8 +94270,11 @@
       <c r="BK280" s="6">
         <v>89.9</v>
       </c>
-    </row>
-    <row r="281" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM280" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="281" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
         <v>315</v>
       </c>
@@ -94468,8 +94401,11 @@
       <c r="BK281" s="6">
         <v>22</v>
       </c>
-    </row>
-    <row r="282" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM281" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="282" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
         <v>261</v>
       </c>
@@ -94606,8 +94542,11 @@
       <c r="BK282" s="6">
         <v>150</v>
       </c>
-    </row>
-    <row r="283" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM282" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="283" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
         <v>262</v>
       </c>
@@ -94744,8 +94683,11 @@
       <c r="BK283" s="6">
         <v>150</v>
       </c>
-    </row>
-    <row r="284" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM283" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="284" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
         <v>263</v>
       </c>
@@ -94880,8 +94822,11 @@
       <c r="BK284" s="6">
         <v>134</v>
       </c>
-    </row>
-    <row r="285" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM284" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="285" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
         <v>317</v>
       </c>
@@ -94998,8 +94943,11 @@
       <c r="BK285" s="6">
         <v>18</v>
       </c>
-    </row>
-    <row r="286" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM285" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="286" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
         <v>264</v>
       </c>
@@ -95134,8 +95082,11 @@
       <c r="BK286" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="287" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM286" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="287" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
         <v>265</v>
       </c>
@@ -95270,8 +95221,11 @@
       <c r="BK287" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="288" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM287" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="288" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
         <v>266</v>
       </c>
@@ -95408,8 +95362,11 @@
       <c r="BK288" s="6">
         <v>112</v>
       </c>
-    </row>
-    <row r="289" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM288" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="289" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
         <v>267</v>
       </c>
@@ -95544,8 +95501,11 @@
       <c r="BK289" s="6">
         <v>20</v>
       </c>
-    </row>
-    <row r="290" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM289" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="290" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
         <v>269</v>
       </c>
@@ -95670,8 +95630,11 @@
       <c r="BK290" s="6">
         <v>193</v>
       </c>
-    </row>
-    <row r="291" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM290" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="291" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
         <v>270</v>
       </c>
@@ -95806,8 +95769,11 @@
       <c r="BK291" s="6">
         <v>178</v>
       </c>
-    </row>
-    <row r="292" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM291" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="292" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
         <v>271</v>
       </c>
@@ -95944,8 +95910,11 @@
       <c r="BK292" s="6">
         <v>189</v>
       </c>
-    </row>
-    <row r="293" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM292" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="293" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
         <v>272</v>
       </c>
@@ -96080,8 +96049,11 @@
       <c r="BK293" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="294" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM293" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="294" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
         <v>212</v>
       </c>
@@ -96188,8 +96160,11 @@
       <c r="BI294" s="6"/>
       <c r="BJ294" s="6"/>
       <c r="BK294" s="6"/>
-    </row>
-    <row r="295" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM294" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="295" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
         <v>274</v>
       </c>
@@ -96324,8 +96299,11 @@
       <c r="BK295" s="6">
         <v>14.6000003814697</v>
       </c>
-    </row>
-    <row r="296" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM295" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="296" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
         <v>275</v>
       </c>
@@ -96460,8 +96438,11 @@
       <c r="BK296" s="6">
         <v>76</v>
       </c>
-    </row>
-    <row r="297" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM296" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="297" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
         <v>276</v>
       </c>
@@ -96596,8 +96577,11 @@
       <c r="BK297" s="6">
         <v>26.9</v>
       </c>
-    </row>
-    <row r="298" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM297" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="298" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
         <v>277</v>
       </c>
@@ -96734,8 +96718,11 @@
       <c r="BK298" s="6">
         <v>35</v>
       </c>
-    </row>
-    <row r="299" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM298" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="299" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
         <v>278</v>
       </c>
@@ -96860,8 +96847,11 @@
       <c r="BK299" s="6" t="e">
         <v>#NUM!</v>
       </c>
-    </row>
-    <row r="300" spans="1:63" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="BM299" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="300" spans="1:65" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
         <v>309</v>
       </c>
@@ -96972,6 +96962,14 @@
       <c r="BK300" s="6" t="s">
         <v>1414</v>
       </c>
+      <c r="BM300" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="301" spans="1:65" x14ac:dyDescent="0.25">
+      <c r="BM301" t="s">
+        <v>2223</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="AC1:AC300" xr:uid="{00000000-0001-0000-0100-000000000000}"/>

--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{572C582A-EEF0-4D97-BB9E-96A60D4F4A3F}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D35ADC4-AD9E-4400-91C2-0CA214A1A8D0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19616" uniqueCount="2268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19916" uniqueCount="2269">
   <si>
     <t>ID</t>
   </si>
@@ -6856,6 +6856,9 @@
   </si>
   <si>
     <t>Nanny Berry</t>
+  </si>
+  <si>
+    <t>pink</t>
   </si>
 </sst>
 </file>
@@ -7771,7 +7774,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O301"/>
+  <dimension ref="A1:P301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
@@ -7787,7 +7790,7 @@
     <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7833,8 +7836,11 @@
       <c r="O1" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="7" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7880,8 +7886,11 @@
       <c r="O2">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P2" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7927,8 +7936,11 @@
       <c r="O3">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P3" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7971,8 +7983,11 @@
       <c r="O4">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8018,8 +8033,11 @@
       <c r="O5">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>318</v>
       </c>
@@ -8059,8 +8077,11 @@
       <c r="M6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P6" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8100,8 +8121,11 @@
       <c r="M7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P7" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8147,8 +8171,11 @@
       <c r="O8">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P8" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8188,8 +8215,11 @@
       <c r="M9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>282</v>
       </c>
@@ -8229,8 +8259,11 @@
       <c r="M10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8276,8 +8309,11 @@
       <c r="O11">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -8323,8 +8359,11 @@
       <c r="O12">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -8370,8 +8409,11 @@
       <c r="O13">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -8417,8 +8459,11 @@
       <c r="O14">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P14" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -8464,8 +8509,11 @@
       <c r="O15">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P15" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -8508,8 +8556,11 @@
       <c r="O16">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -8555,8 +8606,11 @@
       <c r="O17">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -8602,8 +8656,11 @@
       <c r="O18">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -8649,8 +8706,11 @@
       <c r="O19">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -8696,8 +8756,11 @@
       <c r="O20">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P20" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -8743,8 +8806,11 @@
       <c r="O21">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P21" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -8790,8 +8856,11 @@
       <c r="O22">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -8837,8 +8906,11 @@
       <c r="O23">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -8881,8 +8953,11 @@
       <c r="O24">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>312</v>
       </c>
@@ -8925,8 +9000,11 @@
       <c r="O25">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -8972,8 +9050,11 @@
       <c r="O26">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -9019,8 +9100,11 @@
       <c r="O27">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -9066,8 +9150,11 @@
       <c r="O28">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -9113,8 +9200,11 @@
       <c r="O29">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -9160,8 +9250,11 @@
       <c r="O30">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -9204,8 +9297,11 @@
       <c r="O31">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -9251,8 +9347,11 @@
       <c r="O32">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -9298,8 +9397,11 @@
       <c r="O33">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -9345,8 +9447,11 @@
       <c r="O34">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P34" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -9392,8 +9497,11 @@
       <c r="O35">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -9439,8 +9547,11 @@
       <c r="O36">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -9483,8 +9594,11 @@
       <c r="O37">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P37" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -9530,8 +9644,11 @@
       <c r="O38">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P38" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>319</v>
       </c>
@@ -9574,8 +9691,11 @@
       <c r="O39">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P39" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>320</v>
       </c>
@@ -9612,8 +9732,11 @@
       <c r="M40" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P40" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>36</v>
       </c>
@@ -9659,8 +9782,11 @@
       <c r="O41">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -9706,8 +9832,11 @@
       <c r="O42">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P42" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>38</v>
       </c>
@@ -9753,8 +9882,11 @@
       <c r="O43">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P43" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>39</v>
       </c>
@@ -9800,8 +9932,11 @@
       <c r="O44">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -9844,8 +9979,11 @@
       <c r="O45">
         <v>0.76</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P45" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>41</v>
       </c>
@@ -9891,8 +10029,11 @@
       <c r="O46">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P46" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>42</v>
       </c>
@@ -9938,8 +10079,11 @@
       <c r="O47">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P47" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>43</v>
       </c>
@@ -9985,8 +10129,11 @@
       <c r="O48">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P48" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -10029,8 +10176,11 @@
       <c r="O49">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P49" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>307</v>
       </c>
@@ -10070,8 +10220,11 @@
       <c r="M50" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P50" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>45</v>
       </c>
@@ -10117,8 +10270,11 @@
       <c r="O51">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P51" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>46</v>
       </c>
@@ -10164,8 +10320,11 @@
       <c r="O52">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P52" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>47</v>
       </c>
@@ -10211,8 +10370,11 @@
       <c r="O53">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P53" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>48</v>
       </c>
@@ -10258,8 +10420,11 @@
       <c r="O54">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P54" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>49</v>
       </c>
@@ -10305,8 +10470,11 @@
       <c r="O55">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P55" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>50</v>
       </c>
@@ -10352,8 +10520,11 @@
       <c r="O56">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P56" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>51</v>
       </c>
@@ -10399,8 +10570,11 @@
       <c r="O57">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P57" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>52</v>
       </c>
@@ -10446,8 +10620,11 @@
       <c r="O58">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P58" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>53</v>
       </c>
@@ -10493,8 +10670,11 @@
       <c r="O59">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P59" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>54</v>
       </c>
@@ -10540,8 +10720,11 @@
       <c r="O60">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P60" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>55</v>
       </c>
@@ -10587,8 +10770,11 @@
       <c r="O61">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P61" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>56</v>
       </c>
@@ -10634,8 +10820,11 @@
       <c r="O62">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P62" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>57</v>
       </c>
@@ -10681,8 +10870,11 @@
       <c r="O63">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P63" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>58</v>
       </c>
@@ -10722,8 +10914,11 @@
       <c r="M64" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P64" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>59</v>
       </c>
@@ -10766,8 +10961,11 @@
       <c r="O65">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P65" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>60</v>
       </c>
@@ -10813,8 +11011,11 @@
       <c r="O66">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>61</v>
       </c>
@@ -10860,8 +11061,11 @@
       <c r="O67">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P67" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>62</v>
       </c>
@@ -10907,8 +11111,11 @@
       <c r="O68">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P68" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
@@ -10954,8 +11161,11 @@
       <c r="O69">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P69" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
@@ -11001,8 +11211,11 @@
       <c r="O70">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P70" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
@@ -11048,8 +11261,11 @@
       <c r="O71">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P71" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>67</v>
       </c>
@@ -11089,8 +11305,11 @@
       <c r="M72" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P72" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
@@ -11136,8 +11355,11 @@
       <c r="O73">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P73" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
@@ -11183,8 +11405,11 @@
       <c r="O74">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P74" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>70</v>
       </c>
@@ -11230,8 +11455,11 @@
       <c r="O75">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P75" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>289</v>
       </c>
@@ -11271,8 +11499,11 @@
       <c r="M76" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P76" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>71</v>
       </c>
@@ -11318,8 +11549,11 @@
       <c r="O77">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P77" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>72</v>
       </c>
@@ -11365,8 +11599,11 @@
       <c r="O78">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P78" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>313</v>
       </c>
@@ -11406,8 +11643,11 @@
       <c r="M79" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P79" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>73</v>
       </c>
@@ -11450,8 +11690,11 @@
       <c r="O80">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P80" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>75</v>
       </c>
@@ -11494,8 +11737,11 @@
       <c r="O81">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P81" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>76</v>
       </c>
@@ -11541,8 +11787,11 @@
       <c r="O82">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P82" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>77</v>
       </c>
@@ -11588,8 +11837,11 @@
       <c r="O83">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P83" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>314</v>
       </c>
@@ -11632,8 +11884,11 @@
       <c r="N84">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P84" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>78</v>
       </c>
@@ -11679,8 +11934,11 @@
       <c r="O85">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P85" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>79</v>
       </c>
@@ -11726,8 +11984,11 @@
       <c r="O86">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P86" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>80</v>
       </c>
@@ -11773,8 +12034,11 @@
       <c r="O87">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P87" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>81</v>
       </c>
@@ -11820,8 +12084,11 @@
       <c r="O88">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P88" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>82</v>
       </c>
@@ -11867,8 +12134,11 @@
       <c r="O89">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P89" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>83</v>
       </c>
@@ -11914,8 +12184,11 @@
       <c r="O90">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P90" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>84</v>
       </c>
@@ -11961,8 +12234,11 @@
       <c r="O91">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P91" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>85</v>
       </c>
@@ -12005,8 +12281,11 @@
       <c r="O92">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P92" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>86</v>
       </c>
@@ -12052,8 +12331,11 @@
       <c r="O93">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P93" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>87</v>
       </c>
@@ -12096,8 +12378,11 @@
       <c r="O94">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P94" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>88</v>
       </c>
@@ -12143,8 +12428,11 @@
       <c r="O95">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P95" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>89</v>
       </c>
@@ -12190,8 +12478,11 @@
       <c r="O96">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P96" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>90</v>
       </c>
@@ -12237,8 +12528,11 @@
       <c r="O97">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P97" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>91</v>
       </c>
@@ -12284,8 +12578,11 @@
       <c r="O98">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P98" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>92</v>
       </c>
@@ -12328,8 +12625,11 @@
       <c r="O99">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P99" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>93</v>
       </c>
@@ -12375,8 +12675,11 @@
       <c r="O100">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P100" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>94</v>
       </c>
@@ -12422,8 +12725,11 @@
       <c r="O101">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P101" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>95</v>
       </c>
@@ -12463,8 +12769,11 @@
       <c r="M102" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P102" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>96</v>
       </c>
@@ -12510,8 +12819,11 @@
       <c r="O103">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P103" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>97</v>
       </c>
@@ -12557,8 +12869,11 @@
       <c r="O104">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P104" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>98</v>
       </c>
@@ -12604,8 +12919,11 @@
       <c r="O105">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P105" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>99</v>
       </c>
@@ -12651,8 +12969,11 @@
       <c r="O106">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P106" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>100</v>
       </c>
@@ -12698,8 +13019,11 @@
       <c r="O107">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P107" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>101</v>
       </c>
@@ -12745,8 +13069,11 @@
       <c r="O108">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P108" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>102</v>
       </c>
@@ -12792,8 +13119,11 @@
       <c r="O109">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P109" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>103</v>
       </c>
@@ -12839,8 +13169,11 @@
       <c r="O110">
         <v>0.89</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P110" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>290</v>
       </c>
@@ -12880,8 +13213,11 @@
       <c r="M111" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P111" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>104</v>
       </c>
@@ -12927,8 +13263,11 @@
       <c r="O112">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P112" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>105</v>
       </c>
@@ -12971,8 +13310,11 @@
       <c r="O113">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P113" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>106</v>
       </c>
@@ -13018,8 +13360,11 @@
       <c r="O114">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P114" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>107</v>
       </c>
@@ -13065,8 +13410,11 @@
       <c r="O115">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P115" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>108</v>
       </c>
@@ -13112,8 +13460,11 @@
       <c r="O116">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P116" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>109</v>
       </c>
@@ -13150,8 +13501,11 @@
       <c r="M117" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P117" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>110</v>
       </c>
@@ -13197,8 +13551,11 @@
       <c r="O118">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P118" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>111</v>
       </c>
@@ -13244,8 +13601,11 @@
       <c r="O119">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P119" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>112</v>
       </c>
@@ -13291,8 +13651,11 @@
       <c r="O120">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P120" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>113</v>
       </c>
@@ -13338,8 +13701,11 @@
       <c r="O121">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P121" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>114</v>
       </c>
@@ -13385,8 +13751,11 @@
       <c r="O122">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P122" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>115</v>
       </c>
@@ -13429,8 +13798,11 @@
       <c r="O123">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P123" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>116</v>
       </c>
@@ -13470,8 +13842,11 @@
       <c r="M124" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P124" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>300</v>
       </c>
@@ -13511,8 +13886,11 @@
       <c r="M125" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P125" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>117</v>
       </c>
@@ -13552,8 +13930,11 @@
       <c r="M126" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P126" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>118</v>
       </c>
@@ -13599,8 +13980,11 @@
       <c r="O127">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P127" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>119</v>
       </c>
@@ -13646,8 +14030,11 @@
       <c r="O128">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P128" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>120</v>
       </c>
@@ -13693,8 +14080,11 @@
       <c r="O129">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P129" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>121</v>
       </c>
@@ -13740,8 +14130,11 @@
       <c r="O130">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P130" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>122</v>
       </c>
@@ -13781,8 +14174,11 @@
       <c r="M131" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P131" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>123</v>
       </c>
@@ -13828,8 +14224,11 @@
       <c r="O132">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P132" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>124</v>
       </c>
@@ -13875,8 +14274,11 @@
       <c r="O133">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P133" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>304</v>
       </c>
@@ -13916,8 +14318,11 @@
       <c r="M134" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P134" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>125</v>
       </c>
@@ -13963,8 +14368,11 @@
       <c r="O135">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P135" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>301</v>
       </c>
@@ -14004,8 +14412,11 @@
       <c r="M136" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P136" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>302</v>
       </c>
@@ -14045,8 +14456,11 @@
       <c r="M137" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P137" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126</v>
       </c>
@@ -14092,8 +14506,11 @@
       <c r="O138">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P138" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>127</v>
       </c>
@@ -14136,8 +14553,11 @@
       <c r="O139">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P139" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>128</v>
       </c>
@@ -14183,8 +14603,11 @@
       <c r="O140">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P140" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>129</v>
       </c>
@@ -14230,8 +14653,11 @@
       <c r="O141">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P141" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>130</v>
       </c>
@@ -14277,8 +14703,11 @@
       <c r="O142">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P142" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>131</v>
       </c>
@@ -14324,8 +14753,11 @@
       <c r="O143">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P143" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>132</v>
       </c>
@@ -14368,8 +14800,11 @@
       <c r="O144">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P144" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>133</v>
       </c>
@@ -14415,8 +14850,11 @@
       <c r="O145">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P145" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>134</v>
       </c>
@@ -14462,8 +14900,11 @@
       <c r="O146">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P146" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>135</v>
       </c>
@@ -14506,8 +14947,11 @@
       <c r="O147">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P147" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>136</v>
       </c>
@@ -14553,8 +14997,11 @@
       <c r="O148">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P148" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>137</v>
       </c>
@@ -14600,8 +15047,11 @@
       <c r="O149">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P149" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>138</v>
       </c>
@@ -14647,8 +15097,11 @@
       <c r="O150">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P150" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>139</v>
       </c>
@@ -14694,8 +15147,11 @@
       <c r="O151">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P151" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>140</v>
       </c>
@@ -14741,8 +15197,11 @@
       <c r="O152">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P152" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>141</v>
       </c>
@@ -14785,8 +15244,11 @@
       <c r="O153">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P153" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>142</v>
       </c>
@@ -14832,8 +15294,11 @@
       <c r="O154">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P154" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>143</v>
       </c>
@@ -14879,8 +15344,11 @@
       <c r="O155">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P155" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>144</v>
       </c>
@@ -14926,8 +15394,11 @@
       <c r="O156">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P156" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>145</v>
       </c>
@@ -14970,8 +15441,11 @@
       <c r="O157">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P157" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>146</v>
       </c>
@@ -15017,8 +15491,11 @@
       <c r="O158">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P158" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>147</v>
       </c>
@@ -15064,8 +15541,11 @@
       <c r="O159">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P159" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>148</v>
       </c>
@@ -15111,8 +15591,11 @@
       <c r="O160">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P160" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>149</v>
       </c>
@@ -15158,8 +15641,11 @@
       <c r="O161">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P161" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>150</v>
       </c>
@@ -15205,8 +15691,11 @@
       <c r="O162">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P162" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>151</v>
       </c>
@@ -15252,8 +15741,11 @@
       <c r="O163">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P163" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>152</v>
       </c>
@@ -15299,8 +15791,11 @@
       <c r="O164">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P164" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>153</v>
       </c>
@@ -15346,8 +15841,11 @@
       <c r="O165">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P165" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>154</v>
       </c>
@@ -15393,8 +15891,11 @@
       <c r="O166">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P166" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>155</v>
       </c>
@@ -15440,8 +15941,11 @@
       <c r="O167">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P167" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>303</v>
       </c>
@@ -15484,8 +15988,11 @@
       <c r="N168">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P168" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>156</v>
       </c>
@@ -15531,8 +16038,11 @@
       <c r="O169">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P169" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>157</v>
       </c>
@@ -15578,8 +16088,11 @@
       <c r="O170">
         <v>0.83</v>
       </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P170" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>158</v>
       </c>
@@ -15622,8 +16135,11 @@
       <c r="O171">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P171" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>159</v>
       </c>
@@ -15669,8 +16185,11 @@
       <c r="O172">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P172" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>160</v>
       </c>
@@ -15716,8 +16235,11 @@
       <c r="O173">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P173" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>161</v>
       </c>
@@ -15763,8 +16285,11 @@
       <c r="O174">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P174" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>162</v>
       </c>
@@ -15810,8 +16335,11 @@
       <c r="O175">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P175" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>163</v>
       </c>
@@ -15857,8 +16385,11 @@
       <c r="O176">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P176" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>164</v>
       </c>
@@ -15904,8 +16435,11 @@
       <c r="O177">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P177" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>165</v>
       </c>
@@ -15951,8 +16485,11 @@
       <c r="O178">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P178" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>166</v>
       </c>
@@ -15998,8 +16535,11 @@
       <c r="O179">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P179" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>167</v>
       </c>
@@ -16045,8 +16585,11 @@
       <c r="O180">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P180" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>168</v>
       </c>
@@ -16092,8 +16635,11 @@
       <c r="O181">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P181" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>169</v>
       </c>
@@ -16139,8 +16685,11 @@
       <c r="O182">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P182" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>170</v>
       </c>
@@ -16183,8 +16732,11 @@
       <c r="O183">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P183" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>171</v>
       </c>
@@ -16230,8 +16782,11 @@
       <c r="O184">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P184" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>172</v>
       </c>
@@ -16277,8 +16832,11 @@
       <c r="O185">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P185" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>173</v>
       </c>
@@ -16324,8 +16882,11 @@
       <c r="O186">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P186" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>174</v>
       </c>
@@ -16368,8 +16929,11 @@
       <c r="O187">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P187" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>175</v>
       </c>
@@ -16415,8 +16979,11 @@
       <c r="O188">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P188" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>176</v>
       </c>
@@ -16462,8 +17029,11 @@
       <c r="O189">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P189" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>177</v>
       </c>
@@ -16509,8 +17079,11 @@
       <c r="O190">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P190" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>178</v>
       </c>
@@ -16556,8 +17129,11 @@
       <c r="O191">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P191" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>179</v>
       </c>
@@ -16603,8 +17179,11 @@
       <c r="O192">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P192" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>180</v>
       </c>
@@ -16650,8 +17229,11 @@
       <c r="O193">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P193" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>181</v>
       </c>
@@ -16697,8 +17279,11 @@
       <c r="O194">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P194" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>182</v>
       </c>
@@ -16744,8 +17329,11 @@
       <c r="O195">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P195" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>284</v>
       </c>
@@ -16785,8 +17373,11 @@
       <c r="M196" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P196" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>183</v>
       </c>
@@ -16832,8 +17423,11 @@
       <c r="O197">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P197" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>184</v>
       </c>
@@ -16879,8 +17473,11 @@
       <c r="O198">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P198" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>185</v>
       </c>
@@ -16926,8 +17523,11 @@
       <c r="O199">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P199" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>186</v>
       </c>
@@ -16973,8 +17573,11 @@
       <c r="O200">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P200" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>187</v>
       </c>
@@ -17020,8 +17623,11 @@
       <c r="O201">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P201" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>188</v>
       </c>
@@ -17064,8 +17670,11 @@
       <c r="O202">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P202" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>189</v>
       </c>
@@ -17111,8 +17720,11 @@
       <c r="O203">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P203" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>190</v>
       </c>
@@ -17158,8 +17770,11 @@
       <c r="O204">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P204" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>191</v>
       </c>
@@ -17205,8 +17820,11 @@
       <c r="O205">
         <v>0.87</v>
       </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P205" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>192</v>
       </c>
@@ -17252,8 +17870,11 @@
       <c r="O206">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P206" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>308</v>
       </c>
@@ -17293,8 +17914,11 @@
       <c r="M207" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P207" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>193</v>
       </c>
@@ -17340,8 +17964,11 @@
       <c r="O208">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P208" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>281</v>
       </c>
@@ -17381,8 +18008,11 @@
       <c r="M209" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P209" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>194</v>
       </c>
@@ -17428,8 +18058,11 @@
       <c r="O210">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P210" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>195</v>
       </c>
@@ -17475,8 +18108,11 @@
       <c r="O211">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P211" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>196</v>
       </c>
@@ -17522,8 +18158,11 @@
       <c r="O212">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P212" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>197</v>
       </c>
@@ -17569,8 +18208,11 @@
       <c r="O213">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P213" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>198</v>
       </c>
@@ -17616,8 +18258,11 @@
       <c r="O214">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P214" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>199</v>
       </c>
@@ -17663,8 +18308,11 @@
       <c r="O215">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P215" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>200</v>
       </c>
@@ -17710,8 +18358,11 @@
       <c r="O216">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P216" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>201</v>
       </c>
@@ -17757,8 +18408,11 @@
       <c r="O217">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P217" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>305</v>
       </c>
@@ -17798,8 +18452,11 @@
       <c r="M218" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P218" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>202</v>
       </c>
@@ -17845,8 +18502,11 @@
       <c r="O219">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P219" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>306</v>
       </c>
@@ -17886,8 +18546,11 @@
       <c r="M220" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P220" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>203</v>
       </c>
@@ -17933,8 +18596,11 @@
       <c r="O221">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P221" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>204</v>
       </c>
@@ -17980,8 +18646,11 @@
       <c r="O222">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P222" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>205</v>
       </c>
@@ -18027,8 +18696,11 @@
       <c r="O223">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P223" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>206</v>
       </c>
@@ -18074,8 +18746,11 @@
       <c r="O224">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P224" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>208</v>
       </c>
@@ -18121,8 +18796,11 @@
       <c r="O225">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P225" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>209</v>
       </c>
@@ -18165,8 +18843,11 @@
       <c r="O226">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P226" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>311</v>
       </c>
@@ -18209,8 +18890,11 @@
       <c r="O227">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P227" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>210</v>
       </c>
@@ -18256,8 +18940,11 @@
       <c r="O228">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P228" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>211</v>
       </c>
@@ -18303,8 +18990,11 @@
       <c r="O229">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P229" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>213</v>
       </c>
@@ -18347,8 +19037,11 @@
       <c r="O230">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P230" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>214</v>
       </c>
@@ -18394,8 +19087,11 @@
       <c r="O231">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P231" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>215</v>
       </c>
@@ -18441,8 +19137,11 @@
       <c r="O232">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P232" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>216</v>
       </c>
@@ -18488,8 +19187,11 @@
       <c r="O233">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P233" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>287</v>
       </c>
@@ -18529,8 +19231,11 @@
       <c r="M234" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P234" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>217</v>
       </c>
@@ -18576,8 +19281,11 @@
       <c r="O235">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P235" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>218</v>
       </c>
@@ -18623,8 +19331,11 @@
       <c r="O236">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P236" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>219</v>
       </c>
@@ -18670,8 +19381,11 @@
       <c r="O237">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P237" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>220</v>
       </c>
@@ -18714,8 +19428,11 @@
       <c r="O238">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P238" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>221</v>
       </c>
@@ -18761,8 +19478,11 @@
       <c r="O239">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P239" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>222</v>
       </c>
@@ -18805,8 +19525,11 @@
       <c r="O240">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P240" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>223</v>
       </c>
@@ -18852,8 +19575,11 @@
       <c r="O241">
         <v>0.81</v>
       </c>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P241" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>224</v>
       </c>
@@ -18899,8 +19625,11 @@
       <c r="O242">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P242" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>225</v>
       </c>
@@ -18946,8 +19675,11 @@
       <c r="O243">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P243" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>286</v>
       </c>
@@ -18987,8 +19719,11 @@
       <c r="M244" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P244" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>227</v>
       </c>
@@ -19028,8 +19763,11 @@
       <c r="M245" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P245" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>228</v>
       </c>
@@ -19069,8 +19807,11 @@
       <c r="M246" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P246" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>229</v>
       </c>
@@ -19116,8 +19857,11 @@
       <c r="O247">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P247" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>231</v>
       </c>
@@ -19163,8 +19907,11 @@
       <c r="O248">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P248" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>232</v>
       </c>
@@ -19210,8 +19957,11 @@
       <c r="O249">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P249" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>233</v>
       </c>
@@ -19254,8 +20004,11 @@
       <c r="O250">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P250" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>230</v>
       </c>
@@ -19301,8 +20054,11 @@
       <c r="O251">
         <v>0.77</v>
       </c>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P251" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>234</v>
       </c>
@@ -19348,8 +20104,11 @@
       <c r="O252">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P252" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>235</v>
       </c>
@@ -19395,8 +20154,11 @@
       <c r="O253">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P253" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>236</v>
       </c>
@@ -19433,8 +20195,11 @@
       <c r="M254" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P254" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>237</v>
       </c>
@@ -19480,8 +20245,11 @@
       <c r="O255">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P255" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>238</v>
       </c>
@@ -19527,8 +20295,11 @@
       <c r="O256">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P256" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>239</v>
       </c>
@@ -19574,8 +20345,11 @@
       <c r="O257">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P257" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>240</v>
       </c>
@@ -19621,8 +20395,11 @@
       <c r="O258">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P258" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>241</v>
       </c>
@@ -19668,8 +20445,11 @@
       <c r="O259">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P259" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>242</v>
       </c>
@@ -19715,8 +20495,11 @@
       <c r="O260">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P260" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>243</v>
       </c>
@@ -19759,8 +20542,11 @@
       <c r="O261">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P261" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>244</v>
       </c>
@@ -19806,8 +20592,11 @@
       <c r="O262">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P262" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>283</v>
       </c>
@@ -19847,8 +20636,11 @@
       <c r="M263" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P263" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>246</v>
       </c>
@@ -19894,8 +20686,11 @@
       <c r="O264">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P264" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>247</v>
       </c>
@@ -19938,8 +20733,11 @@
       <c r="O265">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P265" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>248</v>
       </c>
@@ -19985,8 +20783,11 @@
       <c r="O266">
         <v>0.82</v>
       </c>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P266" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>249</v>
       </c>
@@ -20032,8 +20833,11 @@
       <c r="O267">
         <v>0.86</v>
       </c>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P267" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>250</v>
       </c>
@@ -20079,8 +20883,11 @@
       <c r="O268">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P268" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>252</v>
       </c>
@@ -20126,8 +20933,11 @@
       <c r="O269">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P269" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>253</v>
       </c>
@@ -20173,8 +20983,11 @@
       <c r="O270">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P270" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>254</v>
       </c>
@@ -20214,8 +21027,11 @@
       <c r="M271" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P271" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>255</v>
       </c>
@@ -20258,8 +21074,11 @@
       <c r="O272">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P272" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>256</v>
       </c>
@@ -20305,8 +21124,11 @@
       <c r="O273">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P273" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>257</v>
       </c>
@@ -20352,8 +21174,11 @@
       <c r="O274">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P274" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>310</v>
       </c>
@@ -20393,8 +21218,11 @@
       <c r="M275" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P275" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>258</v>
       </c>
@@ -20437,8 +21265,11 @@
       <c r="O276">
         <v>0.91</v>
       </c>
-    </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P276" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>285</v>
       </c>
@@ -20478,8 +21309,11 @@
       <c r="M277" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P277" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>226</v>
       </c>
@@ -20525,8 +21359,11 @@
       <c r="O278">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P278" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>259</v>
       </c>
@@ -20572,8 +21409,11 @@
       <c r="O279">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P279" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>316</v>
       </c>
@@ -20613,8 +21453,11 @@
       <c r="M280" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P280" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>260</v>
       </c>
@@ -20660,8 +21503,11 @@
       <c r="O281">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P281" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>315</v>
       </c>
@@ -20701,8 +21547,11 @@
       <c r="M282" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P282" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>261</v>
       </c>
@@ -20748,8 +21597,11 @@
       <c r="O283">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P283" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>262</v>
       </c>
@@ -20795,8 +21647,11 @@
       <c r="O284">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P284" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>263</v>
       </c>
@@ -20842,8 +21697,11 @@
       <c r="O285">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P285" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>317</v>
       </c>
@@ -20883,8 +21741,11 @@
       <c r="M286" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P286" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>264</v>
       </c>
@@ -20930,8 +21791,11 @@
       <c r="O287">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P287" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>265</v>
       </c>
@@ -20977,8 +21841,11 @@
       <c r="O288">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P288" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>266</v>
       </c>
@@ -21024,8 +21891,11 @@
       <c r="O289">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P289" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>267</v>
       </c>
@@ -21071,8 +21941,11 @@
       <c r="O290">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P290" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>269</v>
       </c>
@@ -21115,8 +21988,11 @@
       <c r="O291">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P291" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>270</v>
       </c>
@@ -21162,8 +22038,11 @@
       <c r="O292">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P292" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>271</v>
       </c>
@@ -21209,8 +22088,11 @@
       <c r="O293">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P293" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>272</v>
       </c>
@@ -21256,8 +22138,11 @@
       <c r="O294">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P294" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>212</v>
       </c>
@@ -21297,8 +22182,11 @@
       <c r="M295" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P295" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>274</v>
       </c>
@@ -21344,8 +22232,11 @@
       <c r="O296">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P296" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>275</v>
       </c>
@@ -21391,8 +22282,11 @@
       <c r="O297">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P297" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>276</v>
       </c>
@@ -21438,8 +22332,11 @@
       <c r="O298">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P298" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>277</v>
       </c>
@@ -21485,8 +22382,11 @@
       <c r="O299">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P299" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>278</v>
       </c>
@@ -21529,8 +22429,11 @@
       <c r="O300">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P300" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>309</v>
       </c>
@@ -21569,6 +22472,9 @@
       </c>
       <c r="M301" t="s">
         <v>36</v>
+      </c>
+      <c r="P301" t="s">
+        <v>2268</v>
       </c>
     </row>
   </sheetData>
@@ -55405,7 +56311,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:BM301"/>
+  <dimension ref="A1:BM300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -96966,11 +97872,6 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="301" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="BM301" t="s">
-        <v>2223</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="AC1:AC300" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BK300">

--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D35ADC4-AD9E-4400-91C2-0CA214A1A8D0}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C1BF07-830D-4D89-AAE0-FCD9D2CA1881}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="species" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'all data'!$AC$1:$AC$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">colors!$A$1:$A$335</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$L$1:$L$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$B$1:$B$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C1BF07-830D-4D89-AAE0-FCD9D2CA1881}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C438AE63-C5C7-486A-9C10-4BCDB06FEA7A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="species" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19916" uniqueCount="2269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19916" uniqueCount="2271">
   <si>
     <t>ID</t>
   </si>
@@ -6859,6 +6859,12 @@
   </si>
   <si>
     <t>pink</t>
+  </si>
+  <si>
+    <t>sycamo</t>
+  </si>
+  <si>
+    <t>Manchurian Walnut</t>
   </si>
 </sst>
 </file>
@@ -20792,7 +20798,7 @@
         <v>249</v>
       </c>
       <c r="B267" t="s">
-        <v>848</v>
+        <v>2269</v>
       </c>
       <c r="C267" t="s">
         <v>849</v>
@@ -21192,7 +21198,7 @@
         <v>1032</v>
       </c>
       <c r="E275" t="s">
-        <v>1036</v>
+        <v>2270</v>
       </c>
       <c r="F275" t="s">
         <v>1037</v>
@@ -22197,10 +22203,10 @@
         <v>137</v>
       </c>
       <c r="D296" t="s">
-        <v>1101</v>
+        <v>2264</v>
       </c>
       <c r="E296" t="s">
-        <v>1102</v>
+        <v>2262</v>
       </c>
       <c r="F296" t="s">
         <v>1103</v>

--- a/NWspecies060222.xlsx
+++ b/NWspecies060222.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f0f4fad9919cbe5b/Neighbourwoods/NWAnalytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C438AE63-C5C7-486A-9C10-4BCDB06FEA7A}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{DD247510-64D4-4C56-90AC-C75474531547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B4B925E-0931-4367-B949-35B724ECC164}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'all data'!$AC$1:$AC$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">colors!$A$1:$A$335</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$B$1:$B$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">species!$L$1:$L$301</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -7779,12 +7779,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A1:P301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.5703125" customWidth="1"/>
@@ -7846,7 +7847,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7896,7 +7897,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7946,7 +7947,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7993,7 +7994,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8043,7 +8044,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>318</v>
       </c>
@@ -8087,7 +8088,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8181,7 +8182,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8225,7 +8226,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>282</v>
       </c>
@@ -8269,7 +8270,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -8319,7 +8320,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -8369,7 +8370,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -8419,7 +8420,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -8469,7 +8470,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -8519,7 +8520,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -8566,7 +8567,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -8616,7 +8617,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -8666,7 +8667,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -8716,7 +8717,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -8766,7 +8767,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -8816,7 +8817,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -8866,7 +8867,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -8916,7 +8917,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -8963,7 +8964,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>312</v>
       </c>
@@ -9010,7 +9011,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>23</v>
       </c>
@@ -9060,7 +9061,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>24</v>
       </c>
@@ -9110,7 +9111,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25</v>
       </c>
@@ -9160,7 +9161,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -9210,7 +9211,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>27</v>
       </c>
@@ -9260,7 +9261,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>28</v>
       </c>
@@ -9307,7 +9308,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>29</v>
       </c>
@@ -9357,7 +9358,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>30</v>
       </c>
@@ -9407,7 +9408,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>31</v>
       </c>
@@ -9457,7 +9458,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>33</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>34</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>35</v>
       </c>
@@ -9654,7 +9655,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>319</v>
       </c>
@@ -9701,7 +9702,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>320</v>
       </c>
@@ -9742,7 +9743,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>36</v>
       </c>
@@ -9792,7 +9793,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -9842,7 +9843,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>38</v>
       </c>
@@ -9892,7 +9893,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>39</v>
       </c>
@@ -9942,7 +9943,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>40</v>
       </c>
@@ -9989,7 +9990,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>41</v>
       </c>
@@ -10039,7 +10040,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>42</v>
       </c>
@@ -10089,7 +10090,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>43</v>
       </c>
@@ -10139,7 +10140,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>44</v>
       </c>
@@ -10186,7 +10187,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>307</v>
       </c>
@@ -10230,7 +10231,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>45</v>
       </c>
@@ -10280,7 +10281,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>46</v>
       </c>
@@ -10330,7 +10331,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>47</v>
       </c>
@@ -10380,7 +10381,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>48</v>
       </c>
@@ -10430,7 +10431,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>49</v>
       </c>
@@ -10480,7 +10481,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>50</v>
       </c>
@@ -10530,7 +10531,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>51</v>
       </c>
@@ -10580,7 +10581,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>52</v>
       </c>
@@ -10630,7 +10631,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>53</v>
       </c>
@@ -10680,7 +10681,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>54</v>
       </c>
@@ -10730,7 +10731,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>55</v>
       </c>
@@ -10780,7 +10781,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>56</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>57</v>
       </c>
@@ -10880,7 +10881,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>58</v>
       </c>
@@ -10924,7 +10925,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>59</v>
       </c>
@@ -10971,7 +10972,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>60</v>
       </c>
@@ -11021,7 +11022,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>61</v>
       </c>
@@ -11071,7 +11072,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>62</v>
       </c>
@@ -11121,7 +11122,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>64</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>65</v>
       </c>
@@ -11221,7 +11222,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>66</v>
       </c>
@@ -11315,7 +11316,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>68</v>
       </c>
@@ -11365,7 +11366,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>69</v>
       </c>
@@ -11415,7 +11416,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>70</v>
       </c>
@@ -11465,7 +11466,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>289</v>
       </c>
@@ -11509,7 +11510,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>71</v>
       </c>
@@ -11559,7 +11560,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>72</v>
       </c>
@@ -11609,7 +11610,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>313</v>
       </c>
@@ -11653,7 +11654,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>73</v>
       </c>
@@ -11700,7 +11701,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>75</v>
       </c>
@@ -11747,7 +11748,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>76</v>
       </c>
@@ -11797,7 +11798,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>77</v>
       </c>
@@ -11847,7 +11848,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>314</v>
       </c>
@@ -11894,7 +11895,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>78</v>
       </c>
@@ -11944,7 +11945,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>79</v>
       </c>
@@ -11994,7 +11995,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>80</v>
       </c>
@@ -12044,7 +12045,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>81</v>
       </c>
@@ -12094,7 +12095,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>82</v>
       </c>
@@ -12144,7 +12145,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>83</v>
       </c>
@@ -12194,7 +12195,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>84</v>
       </c>
@@ -12244,7 +12245,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>85</v>
       </c>
@@ -12291,7 +12292,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>86</v>
       </c>
@@ -12341,7 +12342,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>87</v>
       </c>
@@ -12388,7 +12389,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>88</v>
       </c>
@@ -12438,7 +12439,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>89</v>
       </c>
@@ -12488,7 +12489,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>90</v>
       </c>
@@ -12538,7 +12539,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>91</v>
       </c>
@@ -12588,7 +12589,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>92</v>
       </c>
@@ -12635,7 +12636,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>93</v>
       </c>
@@ -12685,7 +12686,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>94</v>
       </c>
@@ -12779,7 +12780,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>96</v>
       </c>
@@ -12829,7 +12830,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>97</v>
       </c>
@@ -12879,7 +12880,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>98</v>
       </c>
@@ -12929,7 +12930,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>99</v>
       </c>
@@ -12979,7 +12980,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>100</v>
       </c>
@@ -13029,7 +13030,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>101</v>
       </c>
@@ -13079,7 +13080,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>102</v>
       </c>
@@ -13129,7 +13130,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>103</v>
       </c>
@@ -13179,7 +13180,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>290</v>
       </c>
@@ -13223,7 +13224,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>104</v>
       </c>
@@ -13273,7 +13274,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>105</v>
       </c>
@@ -13320,7 +13321,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>106</v>
       </c>
@@ -13370,7 +13371,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>107</v>
       </c>
@@ -13420,7 +13421,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>108</v>
       </c>
@@ -13511,7 +13512,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>110</v>
       </c>
@@ -13561,7 +13562,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>111</v>
       </c>
@@ -13611,7 +13612,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>112</v>
       </c>
@@ -13661,7 +13662,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>113</v>
       </c>
@@ -13711,7 +13712,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>114</v>
       </c>
@@ -13761,7 +13762,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>115</v>
       </c>
@@ -13808,7 +13809,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>116</v>
       </c>
@@ -13852,7 +13853,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>300</v>
       </c>
@@ -13896,7 +13897,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>117</v>
       </c>
@@ -13940,7 +13941,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>118</v>
       </c>
@@ -13990,7 +13991,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>119</v>
       </c>
@@ -14040,7 +14041,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>120</v>
       </c>
@@ -14090,7 +14091,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>121</v>
       </c>
@@ -14140,7 +14141,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>122</v>
       </c>
@@ -14184,7 +14185,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>123</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>124</v>
       </c>
@@ -14284,7 +14285,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>304</v>
       </c>
@@ -14328,7 +14329,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>125</v>
       </c>
@@ -14378,7 +14379,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>301</v>
       </c>
@@ -14422,7 +14423,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>302</v>
       </c>
@@ -14466,7 +14467,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126</v>
       </c>
@@ -14516,7 +14517,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>127</v>
       </c>
@@ -14563,7 +14564,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>128</v>
       </c>
@@ -14613,7 +14614,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>129</v>
       </c>
@@ -14663,7 +14664,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>130</v>
       </c>
@@ -14713,7 +14714,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>131</v>
       </c>
@@ -14763,7 +14764,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>132</v>
       </c>
@@ -14810,7 +14811,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>133</v>
       </c>
@@ -14860,7 +14861,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>134</v>
       </c>
@@ -14910,7 +14911,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>135</v>
       </c>
@@ -14957,7 +14958,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>136</v>
       </c>
@@ -15007,7 +15008,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>137</v>
       </c>
@@ -15057,7 +15058,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>138</v>
       </c>
@@ -15107,7 +15108,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>139</v>
       </c>
@@ -15157,7 +15158,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>140</v>
       </c>
@@ -15207,7 +15208,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>141</v>
       </c>
@@ -15254,7 +15255,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>142</v>
       </c>
@@ -15304,7 +15305,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>143</v>
       </c>
@@ -15354,7 +15355,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>144</v>
       </c>
@@ -15404,7 +15405,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>145</v>
       </c>
@@ -15451,7 +15452,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>146</v>
       </c>
@@ -15501,7 +15502,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>147</v>
       </c>
@@ -15551,7 +15552,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>148</v>
       </c>
@@ -15601,7 +15602,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>149</v>
       </c>
@@ -15651,7 +15652,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>150</v>
       </c>
@@ -15701,7 +15702,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>151</v>
       </c>
@@ -15751,7 +15752,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>152</v>
       </c>
@@ -15801,7 +15802,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>153</v>
       </c>
@@ -15851,7 +15852,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>154</v>
       </c>
@@ -15901,7 +15902,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>155</v>
       </c>
@@ -15951,7 +15952,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>303</v>
       </c>
@@ -15998,7 +15999,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>156</v>
       </c>
@@ -16048,7 +16049,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>157</v>
       </c>
@@ -16098,7 +16099,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>158</v>
       </c>
@@ -16145,7 +16146,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>159</v>
       </c>
@@ -16195,7 +16196,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>160</v>
       </c>
@@ -16245,7 +16246,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>161</v>
       </c>
@@ -16295,7 +16296,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>162</v>
       </c>
@@ -16345,7 +16346,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>163</v>
       </c>
@@ -16395,7 +16396,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>164</v>
       </c>
@@ -16445,7 +16446,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>165</v>
       </c>
@@ -16495,7 +16496,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>166</v>
       </c>
@@ -16545,7 +16546,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>167</v>
       </c>
@@ -16595,7 +16596,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>168</v>
       </c>
@@ -16645,7 +16646,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>169</v>
       </c>
@@ -16695,7 +16696,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>170</v>
       </c>
@@ -16742,7 +16743,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>171</v>
       </c>
@@ -16792,7 +16793,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>172</v>
       </c>
@@ -16842,7 +16843,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>173</v>
       </c>
@@ -16892,7 +16893,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>174</v>
       </c>
@@ -16939,7 +16940,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>175</v>
       </c>
@@ -16989,7 +16990,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>176</v>
       </c>
@@ -17039,7 +17040,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>177</v>
       </c>
@@ -17089,7 +17090,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>178</v>
       </c>
@@ -17139,7 +17140,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>179</v>
       </c>
@@ -17189,7 +17190,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>180</v>
       </c>
@@ -17239,7 +17240,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>181</v>
       </c>
@@ -17289,7 +17290,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>182</v>
       </c>
@@ -17339,7 +17340,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>284</v>
       </c>
@@ -17383,7 +17384,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>183</v>
       </c>
@@ -17433,7 +17434,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>184</v>
       </c>
@@ -17483,7 +17484,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>185</v>
       </c>
@@ -17533,7 +17534,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>186</v>
       </c>
@@ -17583,7 +17584,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>187</v>
       </c>
@@ -17633,7 +17634,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>188</v>
       </c>
@@ -17680,7 +17681,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>189</v>
       </c>
@@ -17730,7 +17731,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>190</v>
       </c>
@@ -17780,7 +17781,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>191</v>
       </c>
@@ -17830,7 +17831,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>192</v>
       </c>
@@ -17880,7 +17881,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>308</v>
       </c>
@@ -17924,7 +17925,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>193</v>
       </c>
@@ -17974,7 +17975,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>281</v>
       </c>
@@ -18018,7 +18019,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>194</v>
       </c>
@@ -18068,7 +18069,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>195</v>
       </c>
@@ -18118,7 +18119,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>196</v>
       </c>
@@ -18168,7 +18169,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>197</v>
       </c>
@@ -18218,7 +18219,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>198</v>
       </c>
@@ -18268,7 +18269,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>199</v>
       </c>
@@ -18318,7 +18319,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>200</v>
       </c>
@@ -18368,7 +18369,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>201</v>
       </c>
@@ -18418,7 +18419,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>305</v>
       </c>
@@ -18462,7 +18463,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>202</v>
       </c>
@@ -18512,7 +18513,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>306</v>
       </c>
@@ -18556,7 +18557,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>203</v>
       </c>
@@ -18606,7 +18607,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>204</v>
       </c>
@@ -18656,7 +18657,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>205</v>
       </c>
@@ -18706,7 +18707,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>206</v>
       </c>
@@ -18756,7 +18757,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>208</v>
       </c>
@@ -18806,7 +18807,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>209</v>
       </c>
@@ -18853,7 +18854,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>311</v>
       </c>
@@ -18900,7 +18901,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>210</v>
       </c>
@@ -18950,7 +18951,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>211</v>
       </c>
@@ -19000,7 +19001,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>213</v>
       </c>
@@ -19047,7 +19048,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>214</v>
       </c>
@@ -19097,7 +19098,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>215</v>
       </c>
@@ -19147,7 +19148,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>216</v>
       </c>
@@ -19197,7 +19198,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>287</v>
       </c>
@@ -19241,7 +19242,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>217</v>
       </c>
@@ -19291,7 +19292,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>218</v>
       </c>
@@ -19341,7 +19342,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>219</v>
       </c>
@@ -19391,7 +19392,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>220</v>
       </c>
@@ -19438,7 +19439,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>221</v>
       </c>
@@ -19488,7 +19489,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>222</v>
       </c>
@@ -19535,7 +19536,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>223</v>
       </c>
@@ -19585,7 +19586,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>224</v>
       </c>
@@ -19635,7 +19636,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>225</v>
       </c>
@@ -19685,7 +19686,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>286</v>
       </c>
@@ -19729,7 +19730,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>227</v>
       </c>
@@ -19773,7 +19774,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>228</v>
       </c>
@@ -19817,7 +19818,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>229</v>
       </c>
@@ -19867,7 +19868,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>231</v>
       </c>
@@ -19917,7 +19918,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>232</v>
       </c>
@@ -19967,7 +19968,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>233</v>
       </c>
@@ -20014,7 +20015,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>230</v>
       </c>
@@ -20064,7 +20065,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>234</v>
       </c>
@@ -20114,7 +20115,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>235</v>
       </c>
@@ -20205,7 +20206,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>237</v>
       </c>
@@ -20255,7 +20256,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>238</v>
       </c>
@@ -20305,7 +20306,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>239</v>
       </c>
@@ -20355,7 +20356,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>240</v>
       </c>
@@ -20405,7 +20406,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>241</v>
       </c>
@@ -20455,7 +20456,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>242</v>
       </c>
@@ -20505,7 +20506,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>243</v>
       </c>
@@ -20552,7 +20553,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>244</v>
       </c>
@@ -20646,7 +20647,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>246</v>
       </c>
@@ -20696,7 +20697,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>247</v>
       </c>
@@ -20743,7 +20744,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>248</v>
       </c>
@@ -20793,7 +20794,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>249</v>
       </c>
@@ -20843,7 +20844,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>250</v>
       </c>
@@ -20893,7 +20894,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>252</v>
       </c>
@@ -20943,7 +20944,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>253</v>
       </c>
@@ -21037,7 +21038,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>255</v>
       </c>
@@ -21084,7 +21085,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>256</v>
       </c>
@@ -21134,7 +21135,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>257</v>
       </c>
@@ -21184,7 +21185,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>310</v>
       </c>
@@ -21228,7 +21229,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>258</v>
       </c>
@@ -21275,7 +21276,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>285</v>
       </c>
@@ -21319,7 +21320,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>226</v>
       </c>
@@ -21369,7 +21370,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>259</v>
       </c>
@@ -21419,7 +21420,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>316</v>
       </c>
@@ -21463,7 +21464,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>260</v>
       </c>
@@ -21513,7 +21514,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>315</v>
       </c>
@@ -21557,7 +21558,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>261</v>
       </c>
@@ -21607,7 +21608,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>262</v>
       </c>
@@ -21657,7 +21658,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>263</v>
       </c>
@@ -21707,7 +21708,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>317</v>
       </c>
@@ -21751,7 +21752,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>264</v>
       </c>
@@ -21801,7 +21802,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>265</v>
       </c>
@@ -21851,7 +21852,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>266</v>
       </c>
@@ -21901,7 +21902,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>267</v>
       </c>
@@ -21951,7 +21952,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>269</v>
       </c>
@@ -21998,7 +21999,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>270</v>
       </c>
@@ -22048,7 +22049,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>271</v>
       </c>
@@ -22098,7 +22099,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>272</v>
       </c>
@@ -22192,7 +22193,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>274</v>
       </c>
@@ -22242,7 +22243,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>275</v>
       </c>
@@ -22292,7 +22293,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>276</v>
       </c>
@@ -22342,7 +22343,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>277</v>
       </c>
@@ -22392,7 +22393,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>278</v>
       </c>
@@ -22439,7 +22440,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>309</v>
       </c>
@@ -22484,6 +22485,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="L1:L301" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="other"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O301">
     <sortCondition ref="B2:B301"/>
   </sortState>
